--- a/템플릿/LH간이종심100-300억_템플릿.xlsx
+++ b/템플릿/LH간이종심100-300억_템플릿.xlsx
@@ -2698,7 +2698,7 @@
     <numFmt numFmtId="180" formatCode="0.0000%"/>
     <numFmt numFmtId="181" formatCode="_-* #,##0.000_-;\-* #,##0.000_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="182" formatCode="_-* #,##0.0000_-;\-* #,##0.0000_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="187" formatCode="_-* #,##0_-;\-* #,##0_-;_-* \-_-;_-@_-"/>
+    <numFmt numFmtId="183" formatCode="_-* #,##0_-;\-* #,##0_-;_-* \-_-;_-@_-"/>
   </numFmts>
   <fonts count="22" x14ac:knownFonts="1">
     <font>
@@ -3663,7 +3663,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="187" fontId="1" fillId="0" borderId="0" applyBorder="0" applyProtection="0">
+    <xf numFmtId="183" fontId="1" fillId="0" borderId="0" applyBorder="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyBorder="0" applyProtection="0">
@@ -4067,27 +4067,195 @@
     <xf numFmtId="10" fontId="7" fillId="0" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="7" fillId="10" borderId="46" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="7" fillId="10" borderId="43" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="7" fillId="10" borderId="46" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="7" fillId="10" borderId="43" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="41" fontId="7" fillId="5" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="41" fontId="7" fillId="5" borderId="41" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="7" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="6" fillId="2" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="41" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="41" fontId="7" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4100,126 +4268,6 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="7" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="22" fontId="6" fillId="2" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="180" fontId="9" fillId="2" borderId="17" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4228,54 +4276,6 @@
     </xf>
     <xf numFmtId="180" fontId="9" fillId="2" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="7" fillId="10" borderId="46" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="7" fillId="10" borderId="43" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="7" fillId="10" borderId="46" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="7" fillId="10" borderId="43" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -4605,14 +4605,15 @@
     <col min="1" max="1" width="2.88671875" style="71" customWidth="1"/>
     <col min="2" max="2" width="8.44140625" style="72" customWidth="1"/>
     <col min="3" max="3" width="8.88671875" style="17" customWidth="1"/>
-    <col min="4" max="6" width="8.88671875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="8.88671875" style="1" customWidth="1"/>
+    <col min="5" max="6" width="10" style="1" customWidth="1"/>
     <col min="7" max="7" width="8.21875" style="1" customWidth="1"/>
     <col min="8" max="8" width="7.5546875" style="1" customWidth="1"/>
     <col min="9" max="13" width="8.33203125" style="1" customWidth="1"/>
     <col min="14" max="14" width="7.5546875" style="1" customWidth="1"/>
     <col min="15" max="15" width="6.21875" style="1" customWidth="1"/>
     <col min="16" max="20" width="7.5546875" style="1" customWidth="1"/>
-    <col min="21" max="21" width="8.109375" style="1" customWidth="1"/>
+    <col min="21" max="21" width="9.33203125" style="1" customWidth="1"/>
     <col min="22" max="22" width="7.44140625" style="70" customWidth="1"/>
     <col min="23" max="27" width="8.109375" style="1" customWidth="1"/>
     <col min="28" max="28" width="8.44140625" style="1" customWidth="1"/>
@@ -4643,22 +4644,22 @@
       <c r="D1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="165"/>
-      <c r="F1" s="166"/>
+      <c r="E1" s="189"/>
+      <c r="F1" s="190"/>
       <c r="G1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="167"/>
-      <c r="I1" s="168"/>
-      <c r="J1" s="169"/>
+      <c r="H1" s="191"/>
+      <c r="I1" s="192"/>
+      <c r="J1" s="193"/>
       <c r="K1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="167">
-        <v>0</v>
-      </c>
-      <c r="M1" s="168"/>
-      <c r="N1" s="170"/>
+      <c r="L1" s="191">
+        <v>0</v>
+      </c>
+      <c r="M1" s="192"/>
+      <c r="N1" s="194"/>
       <c r="O1" s="6" t="s">
         <v>52</v>
       </c>
@@ -4672,20 +4673,20 @@
       <c r="W1" s="6"/>
       <c r="X1" s="6"/>
       <c r="Y1" s="6"/>
-      <c r="Z1" s="171" t="s">
+      <c r="Z1" s="184" t="s">
         <v>7</v>
       </c>
-      <c r="AA1" s="171"/>
+      <c r="AA1" s="184"/>
       <c r="AB1" s="7"/>
-      <c r="AC1" s="171" t="s">
+      <c r="AC1" s="184" t="s">
         <v>8</v>
       </c>
-      <c r="AD1" s="171"/>
-      <c r="AE1" s="162" t="s">
+      <c r="AD1" s="184"/>
+      <c r="AE1" s="185" t="s">
         <v>9</v>
       </c>
-      <c r="AF1" s="163"/>
-      <c r="AG1" s="164"/>
+      <c r="AF1" s="186"/>
+      <c r="AG1" s="187"/>
       <c r="AH1" s="6"/>
       <c r="AI1" s="6"/>
       <c r="AJ1" s="6"/>
@@ -4696,69 +4697,69 @@
       <c r="AO1" s="8"/>
     </row>
     <row r="2" spans="1:41" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="154" t="s">
+      <c r="A2" s="169" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="154"/>
-      <c r="C2" s="155"/>
+      <c r="B2" s="169"/>
+      <c r="C2" s="170"/>
       <c r="D2" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="156"/>
-      <c r="F2" s="157"/>
+      <c r="E2" s="171"/>
+      <c r="F2" s="172"/>
       <c r="G2" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="156">
+      <c r="H2" s="171">
         <f>E2</f>
         <v>0</v>
       </c>
-      <c r="I2" s="158"/>
-      <c r="J2" s="157"/>
+      <c r="I2" s="173"/>
+      <c r="J2" s="172"/>
       <c r="K2" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="L2" s="159">
+      <c r="L2" s="174">
         <f>H2*3</f>
         <v>0</v>
       </c>
-      <c r="M2" s="160"/>
+      <c r="M2" s="175"/>
       <c r="N2" s="12" t="s">
         <v>14</v>
       </c>
       <c r="O2" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="P2" s="161" t="s">
+      <c r="P2" s="176" t="s">
         <v>53</v>
       </c>
-      <c r="Q2" s="161"/>
-      <c r="R2" s="161"/>
-      <c r="S2" s="161"/>
-      <c r="T2" s="161"/>
+      <c r="Q2" s="176"/>
+      <c r="R2" s="176"/>
+      <c r="S2" s="176"/>
+      <c r="T2" s="176"/>
       <c r="U2" s="84" t="s">
         <v>51</v>
       </c>
       <c r="V2" s="14"/>
       <c r="W2" s="15"/>
-      <c r="X2" s="138" t="s">
-        <v>0</v>
-      </c>
-      <c r="Y2" s="138"/>
-      <c r="Z2" s="139"/>
-      <c r="AA2" s="140"/>
+      <c r="X2" s="188" t="s">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="188"/>
+      <c r="Z2" s="195"/>
+      <c r="AA2" s="196"/>
       <c r="AB2" s="83"/>
-      <c r="AC2" s="141">
+      <c r="AC2" s="197">
         <f>H1</f>
         <v>0</v>
       </c>
-      <c r="AD2" s="142"/>
-      <c r="AE2" s="183" t="e">
+      <c r="AD2" s="198"/>
+      <c r="AE2" s="199" t="e">
         <f>Z2/AC2</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AF2" s="184"/>
-      <c r="AG2" s="185"/>
+      <c r="AF2" s="200"/>
+      <c r="AG2" s="201"/>
       <c r="AI2" s="16"/>
       <c r="AJ2" s="17"/>
       <c r="AK2" s="17"/>
@@ -4769,77 +4770,77 @@
       </c>
     </row>
     <row r="3" spans="1:41" s="22" customFormat="1" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="143" t="s">
+      <c r="A3" s="177" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="145" t="s">
+      <c r="B3" s="179" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="147" t="s">
+      <c r="C3" s="167" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="147"/>
-      <c r="E3" s="147"/>
-      <c r="F3" s="147"/>
-      <c r="G3" s="147"/>
-      <c r="H3" s="147"/>
-      <c r="I3" s="148" t="s">
+      <c r="D3" s="167"/>
+      <c r="E3" s="167"/>
+      <c r="F3" s="167"/>
+      <c r="G3" s="167"/>
+      <c r="H3" s="167"/>
+      <c r="I3" s="181" t="s">
         <v>20</v>
       </c>
-      <c r="J3" s="149"/>
-      <c r="K3" s="147"/>
-      <c r="L3" s="149"/>
-      <c r="M3" s="150"/>
-      <c r="N3" s="147" t="s">
+      <c r="J3" s="163"/>
+      <c r="K3" s="167"/>
+      <c r="L3" s="163"/>
+      <c r="M3" s="182"/>
+      <c r="N3" s="167" t="s">
         <v>21</v>
       </c>
-      <c r="O3" s="152"/>
-      <c r="P3" s="147" t="s">
+      <c r="O3" s="154"/>
+      <c r="P3" s="167" t="s">
         <v>22</v>
       </c>
-      <c r="Q3" s="147"/>
-      <c r="R3" s="147"/>
-      <c r="S3" s="147"/>
-      <c r="T3" s="177"/>
-      <c r="U3" s="178" t="s">
+      <c r="Q3" s="167"/>
+      <c r="R3" s="167"/>
+      <c r="S3" s="167"/>
+      <c r="T3" s="168"/>
+      <c r="U3" s="162" t="s">
         <v>23</v>
       </c>
-      <c r="V3" s="149"/>
-      <c r="W3" s="149"/>
-      <c r="X3" s="149"/>
-      <c r="Y3" s="149"/>
-      <c r="Z3" s="149"/>
-      <c r="AA3" s="149"/>
-      <c r="AB3" s="149"/>
-      <c r="AC3" s="149"/>
-      <c r="AD3" s="149"/>
-      <c r="AE3" s="149"/>
-      <c r="AF3" s="149"/>
-      <c r="AG3" s="149"/>
-      <c r="AH3" s="179"/>
+      <c r="V3" s="163"/>
+      <c r="W3" s="163"/>
+      <c r="X3" s="163"/>
+      <c r="Y3" s="163"/>
+      <c r="Z3" s="163"/>
+      <c r="AA3" s="163"/>
+      <c r="AB3" s="163"/>
+      <c r="AC3" s="163"/>
+      <c r="AD3" s="163"/>
+      <c r="AE3" s="163"/>
+      <c r="AF3" s="163"/>
+      <c r="AG3" s="163"/>
+      <c r="AH3" s="164"/>
       <c r="AI3" s="26"/>
-      <c r="AJ3" s="180" t="s">
+      <c r="AJ3" s="165" t="s">
         <v>24</v>
       </c>
-      <c r="AK3" s="152" t="s">
+      <c r="AK3" s="154" t="s">
         <v>25</v>
       </c>
-      <c r="AL3" s="134" t="s">
+      <c r="AL3" s="156" t="s">
         <v>26</v>
       </c>
-      <c r="AM3" s="136" t="s">
+      <c r="AM3" s="158" t="s">
         <v>27</v>
       </c>
       <c r="AN3" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="AO3" s="132" t="s">
+      <c r="AO3" s="160" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:41" s="22" customFormat="1" ht="41.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="144"/>
-      <c r="B4" s="146"/>
+      <c r="A4" s="178"/>
+      <c r="B4" s="180"/>
       <c r="C4" s="23" t="s">
         <v>30</v>
       </c>
@@ -4873,8 +4874,8 @@
       <c r="M4" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="N4" s="151"/>
-      <c r="O4" s="153"/>
+      <c r="N4" s="183"/>
+      <c r="O4" s="155"/>
       <c r="P4" s="23" t="s">
         <v>37</v>
       </c>
@@ -4935,23 +4936,23 @@
       <c r="AI4" s="115" t="s">
         <v>47</v>
       </c>
-      <c r="AJ4" s="181"/>
-      <c r="AK4" s="153"/>
-      <c r="AL4" s="135"/>
-      <c r="AM4" s="137"/>
+      <c r="AJ4" s="166"/>
+      <c r="AK4" s="155"/>
+      <c r="AL4" s="157"/>
+      <c r="AM4" s="159"/>
       <c r="AN4" s="31"/>
-      <c r="AO4" s="133"/>
+      <c r="AO4" s="161"/>
     </row>
     <row r="5" spans="1:41" s="22" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="90">
         <v>1</v>
       </c>
-      <c r="B5" s="186"/>
-      <c r="C5" s="189"/>
-      <c r="D5" s="188"/>
-      <c r="E5" s="189"/>
-      <c r="F5" s="189"/>
-      <c r="G5" s="190"/>
+      <c r="B5" s="132"/>
+      <c r="C5" s="135"/>
+      <c r="D5" s="134"/>
+      <c r="E5" s="135"/>
+      <c r="F5" s="135"/>
+      <c r="G5" s="136"/>
       <c r="H5" s="34"/>
       <c r="I5" s="35"/>
       <c r="J5" s="36"/>
@@ -4963,11 +4964,11 @@
         <v>0</v>
       </c>
       <c r="O5" s="37"/>
-      <c r="P5" s="198"/>
-      <c r="Q5" s="199"/>
-      <c r="R5" s="199"/>
-      <c r="S5" s="199"/>
-      <c r="T5" s="199"/>
+      <c r="P5" s="144"/>
+      <c r="Q5" s="145"/>
+      <c r="R5" s="145"/>
+      <c r="S5" s="145"/>
+      <c r="T5" s="145"/>
       <c r="U5" s="40">
         <f>ROUND(((P5*I5)+(Q5*J5)+(R5*K5)+(S5*L5)+(T5*M5)),3)</f>
         <v>0</v>
@@ -5026,14 +5027,14 @@
     </row>
     <row r="6" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="91"/>
-      <c r="B6" s="187"/>
-      <c r="C6" s="174" t="s">
+      <c r="B6" s="133"/>
+      <c r="C6" s="148" t="s">
         <v>48</v>
       </c>
-      <c r="D6" s="175"/>
-      <c r="E6" s="175"/>
-      <c r="F6" s="175"/>
-      <c r="G6" s="176"/>
+      <c r="D6" s="149"/>
+      <c r="E6" s="149"/>
+      <c r="F6" s="149"/>
+      <c r="G6" s="150"/>
       <c r="H6" s="34"/>
       <c r="I6" s="57"/>
       <c r="J6" s="61"/>
@@ -5042,11 +5043,11 @@
       <c r="M6" s="85"/>
       <c r="N6" s="62"/>
       <c r="O6" s="37"/>
-      <c r="P6" s="200"/>
-      <c r="Q6" s="201"/>
-      <c r="R6" s="201"/>
-      <c r="S6" s="201"/>
-      <c r="T6" s="201"/>
+      <c r="P6" s="146"/>
+      <c r="Q6" s="147"/>
+      <c r="R6" s="147"/>
+      <c r="S6" s="147"/>
+      <c r="T6" s="147"/>
       <c r="U6" s="77">
         <f>(I5*P6)+(J5*Q6)+(K5*R6)+(L5*S6)+(M5*T6)</f>
         <v>0</v>
@@ -5076,12 +5077,12 @@
       <c r="A7" s="90">
         <v>2</v>
       </c>
-      <c r="B7" s="186"/>
-      <c r="C7" s="191"/>
-      <c r="D7" s="192"/>
-      <c r="E7" s="188"/>
-      <c r="F7" s="191"/>
-      <c r="G7" s="193"/>
+      <c r="B7" s="132"/>
+      <c r="C7" s="137"/>
+      <c r="D7" s="138"/>
+      <c r="E7" s="134"/>
+      <c r="F7" s="137"/>
+      <c r="G7" s="139"/>
       <c r="H7" s="34"/>
       <c r="I7" s="35"/>
       <c r="J7" s="36"/>
@@ -5093,11 +5094,11 @@
         <v>0</v>
       </c>
       <c r="O7" s="37"/>
-      <c r="P7" s="198"/>
-      <c r="Q7" s="199"/>
-      <c r="R7" s="199"/>
-      <c r="S7" s="199"/>
-      <c r="T7" s="199"/>
+      <c r="P7" s="144"/>
+      <c r="Q7" s="145"/>
+      <c r="R7" s="145"/>
+      <c r="S7" s="145"/>
+      <c r="T7" s="145"/>
       <c r="U7" s="40">
         <f>ROUND(((P7*I7)+(Q7*J7)+(R7*K7)+(S7*L7)+(T7*M7)),3)</f>
         <v>0</v>
@@ -5156,14 +5157,14 @@
     </row>
     <row r="8" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="91"/>
-      <c r="B8" s="186"/>
-      <c r="C8" s="174" t="s">
+      <c r="B8" s="132"/>
+      <c r="C8" s="148" t="s">
         <v>48</v>
       </c>
-      <c r="D8" s="175"/>
-      <c r="E8" s="175"/>
-      <c r="F8" s="175"/>
-      <c r="G8" s="176"/>
+      <c r="D8" s="149"/>
+      <c r="E8" s="149"/>
+      <c r="F8" s="149"/>
+      <c r="G8" s="150"/>
       <c r="H8" s="34"/>
       <c r="I8" s="57"/>
       <c r="J8" s="61"/>
@@ -5172,11 +5173,11 @@
       <c r="M8" s="85"/>
       <c r="N8" s="62"/>
       <c r="O8" s="37"/>
-      <c r="P8" s="200"/>
-      <c r="Q8" s="201"/>
-      <c r="R8" s="201"/>
-      <c r="S8" s="201"/>
-      <c r="T8" s="201"/>
+      <c r="P8" s="146"/>
+      <c r="Q8" s="147"/>
+      <c r="R8" s="147"/>
+      <c r="S8" s="147"/>
+      <c r="T8" s="147"/>
       <c r="U8" s="77">
         <f>(I7*P8)+(J7*Q8)+(K7*R8)+(L7*S8)+(M7*T8)</f>
         <v>0</v>
@@ -5206,12 +5207,12 @@
       <c r="A9" s="90">
         <v>3</v>
       </c>
-      <c r="B9" s="186"/>
-      <c r="C9" s="188"/>
-      <c r="D9" s="188"/>
-      <c r="E9" s="194"/>
-      <c r="F9" s="188"/>
-      <c r="G9" s="193"/>
+      <c r="B9" s="132"/>
+      <c r="C9" s="134"/>
+      <c r="D9" s="134"/>
+      <c r="E9" s="140"/>
+      <c r="F9" s="134"/>
+      <c r="G9" s="139"/>
       <c r="H9" s="34"/>
       <c r="I9" s="35"/>
       <c r="J9" s="61"/>
@@ -5223,11 +5224,11 @@
         <v>0</v>
       </c>
       <c r="O9" s="37"/>
-      <c r="P9" s="198"/>
-      <c r="Q9" s="199"/>
-      <c r="R9" s="199"/>
-      <c r="S9" s="199"/>
-      <c r="T9" s="199"/>
+      <c r="P9" s="144"/>
+      <c r="Q9" s="145"/>
+      <c r="R9" s="145"/>
+      <c r="S9" s="145"/>
+      <c r="T9" s="145"/>
       <c r="U9" s="40">
         <f>ROUND(((P9*I9)+(Q9*J9)+(R9*K9)+(S9*L9)+(T9*M9)),3)</f>
         <v>0</v>
@@ -5286,14 +5287,14 @@
     </row>
     <row r="10" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="91"/>
-      <c r="B10" s="187"/>
-      <c r="C10" s="174" t="s">
+      <c r="B10" s="133"/>
+      <c r="C10" s="148" t="s">
         <v>48</v>
       </c>
-      <c r="D10" s="175"/>
-      <c r="E10" s="175"/>
-      <c r="F10" s="175"/>
-      <c r="G10" s="176"/>
+      <c r="D10" s="149"/>
+      <c r="E10" s="149"/>
+      <c r="F10" s="149"/>
+      <c r="G10" s="150"/>
       <c r="H10" s="34"/>
       <c r="I10" s="57"/>
       <c r="J10" s="61"/>
@@ -5302,11 +5303,11 @@
       <c r="M10" s="85"/>
       <c r="N10" s="62"/>
       <c r="O10" s="37"/>
-      <c r="P10" s="200"/>
-      <c r="Q10" s="201"/>
-      <c r="R10" s="201"/>
-      <c r="S10" s="201"/>
-      <c r="T10" s="201"/>
+      <c r="P10" s="146"/>
+      <c r="Q10" s="147"/>
+      <c r="R10" s="147"/>
+      <c r="S10" s="147"/>
+      <c r="T10" s="147"/>
       <c r="U10" s="77">
         <f>(I9*P10)+(J9*Q10)+(K9*R10)+(L9*S10)+(M9*T10)</f>
         <v>0</v>
@@ -5336,12 +5337,12 @@
       <c r="A11" s="90">
         <v>4</v>
       </c>
-      <c r="B11" s="186"/>
-      <c r="C11" s="195"/>
-      <c r="D11" s="188"/>
-      <c r="E11" s="192"/>
-      <c r="F11" s="188"/>
-      <c r="G11" s="196"/>
+      <c r="B11" s="132"/>
+      <c r="C11" s="141"/>
+      <c r="D11" s="134"/>
+      <c r="E11" s="138"/>
+      <c r="F11" s="134"/>
+      <c r="G11" s="142"/>
       <c r="H11" s="34"/>
       <c r="I11" s="35"/>
       <c r="J11" s="36"/>
@@ -5353,11 +5354,11 @@
         <v>0</v>
       </c>
       <c r="O11" s="37"/>
-      <c r="P11" s="198"/>
-      <c r="Q11" s="199"/>
-      <c r="R11" s="199"/>
-      <c r="S11" s="199"/>
-      <c r="T11" s="199"/>
+      <c r="P11" s="144"/>
+      <c r="Q11" s="145"/>
+      <c r="R11" s="145"/>
+      <c r="S11" s="145"/>
+      <c r="T11" s="145"/>
       <c r="U11" s="40">
         <f>ROUND(((P11*I11)+(Q11*J11)+(R11*K11)+(S11*L11)+(T11*M11)),3)</f>
         <v>0</v>
@@ -5416,14 +5417,14 @@
     </row>
     <row r="12" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="91"/>
-      <c r="B12" s="187"/>
-      <c r="C12" s="174" t="s">
+      <c r="B12" s="133"/>
+      <c r="C12" s="148" t="s">
         <v>48</v>
       </c>
-      <c r="D12" s="175"/>
-      <c r="E12" s="175"/>
-      <c r="F12" s="175"/>
-      <c r="G12" s="176"/>
+      <c r="D12" s="149"/>
+      <c r="E12" s="149"/>
+      <c r="F12" s="149"/>
+      <c r="G12" s="150"/>
       <c r="H12" s="34"/>
       <c r="I12" s="57"/>
       <c r="J12" s="61"/>
@@ -5432,11 +5433,11 @@
       <c r="M12" s="85"/>
       <c r="N12" s="62"/>
       <c r="O12" s="37"/>
-      <c r="P12" s="200"/>
-      <c r="Q12" s="201"/>
-      <c r="R12" s="201"/>
-      <c r="S12" s="201"/>
-      <c r="T12" s="201"/>
+      <c r="P12" s="146"/>
+      <c r="Q12" s="147"/>
+      <c r="R12" s="147"/>
+      <c r="S12" s="147"/>
+      <c r="T12" s="147"/>
       <c r="U12" s="77">
         <f>(I11*P12)+(J11*Q12)+(K11*R12)+(L11*S12)+(M11*T12)</f>
         <v>0</v>
@@ -5466,12 +5467,12 @@
       <c r="A13" s="90">
         <v>5</v>
       </c>
-      <c r="B13" s="186"/>
-      <c r="C13" s="197"/>
-      <c r="D13" s="192"/>
-      <c r="E13" s="188"/>
-      <c r="F13" s="192"/>
-      <c r="G13" s="193"/>
+      <c r="B13" s="132"/>
+      <c r="C13" s="143"/>
+      <c r="D13" s="138"/>
+      <c r="E13" s="134"/>
+      <c r="F13" s="138"/>
+      <c r="G13" s="139"/>
       <c r="H13" s="34"/>
       <c r="I13" s="35"/>
       <c r="J13" s="36"/>
@@ -5483,11 +5484,11 @@
         <v>0</v>
       </c>
       <c r="O13" s="37"/>
-      <c r="P13" s="198"/>
-      <c r="Q13" s="199"/>
-      <c r="R13" s="199"/>
-      <c r="S13" s="199"/>
-      <c r="T13" s="199"/>
+      <c r="P13" s="144"/>
+      <c r="Q13" s="145"/>
+      <c r="R13" s="145"/>
+      <c r="S13" s="145"/>
+      <c r="T13" s="145"/>
       <c r="U13" s="40">
         <f>ROUND(((P13*I13)+(Q13*J13)+(R13*K13)+(S13*L13)+(T13*M13)),3)</f>
         <v>0</v>
@@ -5547,13 +5548,13 @@
     <row r="14" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="91"/>
       <c r="B14" s="89"/>
-      <c r="C14" s="174" t="s">
+      <c r="C14" s="148" t="s">
         <v>48</v>
       </c>
-      <c r="D14" s="175"/>
-      <c r="E14" s="175"/>
-      <c r="F14" s="175"/>
-      <c r="G14" s="176"/>
+      <c r="D14" s="149"/>
+      <c r="E14" s="149"/>
+      <c r="F14" s="149"/>
+      <c r="G14" s="150"/>
       <c r="H14" s="34"/>
       <c r="I14" s="57"/>
       <c r="J14" s="61"/>
@@ -5562,11 +5563,11 @@
       <c r="M14" s="85"/>
       <c r="N14" s="62"/>
       <c r="O14" s="37"/>
-      <c r="P14" s="199"/>
-      <c r="Q14" s="199"/>
-      <c r="R14" s="199"/>
-      <c r="S14" s="199"/>
-      <c r="T14" s="201"/>
+      <c r="P14" s="145"/>
+      <c r="Q14" s="145"/>
+      <c r="R14" s="145"/>
+      <c r="S14" s="145"/>
+      <c r="T14" s="147"/>
       <c r="U14" s="77">
         <f>(I13*P14)+(J13*Q14)+(K13*R14)+(L13*S14)+(M13*T14)</f>
         <v>0</v>
@@ -5595,11 +5596,11 @@
     <row r="15" spans="1:41" s="22" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="90"/>
       <c r="B15" s="88"/>
-      <c r="C15" s="189"/>
-      <c r="D15" s="189"/>
-      <c r="E15" s="191"/>
-      <c r="F15" s="192"/>
-      <c r="G15" s="193"/>
+      <c r="C15" s="135"/>
+      <c r="D15" s="135"/>
+      <c r="E15" s="137"/>
+      <c r="F15" s="138"/>
+      <c r="G15" s="139"/>
       <c r="H15" s="34"/>
       <c r="I15" s="35"/>
       <c r="J15" s="36"/>
@@ -5611,11 +5612,11 @@
         <v>0</v>
       </c>
       <c r="O15" s="37"/>
-      <c r="P15" s="198"/>
-      <c r="Q15" s="199"/>
-      <c r="R15" s="199"/>
-      <c r="S15" s="199"/>
-      <c r="T15" s="199"/>
+      <c r="P15" s="144"/>
+      <c r="Q15" s="145"/>
+      <c r="R15" s="145"/>
+      <c r="S15" s="145"/>
+      <c r="T15" s="145"/>
       <c r="U15" s="40">
         <f>ROUND(((P15*I15)+(Q15*J15)+(R15*K15)+(S15*L15)+(T15*M15)),3)</f>
         <v>0</v>
@@ -5675,13 +5676,13 @@
     <row r="16" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="91"/>
       <c r="B16" s="89"/>
-      <c r="C16" s="174" t="s">
+      <c r="C16" s="148" t="s">
         <v>48</v>
       </c>
-      <c r="D16" s="175"/>
-      <c r="E16" s="175"/>
-      <c r="F16" s="175"/>
-      <c r="G16" s="176"/>
+      <c r="D16" s="149"/>
+      <c r="E16" s="149"/>
+      <c r="F16" s="149"/>
+      <c r="G16" s="150"/>
       <c r="H16" s="34"/>
       <c r="I16" s="57"/>
       <c r="J16" s="61"/>
@@ -5690,11 +5691,11 @@
       <c r="M16" s="85"/>
       <c r="N16" s="62"/>
       <c r="O16" s="37"/>
-      <c r="P16" s="200"/>
-      <c r="Q16" s="201"/>
-      <c r="R16" s="201"/>
-      <c r="S16" s="201"/>
-      <c r="T16" s="201"/>
+      <c r="P16" s="146"/>
+      <c r="Q16" s="147"/>
+      <c r="R16" s="147"/>
+      <c r="S16" s="147"/>
+      <c r="T16" s="147"/>
       <c r="U16" s="77">
         <f>(I15*P16)+(J15*Q16)+(K15*R16)+(L15*S16)+(M15*T16)</f>
         <v>0</v>
@@ -5723,11 +5724,11 @@
     <row r="17" spans="1:41" s="22" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="90"/>
       <c r="B17" s="88"/>
-      <c r="C17" s="191"/>
-      <c r="D17" s="192"/>
-      <c r="E17" s="191"/>
-      <c r="F17" s="189"/>
-      <c r="G17" s="190"/>
+      <c r="C17" s="137"/>
+      <c r="D17" s="138"/>
+      <c r="E17" s="137"/>
+      <c r="F17" s="135"/>
+      <c r="G17" s="136"/>
       <c r="H17" s="58"/>
       <c r="I17" s="35"/>
       <c r="J17" s="36"/>
@@ -5739,11 +5740,11 @@
         <v>0</v>
       </c>
       <c r="O17" s="37"/>
-      <c r="P17" s="198"/>
-      <c r="Q17" s="199"/>
-      <c r="R17" s="199"/>
-      <c r="S17" s="199"/>
-      <c r="T17" s="199"/>
+      <c r="P17" s="144"/>
+      <c r="Q17" s="145"/>
+      <c r="R17" s="145"/>
+      <c r="S17" s="145"/>
+      <c r="T17" s="145"/>
       <c r="U17" s="40">
         <f>ROUND(((P17*I17)+(Q17*J17)+(R17*K17)+(S17*L17)+(T17*M17)),3)</f>
         <v>0</v>
@@ -5803,13 +5804,13 @@
     <row r="18" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="91"/>
       <c r="B18" s="89"/>
-      <c r="C18" s="174" t="s">
+      <c r="C18" s="148" t="s">
         <v>48</v>
       </c>
-      <c r="D18" s="175"/>
-      <c r="E18" s="175"/>
-      <c r="F18" s="175"/>
-      <c r="G18" s="176"/>
+      <c r="D18" s="149"/>
+      <c r="E18" s="149"/>
+      <c r="F18" s="149"/>
+      <c r="G18" s="150"/>
       <c r="H18" s="34"/>
       <c r="I18" s="57"/>
       <c r="J18" s="61"/>
@@ -5818,11 +5819,11 @@
       <c r="M18" s="85"/>
       <c r="N18" s="62"/>
       <c r="O18" s="37"/>
-      <c r="P18" s="199"/>
-      <c r="Q18" s="199"/>
-      <c r="R18" s="200"/>
-      <c r="S18" s="201"/>
-      <c r="T18" s="201"/>
+      <c r="P18" s="145"/>
+      <c r="Q18" s="145"/>
+      <c r="R18" s="146"/>
+      <c r="S18" s="147"/>
+      <c r="T18" s="147"/>
       <c r="U18" s="77">
         <f>(I17*P18)+(J17*Q18)+(K17*R18)+(L17*S18)+(M17*T18)</f>
         <v>0</v>
@@ -5867,11 +5868,11 @@
         <v>0</v>
       </c>
       <c r="O19" s="37"/>
-      <c r="P19" s="198"/>
-      <c r="Q19" s="199"/>
-      <c r="R19" s="199"/>
-      <c r="S19" s="199"/>
-      <c r="T19" s="199"/>
+      <c r="P19" s="144"/>
+      <c r="Q19" s="145"/>
+      <c r="R19" s="145"/>
+      <c r="S19" s="145"/>
+      <c r="T19" s="145"/>
       <c r="U19" s="40">
         <f>ROUND(((P19*I19)+(Q19*J19)+(R19*K19)+(S19*L19)+(T19*M19)),3)</f>
         <v>0</v>
@@ -5931,13 +5932,13 @@
     <row r="20" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="91"/>
       <c r="B20" s="89"/>
-      <c r="C20" s="172" t="s">
+      <c r="C20" s="151" t="s">
         <v>48</v>
       </c>
-      <c r="D20" s="173"/>
-      <c r="E20" s="173"/>
-      <c r="F20" s="173"/>
-      <c r="G20" s="182"/>
+      <c r="D20" s="152"/>
+      <c r="E20" s="152"/>
+      <c r="F20" s="152"/>
+      <c r="G20" s="153"/>
       <c r="H20" s="34"/>
       <c r="I20" s="57"/>
       <c r="J20" s="61"/>
@@ -6053,13 +6054,13 @@
     <row r="22" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="91"/>
       <c r="B22" s="89"/>
-      <c r="C22" s="172" t="s">
+      <c r="C22" s="151" t="s">
         <v>48</v>
       </c>
-      <c r="D22" s="173"/>
-      <c r="E22" s="173"/>
-      <c r="F22" s="173"/>
-      <c r="G22" s="182"/>
+      <c r="D22" s="152"/>
+      <c r="E22" s="152"/>
+      <c r="F22" s="152"/>
+      <c r="G22" s="153"/>
       <c r="H22" s="97"/>
       <c r="I22" s="98"/>
       <c r="J22" s="99"/>
@@ -6175,13 +6176,13 @@
     <row r="24" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="91"/>
       <c r="B24" s="89"/>
-      <c r="C24" s="172" t="s">
+      <c r="C24" s="151" t="s">
         <v>48</v>
       </c>
-      <c r="D24" s="173"/>
-      <c r="E24" s="173"/>
-      <c r="F24" s="173"/>
-      <c r="G24" s="182"/>
+      <c r="D24" s="152"/>
+      <c r="E24" s="152"/>
+      <c r="F24" s="152"/>
+      <c r="G24" s="153"/>
       <c r="H24" s="34"/>
       <c r="I24" s="57"/>
       <c r="J24" s="61"/>
@@ -6297,13 +6298,13 @@
     <row r="26" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="91"/>
       <c r="B26" s="89"/>
-      <c r="C26" s="172" t="s">
+      <c r="C26" s="151" t="s">
         <v>48</v>
       </c>
-      <c r="D26" s="173"/>
-      <c r="E26" s="173"/>
-      <c r="F26" s="173"/>
-      <c r="G26" s="182"/>
+      <c r="D26" s="152"/>
+      <c r="E26" s="152"/>
+      <c r="F26" s="152"/>
+      <c r="G26" s="153"/>
       <c r="H26" s="34"/>
       <c r="I26" s="57"/>
       <c r="J26" s="61"/>
@@ -6361,9 +6362,9 @@
         <v>0</v>
       </c>
       <c r="O27" s="37"/>
-      <c r="P27" s="198"/>
-      <c r="Q27" s="199"/>
-      <c r="R27" s="199"/>
+      <c r="P27" s="144"/>
+      <c r="Q27" s="145"/>
+      <c r="R27" s="145"/>
       <c r="S27" s="39"/>
       <c r="T27" s="39"/>
       <c r="U27" s="40">
@@ -6425,13 +6426,13 @@
     <row r="28" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="91"/>
       <c r="B28" s="89"/>
-      <c r="C28" s="174" t="s">
+      <c r="C28" s="148" t="s">
         <v>48</v>
       </c>
-      <c r="D28" s="175"/>
-      <c r="E28" s="175"/>
-      <c r="F28" s="175"/>
-      <c r="G28" s="176"/>
+      <c r="D28" s="149"/>
+      <c r="E28" s="149"/>
+      <c r="F28" s="149"/>
+      <c r="G28" s="150"/>
       <c r="H28" s="60"/>
       <c r="I28" s="57"/>
       <c r="J28" s="61"/>
@@ -6440,9 +6441,9 @@
       <c r="M28" s="131"/>
       <c r="N28" s="62"/>
       <c r="O28" s="37"/>
-      <c r="P28" s="201"/>
-      <c r="Q28" s="201"/>
-      <c r="R28" s="201"/>
+      <c r="P28" s="147"/>
+      <c r="Q28" s="147"/>
+      <c r="R28" s="147"/>
       <c r="S28" s="40"/>
       <c r="T28" s="40"/>
       <c r="U28" s="77">
@@ -6473,11 +6474,11 @@
     <row r="29" spans="1:41" s="22" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="90"/>
       <c r="B29" s="88"/>
-      <c r="C29" s="189"/>
-      <c r="D29" s="189"/>
-      <c r="E29" s="192"/>
-      <c r="F29" s="188"/>
-      <c r="G29" s="190"/>
+      <c r="C29" s="135"/>
+      <c r="D29" s="135"/>
+      <c r="E29" s="138"/>
+      <c r="F29" s="134"/>
+      <c r="G29" s="136"/>
       <c r="H29" s="34"/>
       <c r="I29" s="35"/>
       <c r="J29" s="36"/>
@@ -6489,9 +6490,9 @@
         <v>0</v>
       </c>
       <c r="O29" s="37"/>
-      <c r="P29" s="198"/>
-      <c r="Q29" s="199"/>
-      <c r="R29" s="199"/>
+      <c r="P29" s="144"/>
+      <c r="Q29" s="145"/>
+      <c r="R29" s="145"/>
       <c r="S29" s="39"/>
       <c r="T29" s="39"/>
       <c r="U29" s="40">
@@ -6553,13 +6554,13 @@
     <row r="30" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="91"/>
       <c r="B30" s="89"/>
-      <c r="C30" s="172" t="s">
+      <c r="C30" s="151" t="s">
         <v>48</v>
       </c>
-      <c r="D30" s="173"/>
-      <c r="E30" s="173"/>
-      <c r="F30" s="173"/>
-      <c r="G30" s="182"/>
+      <c r="D30" s="152"/>
+      <c r="E30" s="152"/>
+      <c r="F30" s="152"/>
+      <c r="G30" s="153"/>
       <c r="H30" s="34"/>
       <c r="I30" s="57"/>
       <c r="J30" s="61"/>
@@ -6568,9 +6569,9 @@
       <c r="M30" s="85"/>
       <c r="N30" s="62"/>
       <c r="O30" s="37"/>
-      <c r="P30" s="200"/>
-      <c r="Q30" s="201"/>
-      <c r="R30" s="201"/>
+      <c r="P30" s="146"/>
+      <c r="Q30" s="147"/>
+      <c r="R30" s="147"/>
       <c r="S30" s="40"/>
       <c r="T30" s="40"/>
       <c r="U30" s="77">
@@ -6617,9 +6618,9 @@
         <v>0</v>
       </c>
       <c r="O31" s="37"/>
-      <c r="P31" s="198"/>
-      <c r="Q31" s="198"/>
-      <c r="R31" s="199"/>
+      <c r="P31" s="144"/>
+      <c r="Q31" s="144"/>
+      <c r="R31" s="145"/>
       <c r="S31" s="39"/>
       <c r="T31" s="39"/>
       <c r="U31" s="40">
@@ -6675,13 +6676,13 @@
     <row r="32" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="91"/>
       <c r="B32" s="89"/>
-      <c r="C32" s="172" t="s">
+      <c r="C32" s="151" t="s">
         <v>48</v>
       </c>
-      <c r="D32" s="173"/>
-      <c r="E32" s="173"/>
-      <c r="F32" s="173"/>
-      <c r="G32" s="182"/>
+      <c r="D32" s="152"/>
+      <c r="E32" s="152"/>
+      <c r="F32" s="152"/>
+      <c r="G32" s="153"/>
       <c r="H32" s="97"/>
       <c r="I32" s="98"/>
       <c r="J32" s="99"/>
@@ -6690,9 +6691,9 @@
       <c r="M32" s="123"/>
       <c r="N32" s="121"/>
       <c r="O32" s="37"/>
-      <c r="P32" s="200"/>
-      <c r="Q32" s="201"/>
-      <c r="R32" s="201"/>
+      <c r="P32" s="146"/>
+      <c r="Q32" s="147"/>
+      <c r="R32" s="147"/>
       <c r="S32" s="40"/>
       <c r="T32" s="40"/>
       <c r="U32" s="77">
@@ -6803,13 +6804,13 @@
     <row r="34" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="91"/>
       <c r="B34" s="89"/>
-      <c r="C34" s="172" t="s">
+      <c r="C34" s="151" t="s">
         <v>48</v>
       </c>
-      <c r="D34" s="173"/>
-      <c r="E34" s="173"/>
-      <c r="F34" s="173"/>
-      <c r="G34" s="182"/>
+      <c r="D34" s="152"/>
+      <c r="E34" s="152"/>
+      <c r="F34" s="152"/>
+      <c r="G34" s="153"/>
       <c r="H34" s="34"/>
       <c r="I34" s="57"/>
       <c r="J34" s="61"/>
@@ -6867,11 +6868,11 @@
         <v>0</v>
       </c>
       <c r="O35" s="37"/>
-      <c r="P35" s="198"/>
-      <c r="Q35" s="199"/>
-      <c r="R35" s="199"/>
-      <c r="S35" s="199"/>
-      <c r="T35" s="199"/>
+      <c r="P35" s="144"/>
+      <c r="Q35" s="145"/>
+      <c r="R35" s="145"/>
+      <c r="S35" s="145"/>
+      <c r="T35" s="145"/>
       <c r="U35" s="40">
         <f>ROUND(((P35*I35)+(Q35*J35)+(R35*K35)+(S35*L35)+(T35*M35)),3)</f>
         <v>0</v>
@@ -6931,13 +6932,13 @@
     <row r="36" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="91"/>
       <c r="B36" s="89"/>
-      <c r="C36" s="172" t="s">
+      <c r="C36" s="151" t="s">
         <v>48</v>
       </c>
-      <c r="D36" s="173"/>
-      <c r="E36" s="173"/>
-      <c r="F36" s="173"/>
-      <c r="G36" s="182"/>
+      <c r="D36" s="152"/>
+      <c r="E36" s="152"/>
+      <c r="F36" s="152"/>
+      <c r="G36" s="153"/>
       <c r="H36" s="34"/>
       <c r="I36" s="57"/>
       <c r="J36" s="61"/>
@@ -6946,11 +6947,11 @@
       <c r="M36" s="85"/>
       <c r="N36" s="62"/>
       <c r="O36" s="37"/>
-      <c r="P36" s="201"/>
-      <c r="Q36" s="201"/>
-      <c r="R36" s="201"/>
-      <c r="S36" s="201"/>
-      <c r="T36" s="201"/>
+      <c r="P36" s="147"/>
+      <c r="Q36" s="147"/>
+      <c r="R36" s="147"/>
+      <c r="S36" s="147"/>
+      <c r="T36" s="147"/>
       <c r="U36" s="77">
         <f>(I35*P36)+(J35*Q36)+(K35*R36)+(L35*S36)+(M35*T36)</f>
         <v>0</v>
@@ -6995,11 +6996,11 @@
         <v>0</v>
       </c>
       <c r="O37" s="37"/>
-      <c r="P37" s="198"/>
-      <c r="Q37" s="199"/>
-      <c r="R37" s="199"/>
-      <c r="S37" s="199"/>
-      <c r="T37" s="199"/>
+      <c r="P37" s="144"/>
+      <c r="Q37" s="145"/>
+      <c r="R37" s="145"/>
+      <c r="S37" s="145"/>
+      <c r="T37" s="145"/>
       <c r="U37" s="40">
         <f>ROUND(((P37*I37)+(Q37*J37)+(R37*K37)+(S37*L37)+(T37*M37)),3)</f>
         <v>0</v>
@@ -7059,13 +7060,13 @@
     <row r="38" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="91"/>
       <c r="B38" s="89"/>
-      <c r="C38" s="172" t="s">
+      <c r="C38" s="151" t="s">
         <v>48</v>
       </c>
-      <c r="D38" s="173"/>
-      <c r="E38" s="173"/>
-      <c r="F38" s="173"/>
-      <c r="G38" s="182"/>
+      <c r="D38" s="152"/>
+      <c r="E38" s="152"/>
+      <c r="F38" s="152"/>
+      <c r="G38" s="153"/>
       <c r="H38" s="34"/>
       <c r="I38" s="57"/>
       <c r="J38" s="61"/>
@@ -7074,11 +7075,11 @@
       <c r="M38" s="85"/>
       <c r="N38" s="62"/>
       <c r="O38" s="37"/>
-      <c r="P38" s="200"/>
-      <c r="Q38" s="201"/>
-      <c r="R38" s="199"/>
-      <c r="S38" s="201"/>
-      <c r="T38" s="201"/>
+      <c r="P38" s="146"/>
+      <c r="Q38" s="147"/>
+      <c r="R38" s="145"/>
+      <c r="S38" s="147"/>
+      <c r="T38" s="147"/>
       <c r="U38" s="77">
         <f>(I37*P38)+(J37*Q38)+(K37*R38)+(L37*S38)+(M37*T38)</f>
         <v>0</v>
@@ -7123,11 +7124,11 @@
         <v>0</v>
       </c>
       <c r="O39" s="37"/>
-      <c r="P39" s="198"/>
-      <c r="Q39" s="199"/>
-      <c r="R39" s="199"/>
-      <c r="S39" s="199"/>
-      <c r="T39" s="199"/>
+      <c r="P39" s="144"/>
+      <c r="Q39" s="145"/>
+      <c r="R39" s="145"/>
+      <c r="S39" s="145"/>
+      <c r="T39" s="145"/>
       <c r="U39" s="40">
         <f>ROUND(((P39*I39)+(Q39*J39)+(R39*K39)+(S39*L39)+(T39*M39)),3)</f>
         <v>0</v>
@@ -7187,13 +7188,13 @@
     <row r="40" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="91"/>
       <c r="B40" s="89"/>
-      <c r="C40" s="172" t="s">
+      <c r="C40" s="151" t="s">
         <v>48</v>
       </c>
-      <c r="D40" s="173"/>
-      <c r="E40" s="173"/>
-      <c r="F40" s="173"/>
-      <c r="G40" s="182"/>
+      <c r="D40" s="152"/>
+      <c r="E40" s="152"/>
+      <c r="F40" s="152"/>
+      <c r="G40" s="153"/>
       <c r="H40" s="34"/>
       <c r="I40" s="57"/>
       <c r="J40" s="61"/>
@@ -7202,11 +7203,11 @@
       <c r="M40" s="85"/>
       <c r="N40" s="62"/>
       <c r="O40" s="37"/>
-      <c r="P40" s="200"/>
-      <c r="Q40" s="201"/>
-      <c r="R40" s="201"/>
-      <c r="S40" s="201"/>
-      <c r="T40" s="201"/>
+      <c r="P40" s="146"/>
+      <c r="Q40" s="147"/>
+      <c r="R40" s="147"/>
+      <c r="S40" s="147"/>
+      <c r="T40" s="147"/>
       <c r="U40" s="77">
         <f>(I39*P40)+(J39*Q40)+(K39*R40)+(L39*S40)+(M39*T40)</f>
         <v>0</v>
@@ -7251,11 +7252,11 @@
         <v>0</v>
       </c>
       <c r="O41" s="37"/>
-      <c r="P41" s="198"/>
-      <c r="Q41" s="199"/>
-      <c r="R41" s="199"/>
-      <c r="S41" s="199"/>
-      <c r="T41" s="199"/>
+      <c r="P41" s="144"/>
+      <c r="Q41" s="145"/>
+      <c r="R41" s="145"/>
+      <c r="S41" s="145"/>
+      <c r="T41" s="145"/>
       <c r="U41" s="40">
         <f>ROUND(((P41*I41)+(Q41*J41)+(R41*K41)+(S41*L41)+(T41*M41)),3)</f>
         <v>0</v>
@@ -7315,13 +7316,13 @@
     <row r="42" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="91"/>
       <c r="B42" s="89"/>
-      <c r="C42" s="172" t="s">
+      <c r="C42" s="151" t="s">
         <v>48</v>
       </c>
-      <c r="D42" s="173"/>
-      <c r="E42" s="173"/>
-      <c r="F42" s="173"/>
-      <c r="G42" s="182"/>
+      <c r="D42" s="152"/>
+      <c r="E42" s="152"/>
+      <c r="F42" s="152"/>
+      <c r="G42" s="153"/>
       <c r="H42" s="34"/>
       <c r="I42" s="57"/>
       <c r="J42" s="61"/>
@@ -7330,11 +7331,11 @@
       <c r="M42" s="85"/>
       <c r="N42" s="62"/>
       <c r="O42" s="37"/>
-      <c r="P42" s="200"/>
-      <c r="Q42" s="201"/>
-      <c r="R42" s="201"/>
-      <c r="S42" s="201"/>
-      <c r="T42" s="201"/>
+      <c r="P42" s="146"/>
+      <c r="Q42" s="147"/>
+      <c r="R42" s="147"/>
+      <c r="S42" s="147"/>
+      <c r="T42" s="147"/>
       <c r="U42" s="77">
         <f>(I41*P42)+(J41*Q42)+(K41*R42)+(L41*S42)+(M41*T42)</f>
         <v>0</v>
@@ -7379,11 +7380,11 @@
         <v>0</v>
       </c>
       <c r="O43" s="37"/>
-      <c r="P43" s="198"/>
-      <c r="Q43" s="199"/>
-      <c r="R43" s="199"/>
-      <c r="S43" s="199"/>
-      <c r="T43" s="199"/>
+      <c r="P43" s="144"/>
+      <c r="Q43" s="145"/>
+      <c r="R43" s="145"/>
+      <c r="S43" s="145"/>
+      <c r="T43" s="145"/>
       <c r="U43" s="40">
         <f>ROUND(((P43*I43)+(Q43*J43)+(R43*K43)+(S43*L43)+(T43*M43)),3)</f>
         <v>0</v>
@@ -7443,13 +7444,13 @@
     <row r="44" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="91"/>
       <c r="B44" s="89"/>
-      <c r="C44" s="172" t="s">
+      <c r="C44" s="151" t="s">
         <v>48</v>
       </c>
-      <c r="D44" s="173"/>
-      <c r="E44" s="173"/>
-      <c r="F44" s="173"/>
-      <c r="G44" s="182"/>
+      <c r="D44" s="152"/>
+      <c r="E44" s="152"/>
+      <c r="F44" s="152"/>
+      <c r="G44" s="153"/>
       <c r="H44" s="34"/>
       <c r="I44" s="57"/>
       <c r="J44" s="61"/>
@@ -7458,11 +7459,11 @@
       <c r="M44" s="85"/>
       <c r="N44" s="62"/>
       <c r="O44" s="37"/>
-      <c r="P44" s="200"/>
-      <c r="Q44" s="199"/>
-      <c r="R44" s="199"/>
-      <c r="S44" s="201"/>
-      <c r="T44" s="201"/>
+      <c r="P44" s="146"/>
+      <c r="Q44" s="145"/>
+      <c r="R44" s="145"/>
+      <c r="S44" s="147"/>
+      <c r="T44" s="147"/>
       <c r="U44" s="77">
         <f>(I43*P44)+(J43*Q44)+(K43*R44)+(L43*S44)+(M43*T44)</f>
         <v>0</v>
@@ -7507,11 +7508,11 @@
         <v>0</v>
       </c>
       <c r="O45" s="37"/>
-      <c r="P45" s="198"/>
-      <c r="Q45" s="199"/>
-      <c r="R45" s="199"/>
-      <c r="S45" s="199"/>
-      <c r="T45" s="199"/>
+      <c r="P45" s="144"/>
+      <c r="Q45" s="145"/>
+      <c r="R45" s="145"/>
+      <c r="S45" s="145"/>
+      <c r="T45" s="145"/>
       <c r="U45" s="40">
         <f>ROUND(((P45*I45)+(Q45*J45)+(R45*K45)+(S45*L45)+(T45*M45)),3)</f>
         <v>0</v>
@@ -7571,13 +7572,13 @@
     <row r="46" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="91"/>
       <c r="B46" s="89"/>
-      <c r="C46" s="172" t="s">
+      <c r="C46" s="151" t="s">
         <v>48</v>
       </c>
-      <c r="D46" s="173"/>
-      <c r="E46" s="173"/>
-      <c r="F46" s="173"/>
-      <c r="G46" s="182"/>
+      <c r="D46" s="152"/>
+      <c r="E46" s="152"/>
+      <c r="F46" s="152"/>
+      <c r="G46" s="153"/>
       <c r="H46" s="34"/>
       <c r="I46" s="57"/>
       <c r="J46" s="61"/>
@@ -7586,11 +7587,11 @@
       <c r="M46" s="85"/>
       <c r="N46" s="62"/>
       <c r="O46" s="37"/>
-      <c r="P46" s="200"/>
-      <c r="Q46" s="201"/>
-      <c r="R46" s="201"/>
-      <c r="S46" s="201"/>
-      <c r="T46" s="201"/>
+      <c r="P46" s="146"/>
+      <c r="Q46" s="147"/>
+      <c r="R46" s="147"/>
+      <c r="S46" s="147"/>
+      <c r="T46" s="147"/>
       <c r="U46" s="77">
         <f>(I45*P46)+(J45*Q46)+(K45*R46)+(L45*S46)+(M45*T46)</f>
         <v>0</v>
@@ -7635,11 +7636,11 @@
         <v>0</v>
       </c>
       <c r="O47" s="37"/>
-      <c r="P47" s="198"/>
-      <c r="Q47" s="199"/>
-      <c r="R47" s="199"/>
-      <c r="S47" s="199"/>
-      <c r="T47" s="199"/>
+      <c r="P47" s="144"/>
+      <c r="Q47" s="145"/>
+      <c r="R47" s="145"/>
+      <c r="S47" s="145"/>
+      <c r="T47" s="145"/>
       <c r="U47" s="40">
         <f>ROUND(((P47*I47)+(Q47*J47)+(R47*K47)+(S47*L47)+(T47*M47)),3)</f>
         <v>0</v>
@@ -7699,13 +7700,13 @@
     <row r="48" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="91"/>
       <c r="B48" s="89"/>
-      <c r="C48" s="172" t="s">
+      <c r="C48" s="151" t="s">
         <v>48</v>
       </c>
-      <c r="D48" s="173"/>
-      <c r="E48" s="173"/>
-      <c r="F48" s="173"/>
-      <c r="G48" s="182"/>
+      <c r="D48" s="152"/>
+      <c r="E48" s="152"/>
+      <c r="F48" s="152"/>
+      <c r="G48" s="153"/>
       <c r="H48" s="34"/>
       <c r="I48" s="57"/>
       <c r="J48" s="61"/>
@@ -7714,11 +7715,11 @@
       <c r="M48" s="85"/>
       <c r="N48" s="62"/>
       <c r="O48" s="37"/>
-      <c r="P48" s="200"/>
-      <c r="Q48" s="199"/>
-      <c r="R48" s="199"/>
-      <c r="S48" s="201"/>
-      <c r="T48" s="201"/>
+      <c r="P48" s="146"/>
+      <c r="Q48" s="145"/>
+      <c r="R48" s="145"/>
+      <c r="S48" s="147"/>
+      <c r="T48" s="147"/>
       <c r="U48" s="77">
         <f>(I47*P48)+(J47*Q48)+(K47*R48)+(L47*S48)+(M47*T48)</f>
         <v>0</v>
@@ -7763,11 +7764,11 @@
         <v>0</v>
       </c>
       <c r="O49" s="37"/>
-      <c r="P49" s="198"/>
-      <c r="Q49" s="199"/>
-      <c r="R49" s="199"/>
-      <c r="S49" s="199"/>
-      <c r="T49" s="199"/>
+      <c r="P49" s="144"/>
+      <c r="Q49" s="145"/>
+      <c r="R49" s="145"/>
+      <c r="S49" s="145"/>
+      <c r="T49" s="145"/>
       <c r="U49" s="40">
         <f>ROUND(((P49*I49)+(Q49*J49)+(R49*K49)+(S49*L49)+(T49*M49)),3)</f>
         <v>0</v>
@@ -7827,13 +7828,13 @@
     <row r="50" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="91"/>
       <c r="B50" s="89"/>
-      <c r="C50" s="172" t="s">
+      <c r="C50" s="151" t="s">
         <v>48</v>
       </c>
-      <c r="D50" s="173"/>
-      <c r="E50" s="173"/>
-      <c r="F50" s="173"/>
-      <c r="G50" s="182"/>
+      <c r="D50" s="152"/>
+      <c r="E50" s="152"/>
+      <c r="F50" s="152"/>
+      <c r="G50" s="153"/>
       <c r="H50" s="34"/>
       <c r="I50" s="57"/>
       <c r="J50" s="61"/>
@@ -7842,11 +7843,11 @@
       <c r="M50" s="85"/>
       <c r="N50" s="62"/>
       <c r="O50" s="37"/>
-      <c r="P50" s="200"/>
-      <c r="Q50" s="201"/>
-      <c r="R50" s="201"/>
-      <c r="S50" s="201"/>
-      <c r="T50" s="201"/>
+      <c r="P50" s="146"/>
+      <c r="Q50" s="147"/>
+      <c r="R50" s="147"/>
+      <c r="S50" s="147"/>
+      <c r="T50" s="147"/>
       <c r="U50" s="77">
         <f>(I49*P50)+(J49*Q50)+(K49*R50)+(L49*S50)+(M49*T50)</f>
         <v>0</v>
@@ -7893,11 +7894,11 @@
         <v>0</v>
       </c>
       <c r="O51" s="37"/>
-      <c r="P51" s="198"/>
-      <c r="Q51" s="199"/>
-      <c r="R51" s="199"/>
-      <c r="S51" s="199"/>
-      <c r="T51" s="199"/>
+      <c r="P51" s="144"/>
+      <c r="Q51" s="145"/>
+      <c r="R51" s="145"/>
+      <c r="S51" s="145"/>
+      <c r="T51" s="145"/>
       <c r="U51" s="40">
         <f>ROUND(((P51*I51)+(Q51*J51)+(R51*K51)+(S51*L51)+(T51*M51)),3)</f>
         <v>0</v>
@@ -7957,13 +7958,13 @@
     <row r="52" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="91"/>
       <c r="B52" s="89"/>
-      <c r="C52" s="172" t="s">
+      <c r="C52" s="151" t="s">
         <v>48</v>
       </c>
-      <c r="D52" s="173"/>
-      <c r="E52" s="173"/>
-      <c r="F52" s="173"/>
-      <c r="G52" s="182"/>
+      <c r="D52" s="152"/>
+      <c r="E52" s="152"/>
+      <c r="F52" s="152"/>
+      <c r="G52" s="153"/>
       <c r="H52" s="34"/>
       <c r="I52" s="57"/>
       <c r="J52" s="61"/>
@@ -7972,11 +7973,11 @@
       <c r="M52" s="85"/>
       <c r="N52" s="62"/>
       <c r="O52" s="37"/>
-      <c r="P52" s="200"/>
-      <c r="Q52" s="199"/>
-      <c r="R52" s="201"/>
-      <c r="S52" s="201"/>
-      <c r="T52" s="201"/>
+      <c r="P52" s="146"/>
+      <c r="Q52" s="145"/>
+      <c r="R52" s="147"/>
+      <c r="S52" s="147"/>
+      <c r="T52" s="147"/>
       <c r="U52" s="77">
         <f>(I51*P52)+(J51*Q52)+(K51*R52)+(L51*S52)+(M51*T52)</f>
         <v>0</v>
@@ -8023,11 +8024,11 @@
         <v>0</v>
       </c>
       <c r="O53" s="37"/>
-      <c r="P53" s="198"/>
-      <c r="Q53" s="199"/>
-      <c r="R53" s="199"/>
-      <c r="S53" s="199"/>
-      <c r="T53" s="199"/>
+      <c r="P53" s="144"/>
+      <c r="Q53" s="145"/>
+      <c r="R53" s="145"/>
+      <c r="S53" s="145"/>
+      <c r="T53" s="145"/>
       <c r="U53" s="40">
         <f>ROUND(((P53*I53)+(Q53*J53)+(R53*K53)+(S53*L53)+(T53*M53)),3)</f>
         <v>0</v>
@@ -8087,13 +8088,13 @@
     <row r="54" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="91"/>
       <c r="B54" s="89"/>
-      <c r="C54" s="172" t="s">
+      <c r="C54" s="151" t="s">
         <v>48</v>
       </c>
-      <c r="D54" s="173"/>
-      <c r="E54" s="173"/>
-      <c r="F54" s="173"/>
-      <c r="G54" s="182"/>
+      <c r="D54" s="152"/>
+      <c r="E54" s="152"/>
+      <c r="F54" s="152"/>
+      <c r="G54" s="153"/>
       <c r="H54" s="34"/>
       <c r="I54" s="57"/>
       <c r="J54" s="61"/>
@@ -8102,11 +8103,11 @@
       <c r="M54" s="85"/>
       <c r="N54" s="62"/>
       <c r="O54" s="37"/>
-      <c r="P54" s="200"/>
-      <c r="Q54" s="200"/>
-      <c r="R54" s="201"/>
-      <c r="S54" s="201"/>
-      <c r="T54" s="201"/>
+      <c r="P54" s="146"/>
+      <c r="Q54" s="146"/>
+      <c r="R54" s="147"/>
+      <c r="S54" s="147"/>
+      <c r="T54" s="147"/>
       <c r="U54" s="77">
         <f>(I53*P54)+(J53*Q54)+(K53*R54)+(L53*S54)+(M53*T54)</f>
         <v>0</v>
@@ -8153,11 +8154,11 @@
         <v>0</v>
       </c>
       <c r="O55" s="37"/>
-      <c r="P55" s="198"/>
-      <c r="Q55" s="199"/>
-      <c r="R55" s="199"/>
-      <c r="S55" s="199"/>
-      <c r="T55" s="199"/>
+      <c r="P55" s="144"/>
+      <c r="Q55" s="145"/>
+      <c r="R55" s="145"/>
+      <c r="S55" s="145"/>
+      <c r="T55" s="145"/>
       <c r="U55" s="40">
         <f>ROUND(((P55*I55)+(Q55*J55)+(R55*K55)+(S55*L55)+(T55*M55)),3)</f>
         <v>0</v>
@@ -8217,13 +8218,13 @@
     <row r="56" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="91"/>
       <c r="B56" s="89"/>
-      <c r="C56" s="172" t="s">
+      <c r="C56" s="151" t="s">
         <v>48</v>
       </c>
-      <c r="D56" s="173"/>
-      <c r="E56" s="173"/>
-      <c r="F56" s="173"/>
-      <c r="G56" s="182"/>
+      <c r="D56" s="152"/>
+      <c r="E56" s="152"/>
+      <c r="F56" s="152"/>
+      <c r="G56" s="153"/>
       <c r="H56" s="34"/>
       <c r="I56" s="57"/>
       <c r="J56" s="61"/>
@@ -8232,11 +8233,11 @@
       <c r="M56" s="85"/>
       <c r="N56" s="62"/>
       <c r="O56" s="37"/>
-      <c r="P56" s="200"/>
-      <c r="Q56" s="200"/>
-      <c r="R56" s="200"/>
-      <c r="S56" s="201"/>
-      <c r="T56" s="201"/>
+      <c r="P56" s="146"/>
+      <c r="Q56" s="146"/>
+      <c r="R56" s="146"/>
+      <c r="S56" s="147"/>
+      <c r="T56" s="147"/>
       <c r="U56" s="77">
         <f>(I55*P56)+(J55*Q56)+(K55*R56)+(L55*S56)+(M55*T56)</f>
         <v>0</v>
@@ -8281,11 +8282,11 @@
         <v>0</v>
       </c>
       <c r="O57" s="37"/>
-      <c r="P57" s="198"/>
-      <c r="Q57" s="198"/>
-      <c r="R57" s="199"/>
-      <c r="S57" s="199"/>
-      <c r="T57" s="199"/>
+      <c r="P57" s="144"/>
+      <c r="Q57" s="144"/>
+      <c r="R57" s="145"/>
+      <c r="S57" s="145"/>
+      <c r="T57" s="145"/>
       <c r="U57" s="40">
         <f>ROUND(((P57*I57)+(Q57*J57)+(R57*K57)+(S57*L57)+(T57*M57)),3)</f>
         <v>0</v>
@@ -8339,13 +8340,13 @@
     <row r="58" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="91"/>
       <c r="B58" s="89"/>
-      <c r="C58" s="172" t="s">
+      <c r="C58" s="151" t="s">
         <v>48</v>
       </c>
-      <c r="D58" s="173"/>
-      <c r="E58" s="173"/>
-      <c r="F58" s="173"/>
-      <c r="G58" s="182"/>
+      <c r="D58" s="152"/>
+      <c r="E58" s="152"/>
+      <c r="F58" s="152"/>
+      <c r="G58" s="153"/>
       <c r="H58" s="97"/>
       <c r="I58" s="98"/>
       <c r="J58" s="99"/>
@@ -8354,11 +8355,11 @@
       <c r="M58" s="123"/>
       <c r="N58" s="121"/>
       <c r="O58" s="37"/>
-      <c r="P58" s="201"/>
-      <c r="Q58" s="201"/>
-      <c r="R58" s="201"/>
-      <c r="S58" s="201"/>
-      <c r="T58" s="201"/>
+      <c r="P58" s="147"/>
+      <c r="Q58" s="147"/>
+      <c r="R58" s="147"/>
+      <c r="S58" s="147"/>
+      <c r="T58" s="147"/>
       <c r="U58" s="77">
         <f>(I57*P58)+(J57*Q58)+(K57*R58)+(L57*S58)+(M57*T58)</f>
         <v>0</v>
@@ -8403,11 +8404,11 @@
         <v>0</v>
       </c>
       <c r="O59" s="37"/>
-      <c r="P59" s="198"/>
-      <c r="Q59" s="199"/>
-      <c r="R59" s="199"/>
-      <c r="S59" s="199"/>
-      <c r="T59" s="199"/>
+      <c r="P59" s="144"/>
+      <c r="Q59" s="145"/>
+      <c r="R59" s="145"/>
+      <c r="S59" s="145"/>
+      <c r="T59" s="145"/>
       <c r="U59" s="40">
         <f>ROUND(((P59*I59)+(Q59*J59)+(R59*K59)+(S59*L59)+(T59*M59)),3)</f>
         <v>0</v>
@@ -8467,13 +8468,13 @@
     <row r="60" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="91"/>
       <c r="B60" s="89"/>
-      <c r="C60" s="172" t="s">
+      <c r="C60" s="151" t="s">
         <v>48</v>
       </c>
-      <c r="D60" s="173"/>
-      <c r="E60" s="173"/>
-      <c r="F60" s="173"/>
-      <c r="G60" s="182"/>
+      <c r="D60" s="152"/>
+      <c r="E60" s="152"/>
+      <c r="F60" s="152"/>
+      <c r="G60" s="153"/>
       <c r="H60" s="34"/>
       <c r="I60" s="57"/>
       <c r="J60" s="61"/>
@@ -8482,11 +8483,11 @@
       <c r="M60" s="85"/>
       <c r="N60" s="62"/>
       <c r="O60" s="37"/>
-      <c r="P60" s="200"/>
-      <c r="Q60" s="201"/>
-      <c r="R60" s="201"/>
-      <c r="S60" s="201"/>
-      <c r="T60" s="201"/>
+      <c r="P60" s="146"/>
+      <c r="Q60" s="147"/>
+      <c r="R60" s="147"/>
+      <c r="S60" s="147"/>
+      <c r="T60" s="147"/>
       <c r="U60" s="77">
         <f>(I59*P60)+(J59*Q60)+(K59*R60)+(L59*S60)+(M59*T60)</f>
         <v>0</v>
@@ -8531,11 +8532,11 @@
         <v>0</v>
       </c>
       <c r="O61" s="37"/>
-      <c r="P61" s="198"/>
-      <c r="Q61" s="199"/>
-      <c r="R61" s="199"/>
-      <c r="S61" s="199"/>
-      <c r="T61" s="199"/>
+      <c r="P61" s="144"/>
+      <c r="Q61" s="145"/>
+      <c r="R61" s="145"/>
+      <c r="S61" s="145"/>
+      <c r="T61" s="145"/>
       <c r="U61" s="40">
         <f>ROUND(((P61*I61)+(Q61*J61)+(R61*K61)+(S61*L61)+(T61*M61)),3)</f>
         <v>0</v>
@@ -8595,13 +8596,13 @@
     <row r="62" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="91"/>
       <c r="B62" s="89"/>
-      <c r="C62" s="172" t="s">
+      <c r="C62" s="151" t="s">
         <v>48</v>
       </c>
-      <c r="D62" s="173"/>
-      <c r="E62" s="173"/>
-      <c r="F62" s="173"/>
-      <c r="G62" s="182"/>
+      <c r="D62" s="152"/>
+      <c r="E62" s="152"/>
+      <c r="F62" s="152"/>
+      <c r="G62" s="153"/>
       <c r="H62" s="34"/>
       <c r="I62" s="57"/>
       <c r="J62" s="61"/>
@@ -8610,11 +8611,11 @@
       <c r="M62" s="85"/>
       <c r="N62" s="62"/>
       <c r="O62" s="37"/>
-      <c r="P62" s="201"/>
-      <c r="Q62" s="201"/>
-      <c r="R62" s="201"/>
-      <c r="S62" s="201"/>
-      <c r="T62" s="201"/>
+      <c r="P62" s="147"/>
+      <c r="Q62" s="147"/>
+      <c r="R62" s="147"/>
+      <c r="S62" s="147"/>
+      <c r="T62" s="147"/>
       <c r="U62" s="77">
         <f>(I61*P62)+(J61*Q62)+(K61*R62)+(L61*S62)+(M61*T62)</f>
         <v>0</v>
@@ -8659,11 +8660,11 @@
         <v>0</v>
       </c>
       <c r="O63" s="37"/>
-      <c r="P63" s="198"/>
-      <c r="Q63" s="199"/>
-      <c r="R63" s="199"/>
-      <c r="S63" s="199"/>
-      <c r="T63" s="199"/>
+      <c r="P63" s="144"/>
+      <c r="Q63" s="145"/>
+      <c r="R63" s="145"/>
+      <c r="S63" s="145"/>
+      <c r="T63" s="145"/>
       <c r="U63" s="40">
         <f>ROUND(((P63*I63)+(Q63*J63)+(R63*K63)+(S63*L63)+(T63*M63)),3)</f>
         <v>0</v>
@@ -8723,13 +8724,13 @@
     <row r="64" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="91"/>
       <c r="B64" s="89"/>
-      <c r="C64" s="172" t="s">
+      <c r="C64" s="151" t="s">
         <v>48</v>
       </c>
-      <c r="D64" s="173"/>
-      <c r="E64" s="173"/>
-      <c r="F64" s="173"/>
-      <c r="G64" s="182"/>
+      <c r="D64" s="152"/>
+      <c r="E64" s="152"/>
+      <c r="F64" s="152"/>
+      <c r="G64" s="153"/>
       <c r="H64" s="34"/>
       <c r="I64" s="57"/>
       <c r="J64" s="61"/>
@@ -8738,11 +8739,11 @@
       <c r="M64" s="85"/>
       <c r="N64" s="62"/>
       <c r="O64" s="37"/>
-      <c r="P64" s="201"/>
-      <c r="Q64" s="201"/>
-      <c r="R64" s="201"/>
-      <c r="S64" s="201"/>
-      <c r="T64" s="201"/>
+      <c r="P64" s="147"/>
+      <c r="Q64" s="147"/>
+      <c r="R64" s="147"/>
+      <c r="S64" s="147"/>
+      <c r="T64" s="147"/>
       <c r="U64" s="77">
         <f>(I63*P64)+(J63*Q64)+(K63*R64)+(L63*S64)+(M63*T64)</f>
         <v>0</v>
@@ -8787,11 +8788,11 @@
         <v>0</v>
       </c>
       <c r="O65" s="37"/>
-      <c r="P65" s="198"/>
-      <c r="Q65" s="199"/>
-      <c r="R65" s="199"/>
-      <c r="S65" s="199"/>
-      <c r="T65" s="199"/>
+      <c r="P65" s="144"/>
+      <c r="Q65" s="145"/>
+      <c r="R65" s="145"/>
+      <c r="S65" s="145"/>
+      <c r="T65" s="145"/>
       <c r="U65" s="40">
         <f>ROUND(((P65*I65)+(Q65*J65)+(R65*K65)+(S65*L65)+(T65*M65)),3)</f>
         <v>0</v>
@@ -8851,13 +8852,13 @@
     <row r="66" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="91"/>
       <c r="B66" s="89"/>
-      <c r="C66" s="172" t="s">
+      <c r="C66" s="151" t="s">
         <v>48</v>
       </c>
-      <c r="D66" s="173"/>
-      <c r="E66" s="173"/>
-      <c r="F66" s="173"/>
-      <c r="G66" s="182"/>
+      <c r="D66" s="152"/>
+      <c r="E66" s="152"/>
+      <c r="F66" s="152"/>
+      <c r="G66" s="153"/>
       <c r="H66" s="34"/>
       <c r="I66" s="57"/>
       <c r="J66" s="61"/>
@@ -8866,11 +8867,11 @@
       <c r="M66" s="85"/>
       <c r="N66" s="62"/>
       <c r="O66" s="37"/>
-      <c r="P66" s="200"/>
-      <c r="Q66" s="201"/>
-      <c r="R66" s="201"/>
-      <c r="S66" s="201"/>
-      <c r="T66" s="201"/>
+      <c r="P66" s="146"/>
+      <c r="Q66" s="147"/>
+      <c r="R66" s="147"/>
+      <c r="S66" s="147"/>
+      <c r="T66" s="147"/>
       <c r="U66" s="77">
         <f>(I65*P66)+(J65*Q66)+(K65*R66)+(L65*S66)+(M65*T66)</f>
         <v>0</v>
@@ -8915,11 +8916,11 @@
         <v>0</v>
       </c>
       <c r="O67" s="37"/>
-      <c r="P67" s="198"/>
-      <c r="Q67" s="199"/>
-      <c r="R67" s="199"/>
-      <c r="S67" s="199"/>
-      <c r="T67" s="199"/>
+      <c r="P67" s="144"/>
+      <c r="Q67" s="145"/>
+      <c r="R67" s="145"/>
+      <c r="S67" s="145"/>
+      <c r="T67" s="145"/>
       <c r="U67" s="40">
         <f>ROUND(((P67*I67)+(Q67*J67)+(R67*K67)+(S67*L67)+(T67*M67)),3)</f>
         <v>0</v>
@@ -8979,13 +8980,13 @@
     <row r="68" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="91"/>
       <c r="B68" s="89"/>
-      <c r="C68" s="172" t="s">
+      <c r="C68" s="151" t="s">
         <v>48</v>
       </c>
-      <c r="D68" s="173"/>
-      <c r="E68" s="173"/>
-      <c r="F68" s="173"/>
-      <c r="G68" s="182"/>
+      <c r="D68" s="152"/>
+      <c r="E68" s="152"/>
+      <c r="F68" s="152"/>
+      <c r="G68" s="153"/>
       <c r="H68" s="34"/>
       <c r="I68" s="57"/>
       <c r="J68" s="61"/>
@@ -8994,11 +8995,11 @@
       <c r="M68" s="85"/>
       <c r="N68" s="62"/>
       <c r="O68" s="37"/>
-      <c r="P68" s="200"/>
-      <c r="Q68" s="199"/>
-      <c r="R68" s="199"/>
-      <c r="S68" s="201"/>
-      <c r="T68" s="201"/>
+      <c r="P68" s="146"/>
+      <c r="Q68" s="145"/>
+      <c r="R68" s="145"/>
+      <c r="S68" s="147"/>
+      <c r="T68" s="147"/>
       <c r="U68" s="77">
         <f>(I67*P68)+(J67*Q68)+(K67*R68)+(L67*S68)+(M67*T68)</f>
         <v>0</v>
@@ -9043,11 +9044,11 @@
         <v>0</v>
       </c>
       <c r="O69" s="37"/>
-      <c r="P69" s="198"/>
-      <c r="Q69" s="199"/>
-      <c r="R69" s="199"/>
-      <c r="S69" s="199"/>
-      <c r="T69" s="199"/>
+      <c r="P69" s="144"/>
+      <c r="Q69" s="145"/>
+      <c r="R69" s="145"/>
+      <c r="S69" s="145"/>
+      <c r="T69" s="145"/>
       <c r="U69" s="40">
         <f>ROUND(((P69*I69)+(Q69*J69)+(R69*K69)+(S69*L69)+(T69*M69)),3)</f>
         <v>0</v>
@@ -9107,13 +9108,13 @@
     <row r="70" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="91"/>
       <c r="B70" s="89"/>
-      <c r="C70" s="174" t="s">
+      <c r="C70" s="148" t="s">
         <v>48</v>
       </c>
-      <c r="D70" s="175"/>
-      <c r="E70" s="175"/>
-      <c r="F70" s="175"/>
-      <c r="G70" s="176"/>
+      <c r="D70" s="149"/>
+      <c r="E70" s="149"/>
+      <c r="F70" s="149"/>
+      <c r="G70" s="150"/>
       <c r="H70" s="34"/>
       <c r="I70" s="57"/>
       <c r="J70" s="61"/>
@@ -9122,11 +9123,11 @@
       <c r="M70" s="85"/>
       <c r="N70" s="62"/>
       <c r="O70" s="37"/>
-      <c r="P70" s="200"/>
-      <c r="Q70" s="200"/>
-      <c r="R70" s="200"/>
-      <c r="S70" s="201"/>
-      <c r="T70" s="201"/>
+      <c r="P70" s="146"/>
+      <c r="Q70" s="146"/>
+      <c r="R70" s="146"/>
+      <c r="S70" s="147"/>
+      <c r="T70" s="147"/>
       <c r="U70" s="77">
         <f>(I69*P70)+(J69*Q70)+(K69*R70)+(L69*S70)+(M69*T70)</f>
         <v>0</v>
@@ -9171,11 +9172,11 @@
         <v>0</v>
       </c>
       <c r="O71" s="37"/>
-      <c r="P71" s="198"/>
-      <c r="Q71" s="199"/>
-      <c r="R71" s="199"/>
-      <c r="S71" s="199"/>
-      <c r="T71" s="199"/>
+      <c r="P71" s="144"/>
+      <c r="Q71" s="145"/>
+      <c r="R71" s="145"/>
+      <c r="S71" s="145"/>
+      <c r="T71" s="145"/>
       <c r="U71" s="40">
         <f>ROUND(((P71*I71)+(Q71*J71)+(R71*K71)+(S71*L71)+(T71*M71)),2)</f>
         <v>0</v>
@@ -9229,13 +9230,13 @@
     <row r="72" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="91"/>
       <c r="B72" s="89"/>
-      <c r="C72" s="174" t="s">
+      <c r="C72" s="148" t="s">
         <v>48</v>
       </c>
-      <c r="D72" s="175"/>
-      <c r="E72" s="175"/>
-      <c r="F72" s="175"/>
-      <c r="G72" s="176"/>
+      <c r="D72" s="149"/>
+      <c r="E72" s="149"/>
+      <c r="F72" s="149"/>
+      <c r="G72" s="150"/>
       <c r="H72" s="34"/>
       <c r="I72" s="57"/>
       <c r="J72" s="61"/>
@@ -9244,11 +9245,11 @@
       <c r="M72" s="85"/>
       <c r="N72" s="62"/>
       <c r="O72" s="37"/>
-      <c r="P72" s="201"/>
-      <c r="Q72" s="201"/>
-      <c r="R72" s="201"/>
-      <c r="S72" s="201"/>
-      <c r="T72" s="201"/>
+      <c r="P72" s="147"/>
+      <c r="Q72" s="147"/>
+      <c r="R72" s="147"/>
+      <c r="S72" s="147"/>
+      <c r="T72" s="147"/>
       <c r="U72" s="77">
         <f>(I71*P72)+(J71*Q72)+(K71*R72)+(L71*S72)+(M71*T72)</f>
         <v>0</v>
@@ -9293,11 +9294,11 @@
         <v>0</v>
       </c>
       <c r="O73" s="37"/>
-      <c r="P73" s="198"/>
-      <c r="Q73" s="199"/>
-      <c r="R73" s="199"/>
-      <c r="S73" s="199"/>
-      <c r="T73" s="199"/>
+      <c r="P73" s="144"/>
+      <c r="Q73" s="145"/>
+      <c r="R73" s="145"/>
+      <c r="S73" s="145"/>
+      <c r="T73" s="145"/>
       <c r="U73" s="40">
         <f>ROUND(((P73*I73)+(Q73*J73)+(R73*K73)+(S73*L73)+(T73*M73)),3)</f>
         <v>0</v>
@@ -9357,13 +9358,13 @@
     <row r="74" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="91"/>
       <c r="B74" s="89"/>
-      <c r="C74" s="174" t="s">
+      <c r="C74" s="148" t="s">
         <v>48</v>
       </c>
-      <c r="D74" s="175"/>
-      <c r="E74" s="175"/>
-      <c r="F74" s="175"/>
-      <c r="G74" s="176"/>
+      <c r="D74" s="149"/>
+      <c r="E74" s="149"/>
+      <c r="F74" s="149"/>
+      <c r="G74" s="150"/>
       <c r="H74" s="34"/>
       <c r="I74" s="57"/>
       <c r="J74" s="61"/>
@@ -9372,11 +9373,11 @@
       <c r="M74" s="85"/>
       <c r="N74" s="62"/>
       <c r="O74" s="37"/>
-      <c r="P74" s="200"/>
-      <c r="Q74" s="201"/>
-      <c r="R74" s="201"/>
-      <c r="S74" s="201"/>
-      <c r="T74" s="201"/>
+      <c r="P74" s="146"/>
+      <c r="Q74" s="147"/>
+      <c r="R74" s="147"/>
+      <c r="S74" s="147"/>
+      <c r="T74" s="147"/>
       <c r="U74" s="77">
         <f>(I73*P74)+(J73*Q74)+(K73*R74)+(L73*S74)+(M73*T74)</f>
         <v>0</v>
@@ -9421,11 +9422,11 @@
         <v>0</v>
       </c>
       <c r="O75" s="37"/>
-      <c r="P75" s="198"/>
-      <c r="Q75" s="199"/>
-      <c r="R75" s="199"/>
-      <c r="S75" s="199"/>
-      <c r="T75" s="199"/>
+      <c r="P75" s="144"/>
+      <c r="Q75" s="145"/>
+      <c r="R75" s="145"/>
+      <c r="S75" s="145"/>
+      <c r="T75" s="145"/>
       <c r="U75" s="40">
         <f>ROUND(((P75*I75)+(Q75*J75)+(R75*K75)+(S75*L75)+(T75*M75)),3)</f>
         <v>0</v>
@@ -9485,13 +9486,13 @@
     <row r="76" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="91"/>
       <c r="B76" s="89"/>
-      <c r="C76" s="174" t="s">
+      <c r="C76" s="148" t="s">
         <v>48</v>
       </c>
-      <c r="D76" s="175"/>
-      <c r="E76" s="175"/>
-      <c r="F76" s="175"/>
-      <c r="G76" s="176"/>
+      <c r="D76" s="149"/>
+      <c r="E76" s="149"/>
+      <c r="F76" s="149"/>
+      <c r="G76" s="150"/>
       <c r="H76" s="34"/>
       <c r="I76" s="57"/>
       <c r="J76" s="61"/>
@@ -9500,11 +9501,11 @@
       <c r="M76" s="85"/>
       <c r="N76" s="62"/>
       <c r="O76" s="37"/>
-      <c r="P76" s="200"/>
-      <c r="Q76" s="201"/>
-      <c r="R76" s="201"/>
-      <c r="S76" s="201"/>
-      <c r="T76" s="201"/>
+      <c r="P76" s="146"/>
+      <c r="Q76" s="147"/>
+      <c r="R76" s="147"/>
+      <c r="S76" s="147"/>
+      <c r="T76" s="147"/>
       <c r="U76" s="77">
         <f>(I75*P76)+(J75*Q76)+(K75*R76)+(L75*S76)+(M75*T76)</f>
         <v>0</v>
@@ -9549,11 +9550,11 @@
         <v>0</v>
       </c>
       <c r="O77" s="37"/>
-      <c r="P77" s="199"/>
-      <c r="Q77" s="199"/>
-      <c r="R77" s="199"/>
-      <c r="S77" s="199"/>
-      <c r="T77" s="199"/>
+      <c r="P77" s="145"/>
+      <c r="Q77" s="145"/>
+      <c r="R77" s="145"/>
+      <c r="S77" s="145"/>
+      <c r="T77" s="145"/>
       <c r="U77" s="40">
         <f>ROUND(((P77*I77)+(Q77*J77)+(R77*K77)+(S77*L77)+(T77*M77)),3)</f>
         <v>0</v>
@@ -9613,13 +9614,13 @@
     <row r="78" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="91"/>
       <c r="B78" s="89"/>
-      <c r="C78" s="174" t="s">
+      <c r="C78" s="148" t="s">
         <v>48</v>
       </c>
-      <c r="D78" s="175"/>
-      <c r="E78" s="175"/>
-      <c r="F78" s="175"/>
-      <c r="G78" s="176"/>
+      <c r="D78" s="149"/>
+      <c r="E78" s="149"/>
+      <c r="F78" s="149"/>
+      <c r="G78" s="150"/>
       <c r="H78" s="34"/>
       <c r="I78" s="57"/>
       <c r="J78" s="61"/>
@@ -9628,11 +9629,11 @@
       <c r="M78" s="85"/>
       <c r="N78" s="62"/>
       <c r="O78" s="37"/>
-      <c r="P78" s="200"/>
-      <c r="Q78" s="201"/>
-      <c r="R78" s="201"/>
-      <c r="S78" s="201"/>
-      <c r="T78" s="201"/>
+      <c r="P78" s="146"/>
+      <c r="Q78" s="147"/>
+      <c r="R78" s="147"/>
+      <c r="S78" s="147"/>
+      <c r="T78" s="147"/>
       <c r="U78" s="77">
         <f>(I77*P78)+(J77*Q78)+(K77*R78)+(L77*S78)+(M77*T78)</f>
         <v>0</v>
@@ -9677,11 +9678,11 @@
         <v>0</v>
       </c>
       <c r="O79" s="37"/>
-      <c r="P79" s="198"/>
-      <c r="Q79" s="199"/>
-      <c r="R79" s="199"/>
-      <c r="S79" s="199"/>
-      <c r="T79" s="199"/>
+      <c r="P79" s="144"/>
+      <c r="Q79" s="145"/>
+      <c r="R79" s="145"/>
+      <c r="S79" s="145"/>
+      <c r="T79" s="145"/>
       <c r="U79" s="40">
         <f>ROUND(((P79*I79)+(Q79*J79)+(R79*K79)+(S79*L79)+(T79*M79)),3)</f>
         <v>0</v>
@@ -9741,13 +9742,13 @@
     <row r="80" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="91"/>
       <c r="B80" s="89"/>
-      <c r="C80" s="174" t="s">
+      <c r="C80" s="148" t="s">
         <v>48</v>
       </c>
-      <c r="D80" s="175"/>
-      <c r="E80" s="175"/>
-      <c r="F80" s="175"/>
-      <c r="G80" s="176"/>
+      <c r="D80" s="149"/>
+      <c r="E80" s="149"/>
+      <c r="F80" s="149"/>
+      <c r="G80" s="150"/>
       <c r="H80" s="34"/>
       <c r="I80" s="57"/>
       <c r="J80" s="61"/>
@@ -9756,11 +9757,11 @@
       <c r="M80" s="85"/>
       <c r="N80" s="62"/>
       <c r="O80" s="37"/>
-      <c r="P80" s="201"/>
-      <c r="Q80" s="201"/>
-      <c r="R80" s="199"/>
-      <c r="S80" s="201"/>
-      <c r="T80" s="201"/>
+      <c r="P80" s="147"/>
+      <c r="Q80" s="147"/>
+      <c r="R80" s="145"/>
+      <c r="S80" s="147"/>
+      <c r="T80" s="147"/>
       <c r="U80" s="77">
         <f>(I79*P80)+(J79*Q80)+(K79*R80)+(L79*S80)+(M79*T80)</f>
         <v>0</v>
@@ -9805,11 +9806,11 @@
         <v>0</v>
       </c>
       <c r="O81" s="37"/>
-      <c r="P81" s="198"/>
-      <c r="Q81" s="199"/>
-      <c r="R81" s="199"/>
-      <c r="S81" s="199"/>
-      <c r="T81" s="199"/>
+      <c r="P81" s="144"/>
+      <c r="Q81" s="145"/>
+      <c r="R81" s="145"/>
+      <c r="S81" s="145"/>
+      <c r="T81" s="145"/>
       <c r="U81" s="40">
         <f>ROUND(((P81*I81)+(Q81*J81)+(R81*K81)+(S81*L81)+(T81*M81)),3)</f>
         <v>0</v>
@@ -9869,13 +9870,13 @@
     <row r="82" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="91"/>
       <c r="B82" s="89"/>
-      <c r="C82" s="174" t="s">
+      <c r="C82" s="148" t="s">
         <v>48</v>
       </c>
-      <c r="D82" s="175"/>
-      <c r="E82" s="175"/>
-      <c r="F82" s="175"/>
-      <c r="G82" s="176"/>
+      <c r="D82" s="149"/>
+      <c r="E82" s="149"/>
+      <c r="F82" s="149"/>
+      <c r="G82" s="150"/>
       <c r="H82" s="34"/>
       <c r="I82" s="57"/>
       <c r="J82" s="61"/>
@@ -9884,11 +9885,11 @@
       <c r="M82" s="85"/>
       <c r="N82" s="62"/>
       <c r="O82" s="37"/>
-      <c r="P82" s="200"/>
-      <c r="Q82" s="201"/>
-      <c r="R82" s="201"/>
-      <c r="S82" s="201"/>
-      <c r="T82" s="201"/>
+      <c r="P82" s="146"/>
+      <c r="Q82" s="147"/>
+      <c r="R82" s="147"/>
+      <c r="S82" s="147"/>
+      <c r="T82" s="147"/>
       <c r="U82" s="77">
         <f>(I81*P82)+(J81*Q82)+(K81*R82)+(L81*S82)+(M81*T82)</f>
         <v>0</v>
@@ -9933,11 +9934,11 @@
         <v>0</v>
       </c>
       <c r="O83" s="37"/>
-      <c r="P83" s="198"/>
-      <c r="Q83" s="199"/>
-      <c r="R83" s="199"/>
-      <c r="S83" s="199"/>
-      <c r="T83" s="199"/>
+      <c r="P83" s="144"/>
+      <c r="Q83" s="145"/>
+      <c r="R83" s="145"/>
+      <c r="S83" s="145"/>
+      <c r="T83" s="145"/>
       <c r="U83" s="40">
         <f>ROUND(((P83*I83)+(Q83*J83)+(R83*K83)+(S83*L83)+(T83*M83)),3)</f>
         <v>0</v>
@@ -9997,13 +9998,13 @@
     <row r="84" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" s="91"/>
       <c r="B84" s="88"/>
-      <c r="C84" s="174" t="s">
+      <c r="C84" s="148" t="s">
         <v>48</v>
       </c>
-      <c r="D84" s="175"/>
-      <c r="E84" s="175"/>
-      <c r="F84" s="175"/>
-      <c r="G84" s="176"/>
+      <c r="D84" s="149"/>
+      <c r="E84" s="149"/>
+      <c r="F84" s="149"/>
+      <c r="G84" s="150"/>
       <c r="H84" s="34"/>
       <c r="I84" s="57"/>
       <c r="J84" s="61"/>
@@ -10012,11 +10013,11 @@
       <c r="M84" s="85"/>
       <c r="N84" s="62"/>
       <c r="O84" s="37"/>
-      <c r="P84" s="200"/>
-      <c r="Q84" s="201"/>
-      <c r="R84" s="201"/>
-      <c r="S84" s="201"/>
-      <c r="T84" s="201"/>
+      <c r="P84" s="146"/>
+      <c r="Q84" s="147"/>
+      <c r="R84" s="147"/>
+      <c r="S84" s="147"/>
+      <c r="T84" s="147"/>
       <c r="U84" s="77">
         <f>(I83*P84)+(J83*Q84)+(K83*R84)+(L83*S84)+(M83*T84)</f>
         <v>0</v>
@@ -10061,11 +10062,11 @@
         <v>0</v>
       </c>
       <c r="O85" s="37"/>
-      <c r="P85" s="198"/>
-      <c r="Q85" s="199"/>
-      <c r="R85" s="199"/>
-      <c r="S85" s="199"/>
-      <c r="T85" s="199"/>
+      <c r="P85" s="144"/>
+      <c r="Q85" s="145"/>
+      <c r="R85" s="145"/>
+      <c r="S85" s="145"/>
+      <c r="T85" s="145"/>
       <c r="U85" s="40">
         <f>ROUND(((P85*I85)+(Q85*J85)+(R85*K85)+(S85*L85)+(T85*M85)),3)</f>
         <v>0</v>
@@ -10119,13 +10120,13 @@
     <row r="86" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="91"/>
       <c r="B86" s="89"/>
-      <c r="C86" s="174" t="s">
+      <c r="C86" s="148" t="s">
         <v>48</v>
       </c>
-      <c r="D86" s="175"/>
-      <c r="E86" s="175"/>
-      <c r="F86" s="175"/>
-      <c r="G86" s="176"/>
+      <c r="D86" s="149"/>
+      <c r="E86" s="149"/>
+      <c r="F86" s="149"/>
+      <c r="G86" s="150"/>
       <c r="H86" s="34"/>
       <c r="I86" s="57"/>
       <c r="J86" s="61"/>
@@ -10134,11 +10135,11 @@
       <c r="M86" s="85"/>
       <c r="N86" s="62"/>
       <c r="O86" s="37"/>
-      <c r="P86" s="200"/>
-      <c r="Q86" s="199"/>
-      <c r="R86" s="199"/>
-      <c r="S86" s="201"/>
-      <c r="T86" s="201"/>
+      <c r="P86" s="146"/>
+      <c r="Q86" s="145"/>
+      <c r="R86" s="145"/>
+      <c r="S86" s="147"/>
+      <c r="T86" s="147"/>
       <c r="U86" s="77">
         <f>(I85*P86)+(J85*Q86)+(K85*R86)+(L85*S86)+(M85*T86)</f>
         <v>0</v>
@@ -10183,11 +10184,11 @@
         <v>0</v>
       </c>
       <c r="O87" s="37"/>
-      <c r="P87" s="198"/>
-      <c r="Q87" s="199"/>
-      <c r="R87" s="199"/>
-      <c r="S87" s="199"/>
-      <c r="T87" s="199"/>
+      <c r="P87" s="144"/>
+      <c r="Q87" s="145"/>
+      <c r="R87" s="145"/>
+      <c r="S87" s="145"/>
+      <c r="T87" s="145"/>
       <c r="U87" s="40">
         <f>ROUND(((P87*I87)+(Q87*J87)+(R87*K87)+(S87*L87)+(T87*M87)),3)</f>
         <v>0</v>
@@ -10247,13 +10248,13 @@
     <row r="88" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="91"/>
       <c r="B88" s="89"/>
-      <c r="C88" s="174" t="s">
+      <c r="C88" s="148" t="s">
         <v>48</v>
       </c>
-      <c r="D88" s="175"/>
-      <c r="E88" s="175"/>
-      <c r="F88" s="175"/>
-      <c r="G88" s="176"/>
+      <c r="D88" s="149"/>
+      <c r="E88" s="149"/>
+      <c r="F88" s="149"/>
+      <c r="G88" s="150"/>
       <c r="H88" s="34"/>
       <c r="I88" s="57"/>
       <c r="J88" s="61"/>
@@ -10262,11 +10263,11 @@
       <c r="M88" s="85"/>
       <c r="N88" s="62"/>
       <c r="O88" s="37"/>
-      <c r="P88" s="200"/>
-      <c r="Q88" s="201"/>
-      <c r="R88" s="201"/>
-      <c r="S88" s="201"/>
-      <c r="T88" s="201"/>
+      <c r="P88" s="146"/>
+      <c r="Q88" s="147"/>
+      <c r="R88" s="147"/>
+      <c r="S88" s="147"/>
+      <c r="T88" s="147"/>
       <c r="U88" s="77">
         <f>(I87*P88)+(J87*Q88)+(K87*R88)+(L87*S88)+(M87*T88)</f>
         <v>0</v>
@@ -10311,11 +10312,11 @@
         <v>0</v>
       </c>
       <c r="O89" s="37"/>
-      <c r="P89" s="198"/>
-      <c r="Q89" s="199"/>
-      <c r="R89" s="199"/>
-      <c r="S89" s="199"/>
-      <c r="T89" s="199"/>
+      <c r="P89" s="144"/>
+      <c r="Q89" s="145"/>
+      <c r="R89" s="145"/>
+      <c r="S89" s="145"/>
+      <c r="T89" s="145"/>
       <c r="U89" s="40">
         <f>ROUND(((P89*I89)+(Q89*J89)+(R89*K89)+(S89*L89)+(T89*M89)),3)</f>
         <v>0</v>
@@ -10375,13 +10376,13 @@
     <row r="90" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" s="59"/>
       <c r="B90" s="64"/>
-      <c r="C90" s="174" t="s">
+      <c r="C90" s="148" t="s">
         <v>48</v>
       </c>
-      <c r="D90" s="175"/>
-      <c r="E90" s="175"/>
-      <c r="F90" s="175"/>
-      <c r="G90" s="176"/>
+      <c r="D90" s="149"/>
+      <c r="E90" s="149"/>
+      <c r="F90" s="149"/>
+      <c r="G90" s="150"/>
       <c r="H90" s="34"/>
       <c r="I90" s="57"/>
       <c r="J90" s="61"/>
@@ -10390,11 +10391,11 @@
       <c r="M90" s="85"/>
       <c r="N90" s="62"/>
       <c r="O90" s="37"/>
-      <c r="P90" s="200"/>
-      <c r="Q90" s="201"/>
-      <c r="R90" s="201"/>
-      <c r="S90" s="201"/>
-      <c r="T90" s="201"/>
+      <c r="P90" s="146"/>
+      <c r="Q90" s="147"/>
+      <c r="R90" s="147"/>
+      <c r="S90" s="147"/>
+      <c r="T90" s="147"/>
       <c r="U90" s="77">
         <f>(I89*P90)+(J89*Q90)+(K89*R90)+(L89*S90)+(M89*T90)</f>
         <v>0</v>

--- a/템플릿/LH간이종심100-300억_템플릿.xlsx
+++ b/템플릿/LH간이종심100-300억_템플릿.xlsx
@@ -4115,6 +4115,144 @@
     <xf numFmtId="177" fontId="7" fillId="10" borderId="43" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="7" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="7" fillId="2" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="7" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="9" fillId="2" borderId="17" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="9" fillId="2" borderId="55" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="9" fillId="2" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="7" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="6" fillId="2" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="7" fillId="5" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="7" fillId="5" borderId="41" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
@@ -4124,45 +4262,9 @@
     <xf numFmtId="0" fontId="11" fillId="10" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="7" fillId="5" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="7" fillId="5" borderId="41" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4172,109 +4274,7 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="7" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="22" fontId="6" fillId="2" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="7" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="7" fillId="2" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="7" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="9" fillId="2" borderId="17" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="9" fillId="2" borderId="55" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="9" fillId="2" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -4618,7 +4618,7 @@
     <col min="23" max="27" width="8.109375" style="1" customWidth="1"/>
     <col min="28" max="28" width="8.44140625" style="1" customWidth="1"/>
     <col min="29" max="29" width="8.77734375" style="1" customWidth="1"/>
-    <col min="30" max="30" width="7.88671875" style="1" customWidth="1"/>
+    <col min="30" max="30" width="8.88671875" style="1" customWidth="1"/>
     <col min="31" max="31" width="7" style="1" customWidth="1"/>
     <col min="32" max="32" width="7.21875" style="1" customWidth="1"/>
     <col min="33" max="33" width="7.6640625" style="76" customWidth="1"/>
@@ -4644,22 +4644,22 @@
       <c r="D1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="189"/>
-      <c r="F1" s="190"/>
+      <c r="E1" s="153"/>
+      <c r="F1" s="154"/>
       <c r="G1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="191"/>
-      <c r="I1" s="192"/>
-      <c r="J1" s="193"/>
+      <c r="H1" s="155"/>
+      <c r="I1" s="156"/>
+      <c r="J1" s="157"/>
       <c r="K1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="191">
-        <v>0</v>
-      </c>
-      <c r="M1" s="192"/>
-      <c r="N1" s="194"/>
+      <c r="L1" s="155">
+        <v>0</v>
+      </c>
+      <c r="M1" s="156"/>
+      <c r="N1" s="158"/>
       <c r="O1" s="6" t="s">
         <v>52</v>
       </c>
@@ -4673,20 +4673,20 @@
       <c r="W1" s="6"/>
       <c r="X1" s="6"/>
       <c r="Y1" s="6"/>
-      <c r="Z1" s="184" t="s">
+      <c r="Z1" s="148" t="s">
         <v>7</v>
       </c>
-      <c r="AA1" s="184"/>
+      <c r="AA1" s="148"/>
       <c r="AB1" s="7"/>
-      <c r="AC1" s="184" t="s">
+      <c r="AC1" s="148" t="s">
         <v>8</v>
       </c>
-      <c r="AD1" s="184"/>
-      <c r="AE1" s="185" t="s">
+      <c r="AD1" s="148"/>
+      <c r="AE1" s="149" t="s">
         <v>9</v>
       </c>
-      <c r="AF1" s="186"/>
-      <c r="AG1" s="187"/>
+      <c r="AF1" s="150"/>
+      <c r="AG1" s="151"/>
       <c r="AH1" s="6"/>
       <c r="AI1" s="6"/>
       <c r="AJ1" s="6"/>
@@ -4697,69 +4697,69 @@
       <c r="AO1" s="8"/>
     </row>
     <row r="2" spans="1:41" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="169" t="s">
+      <c r="A2" s="175" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="169"/>
-      <c r="C2" s="170"/>
+      <c r="B2" s="175"/>
+      <c r="C2" s="176"/>
       <c r="D2" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="171"/>
-      <c r="F2" s="172"/>
+      <c r="E2" s="177"/>
+      <c r="F2" s="178"/>
       <c r="G2" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="171">
+      <c r="H2" s="177">
         <f>E2</f>
         <v>0</v>
       </c>
-      <c r="I2" s="173"/>
-      <c r="J2" s="172"/>
+      <c r="I2" s="179"/>
+      <c r="J2" s="178"/>
       <c r="K2" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="L2" s="174">
+      <c r="L2" s="180">
         <f>H2*3</f>
         <v>0</v>
       </c>
-      <c r="M2" s="175"/>
+      <c r="M2" s="181"/>
       <c r="N2" s="12" t="s">
         <v>14</v>
       </c>
       <c r="O2" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="P2" s="176" t="s">
+      <c r="P2" s="182" t="s">
         <v>53</v>
       </c>
-      <c r="Q2" s="176"/>
-      <c r="R2" s="176"/>
-      <c r="S2" s="176"/>
-      <c r="T2" s="176"/>
+      <c r="Q2" s="182"/>
+      <c r="R2" s="182"/>
+      <c r="S2" s="182"/>
+      <c r="T2" s="182"/>
       <c r="U2" s="84" t="s">
         <v>51</v>
       </c>
       <c r="V2" s="14"/>
       <c r="W2" s="15"/>
-      <c r="X2" s="188" t="s">
-        <v>0</v>
-      </c>
-      <c r="Y2" s="188"/>
-      <c r="Z2" s="195"/>
-      <c r="AA2" s="196"/>
+      <c r="X2" s="152" t="s">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="152"/>
+      <c r="Z2" s="159"/>
+      <c r="AA2" s="160"/>
       <c r="AB2" s="83"/>
-      <c r="AC2" s="197">
+      <c r="AC2" s="161">
         <f>H1</f>
         <v>0</v>
       </c>
-      <c r="AD2" s="198"/>
-      <c r="AE2" s="199" t="e">
+      <c r="AD2" s="162"/>
+      <c r="AE2" s="163" t="e">
         <f>Z2/AC2</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AF2" s="200"/>
-      <c r="AG2" s="201"/>
+      <c r="AF2" s="164"/>
+      <c r="AG2" s="165"/>
       <c r="AI2" s="16"/>
       <c r="AJ2" s="17"/>
       <c r="AK2" s="17"/>
@@ -4770,77 +4770,77 @@
       </c>
     </row>
     <row r="3" spans="1:41" s="22" customFormat="1" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="177" t="s">
+      <c r="A3" s="166" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="179" t="s">
+      <c r="B3" s="168" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="167" t="s">
+      <c r="C3" s="170" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="167"/>
-      <c r="E3" s="167"/>
-      <c r="F3" s="167"/>
-      <c r="G3" s="167"/>
-      <c r="H3" s="167"/>
-      <c r="I3" s="181" t="s">
+      <c r="D3" s="170"/>
+      <c r="E3" s="170"/>
+      <c r="F3" s="170"/>
+      <c r="G3" s="170"/>
+      <c r="H3" s="170"/>
+      <c r="I3" s="171" t="s">
         <v>20</v>
       </c>
-      <c r="J3" s="163"/>
-      <c r="K3" s="167"/>
-      <c r="L3" s="163"/>
-      <c r="M3" s="182"/>
-      <c r="N3" s="167" t="s">
+      <c r="J3" s="172"/>
+      <c r="K3" s="170"/>
+      <c r="L3" s="172"/>
+      <c r="M3" s="173"/>
+      <c r="N3" s="170" t="s">
         <v>21</v>
       </c>
-      <c r="O3" s="154"/>
-      <c r="P3" s="167" t="s">
+      <c r="O3" s="186"/>
+      <c r="P3" s="170" t="s">
         <v>22</v>
       </c>
-      <c r="Q3" s="167"/>
-      <c r="R3" s="167"/>
-      <c r="S3" s="167"/>
-      <c r="T3" s="168"/>
-      <c r="U3" s="162" t="s">
+      <c r="Q3" s="170"/>
+      <c r="R3" s="170"/>
+      <c r="S3" s="170"/>
+      <c r="T3" s="201"/>
+      <c r="U3" s="197" t="s">
         <v>23</v>
       </c>
-      <c r="V3" s="163"/>
-      <c r="W3" s="163"/>
-      <c r="X3" s="163"/>
-      <c r="Y3" s="163"/>
-      <c r="Z3" s="163"/>
-      <c r="AA3" s="163"/>
-      <c r="AB3" s="163"/>
-      <c r="AC3" s="163"/>
-      <c r="AD3" s="163"/>
-      <c r="AE3" s="163"/>
-      <c r="AF3" s="163"/>
-      <c r="AG3" s="163"/>
-      <c r="AH3" s="164"/>
+      <c r="V3" s="172"/>
+      <c r="W3" s="172"/>
+      <c r="X3" s="172"/>
+      <c r="Y3" s="172"/>
+      <c r="Z3" s="172"/>
+      <c r="AA3" s="172"/>
+      <c r="AB3" s="172"/>
+      <c r="AC3" s="172"/>
+      <c r="AD3" s="172"/>
+      <c r="AE3" s="172"/>
+      <c r="AF3" s="172"/>
+      <c r="AG3" s="172"/>
+      <c r="AH3" s="198"/>
       <c r="AI3" s="26"/>
-      <c r="AJ3" s="165" t="s">
+      <c r="AJ3" s="199" t="s">
         <v>24</v>
       </c>
-      <c r="AK3" s="154" t="s">
+      <c r="AK3" s="186" t="s">
         <v>25</v>
       </c>
-      <c r="AL3" s="156" t="s">
+      <c r="AL3" s="188" t="s">
         <v>26</v>
       </c>
-      <c r="AM3" s="158" t="s">
+      <c r="AM3" s="190" t="s">
         <v>27</v>
       </c>
       <c r="AN3" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="AO3" s="160" t="s">
+      <c r="AO3" s="192" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:41" s="22" customFormat="1" ht="41.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="178"/>
-      <c r="B4" s="180"/>
+      <c r="A4" s="167"/>
+      <c r="B4" s="169"/>
       <c r="C4" s="23" t="s">
         <v>30</v>
       </c>
@@ -4874,8 +4874,8 @@
       <c r="M4" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="N4" s="183"/>
-      <c r="O4" s="155"/>
+      <c r="N4" s="174"/>
+      <c r="O4" s="187"/>
       <c r="P4" s="23" t="s">
         <v>37</v>
       </c>
@@ -4936,12 +4936,12 @@
       <c r="AI4" s="115" t="s">
         <v>47</v>
       </c>
-      <c r="AJ4" s="166"/>
-      <c r="AK4" s="155"/>
-      <c r="AL4" s="157"/>
-      <c r="AM4" s="159"/>
+      <c r="AJ4" s="200"/>
+      <c r="AK4" s="187"/>
+      <c r="AL4" s="189"/>
+      <c r="AM4" s="191"/>
       <c r="AN4" s="31"/>
-      <c r="AO4" s="161"/>
+      <c r="AO4" s="193"/>
     </row>
     <row r="5" spans="1:41" s="22" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="90">
@@ -5028,13 +5028,13 @@
     <row r="6" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="91"/>
       <c r="B6" s="133"/>
-      <c r="C6" s="148" t="s">
+      <c r="C6" s="194" t="s">
         <v>48</v>
       </c>
-      <c r="D6" s="149"/>
-      <c r="E6" s="149"/>
-      <c r="F6" s="149"/>
-      <c r="G6" s="150"/>
+      <c r="D6" s="195"/>
+      <c r="E6" s="195"/>
+      <c r="F6" s="195"/>
+      <c r="G6" s="196"/>
       <c r="H6" s="34"/>
       <c r="I6" s="57"/>
       <c r="J6" s="61"/>
@@ -5158,13 +5158,13 @@
     <row r="8" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="91"/>
       <c r="B8" s="132"/>
-      <c r="C8" s="148" t="s">
+      <c r="C8" s="194" t="s">
         <v>48</v>
       </c>
-      <c r="D8" s="149"/>
-      <c r="E8" s="149"/>
-      <c r="F8" s="149"/>
-      <c r="G8" s="150"/>
+      <c r="D8" s="195"/>
+      <c r="E8" s="195"/>
+      <c r="F8" s="195"/>
+      <c r="G8" s="196"/>
       <c r="H8" s="34"/>
       <c r="I8" s="57"/>
       <c r="J8" s="61"/>
@@ -5288,13 +5288,13 @@
     <row r="10" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="91"/>
       <c r="B10" s="133"/>
-      <c r="C10" s="148" t="s">
+      <c r="C10" s="194" t="s">
         <v>48</v>
       </c>
-      <c r="D10" s="149"/>
-      <c r="E10" s="149"/>
-      <c r="F10" s="149"/>
-      <c r="G10" s="150"/>
+      <c r="D10" s="195"/>
+      <c r="E10" s="195"/>
+      <c r="F10" s="195"/>
+      <c r="G10" s="196"/>
       <c r="H10" s="34"/>
       <c r="I10" s="57"/>
       <c r="J10" s="61"/>
@@ -5418,13 +5418,13 @@
     <row r="12" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="91"/>
       <c r="B12" s="133"/>
-      <c r="C12" s="148" t="s">
+      <c r="C12" s="194" t="s">
         <v>48</v>
       </c>
-      <c r="D12" s="149"/>
-      <c r="E12" s="149"/>
-      <c r="F12" s="149"/>
-      <c r="G12" s="150"/>
+      <c r="D12" s="195"/>
+      <c r="E12" s="195"/>
+      <c r="F12" s="195"/>
+      <c r="G12" s="196"/>
       <c r="H12" s="34"/>
       <c r="I12" s="57"/>
       <c r="J12" s="61"/>
@@ -5548,13 +5548,13 @@
     <row r="14" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="91"/>
       <c r="B14" s="89"/>
-      <c r="C14" s="148" t="s">
+      <c r="C14" s="194" t="s">
         <v>48</v>
       </c>
-      <c r="D14" s="149"/>
-      <c r="E14" s="149"/>
-      <c r="F14" s="149"/>
-      <c r="G14" s="150"/>
+      <c r="D14" s="195"/>
+      <c r="E14" s="195"/>
+      <c r="F14" s="195"/>
+      <c r="G14" s="196"/>
       <c r="H14" s="34"/>
       <c r="I14" s="57"/>
       <c r="J14" s="61"/>
@@ -5676,13 +5676,13 @@
     <row r="16" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="91"/>
       <c r="B16" s="89"/>
-      <c r="C16" s="148" t="s">
+      <c r="C16" s="194" t="s">
         <v>48</v>
       </c>
-      <c r="D16" s="149"/>
-      <c r="E16" s="149"/>
-      <c r="F16" s="149"/>
-      <c r="G16" s="150"/>
+      <c r="D16" s="195"/>
+      <c r="E16" s="195"/>
+      <c r="F16" s="195"/>
+      <c r="G16" s="196"/>
       <c r="H16" s="34"/>
       <c r="I16" s="57"/>
       <c r="J16" s="61"/>
@@ -5804,13 +5804,13 @@
     <row r="18" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="91"/>
       <c r="B18" s="89"/>
-      <c r="C18" s="148" t="s">
+      <c r="C18" s="194" t="s">
         <v>48</v>
       </c>
-      <c r="D18" s="149"/>
-      <c r="E18" s="149"/>
-      <c r="F18" s="149"/>
-      <c r="G18" s="150"/>
+      <c r="D18" s="195"/>
+      <c r="E18" s="195"/>
+      <c r="F18" s="195"/>
+      <c r="G18" s="196"/>
       <c r="H18" s="34"/>
       <c r="I18" s="57"/>
       <c r="J18" s="61"/>
@@ -5932,13 +5932,13 @@
     <row r="20" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="91"/>
       <c r="B20" s="89"/>
-      <c r="C20" s="151" t="s">
+      <c r="C20" s="183" t="s">
         <v>48</v>
       </c>
-      <c r="D20" s="152"/>
-      <c r="E20" s="152"/>
-      <c r="F20" s="152"/>
-      <c r="G20" s="153"/>
+      <c r="D20" s="184"/>
+      <c r="E20" s="184"/>
+      <c r="F20" s="184"/>
+      <c r="G20" s="185"/>
       <c r="H20" s="34"/>
       <c r="I20" s="57"/>
       <c r="J20" s="61"/>
@@ -6054,13 +6054,13 @@
     <row r="22" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="91"/>
       <c r="B22" s="89"/>
-      <c r="C22" s="151" t="s">
+      <c r="C22" s="183" t="s">
         <v>48</v>
       </c>
-      <c r="D22" s="152"/>
-      <c r="E22" s="152"/>
-      <c r="F22" s="152"/>
-      <c r="G22" s="153"/>
+      <c r="D22" s="184"/>
+      <c r="E22" s="184"/>
+      <c r="F22" s="184"/>
+      <c r="G22" s="185"/>
       <c r="H22" s="97"/>
       <c r="I22" s="98"/>
       <c r="J22" s="99"/>
@@ -6176,13 +6176,13 @@
     <row r="24" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="91"/>
       <c r="B24" s="89"/>
-      <c r="C24" s="151" t="s">
+      <c r="C24" s="183" t="s">
         <v>48</v>
       </c>
-      <c r="D24" s="152"/>
-      <c r="E24" s="152"/>
-      <c r="F24" s="152"/>
-      <c r="G24" s="153"/>
+      <c r="D24" s="184"/>
+      <c r="E24" s="184"/>
+      <c r="F24" s="184"/>
+      <c r="G24" s="185"/>
       <c r="H24" s="34"/>
       <c r="I24" s="57"/>
       <c r="J24" s="61"/>
@@ -6298,13 +6298,13 @@
     <row r="26" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="91"/>
       <c r="B26" s="89"/>
-      <c r="C26" s="151" t="s">
+      <c r="C26" s="183" t="s">
         <v>48</v>
       </c>
-      <c r="D26" s="152"/>
-      <c r="E26" s="152"/>
-      <c r="F26" s="152"/>
-      <c r="G26" s="153"/>
+      <c r="D26" s="184"/>
+      <c r="E26" s="184"/>
+      <c r="F26" s="184"/>
+      <c r="G26" s="185"/>
       <c r="H26" s="34"/>
       <c r="I26" s="57"/>
       <c r="J26" s="61"/>
@@ -6426,13 +6426,13 @@
     <row r="28" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="91"/>
       <c r="B28" s="89"/>
-      <c r="C28" s="148" t="s">
+      <c r="C28" s="194" t="s">
         <v>48</v>
       </c>
-      <c r="D28" s="149"/>
-      <c r="E28" s="149"/>
-      <c r="F28" s="149"/>
-      <c r="G28" s="150"/>
+      <c r="D28" s="195"/>
+      <c r="E28" s="195"/>
+      <c r="F28" s="195"/>
+      <c r="G28" s="196"/>
       <c r="H28" s="60"/>
       <c r="I28" s="57"/>
       <c r="J28" s="61"/>
@@ -6554,13 +6554,13 @@
     <row r="30" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="91"/>
       <c r="B30" s="89"/>
-      <c r="C30" s="151" t="s">
+      <c r="C30" s="183" t="s">
         <v>48</v>
       </c>
-      <c r="D30" s="152"/>
-      <c r="E30" s="152"/>
-      <c r="F30" s="152"/>
-      <c r="G30" s="153"/>
+      <c r="D30" s="184"/>
+      <c r="E30" s="184"/>
+      <c r="F30" s="184"/>
+      <c r="G30" s="185"/>
       <c r="H30" s="34"/>
       <c r="I30" s="57"/>
       <c r="J30" s="61"/>
@@ -6676,13 +6676,13 @@
     <row r="32" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="91"/>
       <c r="B32" s="89"/>
-      <c r="C32" s="151" t="s">
+      <c r="C32" s="183" t="s">
         <v>48</v>
       </c>
-      <c r="D32" s="152"/>
-      <c r="E32" s="152"/>
-      <c r="F32" s="152"/>
-      <c r="G32" s="153"/>
+      <c r="D32" s="184"/>
+      <c r="E32" s="184"/>
+      <c r="F32" s="184"/>
+      <c r="G32" s="185"/>
       <c r="H32" s="97"/>
       <c r="I32" s="98"/>
       <c r="J32" s="99"/>
@@ -6804,13 +6804,13 @@
     <row r="34" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="91"/>
       <c r="B34" s="89"/>
-      <c r="C34" s="151" t="s">
+      <c r="C34" s="183" t="s">
         <v>48</v>
       </c>
-      <c r="D34" s="152"/>
-      <c r="E34" s="152"/>
-      <c r="F34" s="152"/>
-      <c r="G34" s="153"/>
+      <c r="D34" s="184"/>
+      <c r="E34" s="184"/>
+      <c r="F34" s="184"/>
+      <c r="G34" s="185"/>
       <c r="H34" s="34"/>
       <c r="I34" s="57"/>
       <c r="J34" s="61"/>
@@ -6932,13 +6932,13 @@
     <row r="36" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="91"/>
       <c r="B36" s="89"/>
-      <c r="C36" s="151" t="s">
+      <c r="C36" s="183" t="s">
         <v>48</v>
       </c>
-      <c r="D36" s="152"/>
-      <c r="E36" s="152"/>
-      <c r="F36" s="152"/>
-      <c r="G36" s="153"/>
+      <c r="D36" s="184"/>
+      <c r="E36" s="184"/>
+      <c r="F36" s="184"/>
+      <c r="G36" s="185"/>
       <c r="H36" s="34"/>
       <c r="I36" s="57"/>
       <c r="J36" s="61"/>
@@ -7060,13 +7060,13 @@
     <row r="38" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="91"/>
       <c r="B38" s="89"/>
-      <c r="C38" s="151" t="s">
+      <c r="C38" s="183" t="s">
         <v>48</v>
       </c>
-      <c r="D38" s="152"/>
-      <c r="E38" s="152"/>
-      <c r="F38" s="152"/>
-      <c r="G38" s="153"/>
+      <c r="D38" s="184"/>
+      <c r="E38" s="184"/>
+      <c r="F38" s="184"/>
+      <c r="G38" s="185"/>
       <c r="H38" s="34"/>
       <c r="I38" s="57"/>
       <c r="J38" s="61"/>
@@ -7188,13 +7188,13 @@
     <row r="40" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="91"/>
       <c r="B40" s="89"/>
-      <c r="C40" s="151" t="s">
+      <c r="C40" s="183" t="s">
         <v>48</v>
       </c>
-      <c r="D40" s="152"/>
-      <c r="E40" s="152"/>
-      <c r="F40" s="152"/>
-      <c r="G40" s="153"/>
+      <c r="D40" s="184"/>
+      <c r="E40" s="184"/>
+      <c r="F40" s="184"/>
+      <c r="G40" s="185"/>
       <c r="H40" s="34"/>
       <c r="I40" s="57"/>
       <c r="J40" s="61"/>
@@ -7316,13 +7316,13 @@
     <row r="42" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="91"/>
       <c r="B42" s="89"/>
-      <c r="C42" s="151" t="s">
+      <c r="C42" s="183" t="s">
         <v>48</v>
       </c>
-      <c r="D42" s="152"/>
-      <c r="E42" s="152"/>
-      <c r="F42" s="152"/>
-      <c r="G42" s="153"/>
+      <c r="D42" s="184"/>
+      <c r="E42" s="184"/>
+      <c r="F42" s="184"/>
+      <c r="G42" s="185"/>
       <c r="H42" s="34"/>
       <c r="I42" s="57"/>
       <c r="J42" s="61"/>
@@ -7444,13 +7444,13 @@
     <row r="44" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="91"/>
       <c r="B44" s="89"/>
-      <c r="C44" s="151" t="s">
+      <c r="C44" s="183" t="s">
         <v>48</v>
       </c>
-      <c r="D44" s="152"/>
-      <c r="E44" s="152"/>
-      <c r="F44" s="152"/>
-      <c r="G44" s="153"/>
+      <c r="D44" s="184"/>
+      <c r="E44" s="184"/>
+      <c r="F44" s="184"/>
+      <c r="G44" s="185"/>
       <c r="H44" s="34"/>
       <c r="I44" s="57"/>
       <c r="J44" s="61"/>
@@ -7572,13 +7572,13 @@
     <row r="46" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="91"/>
       <c r="B46" s="89"/>
-      <c r="C46" s="151" t="s">
+      <c r="C46" s="183" t="s">
         <v>48</v>
       </c>
-      <c r="D46" s="152"/>
-      <c r="E46" s="152"/>
-      <c r="F46" s="152"/>
-      <c r="G46" s="153"/>
+      <c r="D46" s="184"/>
+      <c r="E46" s="184"/>
+      <c r="F46" s="184"/>
+      <c r="G46" s="185"/>
       <c r="H46" s="34"/>
       <c r="I46" s="57"/>
       <c r="J46" s="61"/>
@@ -7700,13 +7700,13 @@
     <row r="48" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="91"/>
       <c r="B48" s="89"/>
-      <c r="C48" s="151" t="s">
+      <c r="C48" s="183" t="s">
         <v>48</v>
       </c>
-      <c r="D48" s="152"/>
-      <c r="E48" s="152"/>
-      <c r="F48" s="152"/>
-      <c r="G48" s="153"/>
+      <c r="D48" s="184"/>
+      <c r="E48" s="184"/>
+      <c r="F48" s="184"/>
+      <c r="G48" s="185"/>
       <c r="H48" s="34"/>
       <c r="I48" s="57"/>
       <c r="J48" s="61"/>
@@ -7828,13 +7828,13 @@
     <row r="50" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="91"/>
       <c r="B50" s="89"/>
-      <c r="C50" s="151" t="s">
+      <c r="C50" s="183" t="s">
         <v>48</v>
       </c>
-      <c r="D50" s="152"/>
-      <c r="E50" s="152"/>
-      <c r="F50" s="152"/>
-      <c r="G50" s="153"/>
+      <c r="D50" s="184"/>
+      <c r="E50" s="184"/>
+      <c r="F50" s="184"/>
+      <c r="G50" s="185"/>
       <c r="H50" s="34"/>
       <c r="I50" s="57"/>
       <c r="J50" s="61"/>
@@ -7958,13 +7958,13 @@
     <row r="52" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="91"/>
       <c r="B52" s="89"/>
-      <c r="C52" s="151" t="s">
+      <c r="C52" s="183" t="s">
         <v>48</v>
       </c>
-      <c r="D52" s="152"/>
-      <c r="E52" s="152"/>
-      <c r="F52" s="152"/>
-      <c r="G52" s="153"/>
+      <c r="D52" s="184"/>
+      <c r="E52" s="184"/>
+      <c r="F52" s="184"/>
+      <c r="G52" s="185"/>
       <c r="H52" s="34"/>
       <c r="I52" s="57"/>
       <c r="J52" s="61"/>
@@ -8088,13 +8088,13 @@
     <row r="54" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="91"/>
       <c r="B54" s="89"/>
-      <c r="C54" s="151" t="s">
+      <c r="C54" s="183" t="s">
         <v>48</v>
       </c>
-      <c r="D54" s="152"/>
-      <c r="E54" s="152"/>
-      <c r="F54" s="152"/>
-      <c r="G54" s="153"/>
+      <c r="D54" s="184"/>
+      <c r="E54" s="184"/>
+      <c r="F54" s="184"/>
+      <c r="G54" s="185"/>
       <c r="H54" s="34"/>
       <c r="I54" s="57"/>
       <c r="J54" s="61"/>
@@ -8218,13 +8218,13 @@
     <row r="56" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="91"/>
       <c r="B56" s="89"/>
-      <c r="C56" s="151" t="s">
+      <c r="C56" s="183" t="s">
         <v>48</v>
       </c>
-      <c r="D56" s="152"/>
-      <c r="E56" s="152"/>
-      <c r="F56" s="152"/>
-      <c r="G56" s="153"/>
+      <c r="D56" s="184"/>
+      <c r="E56" s="184"/>
+      <c r="F56" s="184"/>
+      <c r="G56" s="185"/>
       <c r="H56" s="34"/>
       <c r="I56" s="57"/>
       <c r="J56" s="61"/>
@@ -8340,13 +8340,13 @@
     <row r="58" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="91"/>
       <c r="B58" s="89"/>
-      <c r="C58" s="151" t="s">
+      <c r="C58" s="183" t="s">
         <v>48</v>
       </c>
-      <c r="D58" s="152"/>
-      <c r="E58" s="152"/>
-      <c r="F58" s="152"/>
-      <c r="G58" s="153"/>
+      <c r="D58" s="184"/>
+      <c r="E58" s="184"/>
+      <c r="F58" s="184"/>
+      <c r="G58" s="185"/>
       <c r="H58" s="97"/>
       <c r="I58" s="98"/>
       <c r="J58" s="99"/>
@@ -8468,13 +8468,13 @@
     <row r="60" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="91"/>
       <c r="B60" s="89"/>
-      <c r="C60" s="151" t="s">
+      <c r="C60" s="183" t="s">
         <v>48</v>
       </c>
-      <c r="D60" s="152"/>
-      <c r="E60" s="152"/>
-      <c r="F60" s="152"/>
-      <c r="G60" s="153"/>
+      <c r="D60" s="184"/>
+      <c r="E60" s="184"/>
+      <c r="F60" s="184"/>
+      <c r="G60" s="185"/>
       <c r="H60" s="34"/>
       <c r="I60" s="57"/>
       <c r="J60" s="61"/>
@@ -8596,13 +8596,13 @@
     <row r="62" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="91"/>
       <c r="B62" s="89"/>
-      <c r="C62" s="151" t="s">
+      <c r="C62" s="183" t="s">
         <v>48</v>
       </c>
-      <c r="D62" s="152"/>
-      <c r="E62" s="152"/>
-      <c r="F62" s="152"/>
-      <c r="G62" s="153"/>
+      <c r="D62" s="184"/>
+      <c r="E62" s="184"/>
+      <c r="F62" s="184"/>
+      <c r="G62" s="185"/>
       <c r="H62" s="34"/>
       <c r="I62" s="57"/>
       <c r="J62" s="61"/>
@@ -8724,13 +8724,13 @@
     <row r="64" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="91"/>
       <c r="B64" s="89"/>
-      <c r="C64" s="151" t="s">
+      <c r="C64" s="183" t="s">
         <v>48</v>
       </c>
-      <c r="D64" s="152"/>
-      <c r="E64" s="152"/>
-      <c r="F64" s="152"/>
-      <c r="G64" s="153"/>
+      <c r="D64" s="184"/>
+      <c r="E64" s="184"/>
+      <c r="F64" s="184"/>
+      <c r="G64" s="185"/>
       <c r="H64" s="34"/>
       <c r="I64" s="57"/>
       <c r="J64" s="61"/>
@@ -8852,13 +8852,13 @@
     <row r="66" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="91"/>
       <c r="B66" s="89"/>
-      <c r="C66" s="151" t="s">
+      <c r="C66" s="183" t="s">
         <v>48</v>
       </c>
-      <c r="D66" s="152"/>
-      <c r="E66" s="152"/>
-      <c r="F66" s="152"/>
-      <c r="G66" s="153"/>
+      <c r="D66" s="184"/>
+      <c r="E66" s="184"/>
+      <c r="F66" s="184"/>
+      <c r="G66" s="185"/>
       <c r="H66" s="34"/>
       <c r="I66" s="57"/>
       <c r="J66" s="61"/>
@@ -8980,13 +8980,13 @@
     <row r="68" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="91"/>
       <c r="B68" s="89"/>
-      <c r="C68" s="151" t="s">
+      <c r="C68" s="183" t="s">
         <v>48</v>
       </c>
-      <c r="D68" s="152"/>
-      <c r="E68" s="152"/>
-      <c r="F68" s="152"/>
-      <c r="G68" s="153"/>
+      <c r="D68" s="184"/>
+      <c r="E68" s="184"/>
+      <c r="F68" s="184"/>
+      <c r="G68" s="185"/>
       <c r="H68" s="34"/>
       <c r="I68" s="57"/>
       <c r="J68" s="61"/>
@@ -9108,13 +9108,13 @@
     <row r="70" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="91"/>
       <c r="B70" s="89"/>
-      <c r="C70" s="148" t="s">
+      <c r="C70" s="194" t="s">
         <v>48</v>
       </c>
-      <c r="D70" s="149"/>
-      <c r="E70" s="149"/>
-      <c r="F70" s="149"/>
-      <c r="G70" s="150"/>
+      <c r="D70" s="195"/>
+      <c r="E70" s="195"/>
+      <c r="F70" s="195"/>
+      <c r="G70" s="196"/>
       <c r="H70" s="34"/>
       <c r="I70" s="57"/>
       <c r="J70" s="61"/>
@@ -9230,13 +9230,13 @@
     <row r="72" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="91"/>
       <c r="B72" s="89"/>
-      <c r="C72" s="148" t="s">
+      <c r="C72" s="194" t="s">
         <v>48</v>
       </c>
-      <c r="D72" s="149"/>
-      <c r="E72" s="149"/>
-      <c r="F72" s="149"/>
-      <c r="G72" s="150"/>
+      <c r="D72" s="195"/>
+      <c r="E72" s="195"/>
+      <c r="F72" s="195"/>
+      <c r="G72" s="196"/>
       <c r="H72" s="34"/>
       <c r="I72" s="57"/>
       <c r="J72" s="61"/>
@@ -9358,13 +9358,13 @@
     <row r="74" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="91"/>
       <c r="B74" s="89"/>
-      <c r="C74" s="148" t="s">
+      <c r="C74" s="194" t="s">
         <v>48</v>
       </c>
-      <c r="D74" s="149"/>
-      <c r="E74" s="149"/>
-      <c r="F74" s="149"/>
-      <c r="G74" s="150"/>
+      <c r="D74" s="195"/>
+      <c r="E74" s="195"/>
+      <c r="F74" s="195"/>
+      <c r="G74" s="196"/>
       <c r="H74" s="34"/>
       <c r="I74" s="57"/>
       <c r="J74" s="61"/>
@@ -9486,13 +9486,13 @@
     <row r="76" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="91"/>
       <c r="B76" s="89"/>
-      <c r="C76" s="148" t="s">
+      <c r="C76" s="194" t="s">
         <v>48</v>
       </c>
-      <c r="D76" s="149"/>
-      <c r="E76" s="149"/>
-      <c r="F76" s="149"/>
-      <c r="G76" s="150"/>
+      <c r="D76" s="195"/>
+      <c r="E76" s="195"/>
+      <c r="F76" s="195"/>
+      <c r="G76" s="196"/>
       <c r="H76" s="34"/>
       <c r="I76" s="57"/>
       <c r="J76" s="61"/>
@@ -9614,13 +9614,13 @@
     <row r="78" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="91"/>
       <c r="B78" s="89"/>
-      <c r="C78" s="148" t="s">
+      <c r="C78" s="194" t="s">
         <v>48</v>
       </c>
-      <c r="D78" s="149"/>
-      <c r="E78" s="149"/>
-      <c r="F78" s="149"/>
-      <c r="G78" s="150"/>
+      <c r="D78" s="195"/>
+      <c r="E78" s="195"/>
+      <c r="F78" s="195"/>
+      <c r="G78" s="196"/>
       <c r="H78" s="34"/>
       <c r="I78" s="57"/>
       <c r="J78" s="61"/>
@@ -9742,13 +9742,13 @@
     <row r="80" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="91"/>
       <c r="B80" s="89"/>
-      <c r="C80" s="148" t="s">
+      <c r="C80" s="194" t="s">
         <v>48</v>
       </c>
-      <c r="D80" s="149"/>
-      <c r="E80" s="149"/>
-      <c r="F80" s="149"/>
-      <c r="G80" s="150"/>
+      <c r="D80" s="195"/>
+      <c r="E80" s="195"/>
+      <c r="F80" s="195"/>
+      <c r="G80" s="196"/>
       <c r="H80" s="34"/>
       <c r="I80" s="57"/>
       <c r="J80" s="61"/>
@@ -9870,13 +9870,13 @@
     <row r="82" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="91"/>
       <c r="B82" s="89"/>
-      <c r="C82" s="148" t="s">
+      <c r="C82" s="194" t="s">
         <v>48</v>
       </c>
-      <c r="D82" s="149"/>
-      <c r="E82" s="149"/>
-      <c r="F82" s="149"/>
-      <c r="G82" s="150"/>
+      <c r="D82" s="195"/>
+      <c r="E82" s="195"/>
+      <c r="F82" s="195"/>
+      <c r="G82" s="196"/>
       <c r="H82" s="34"/>
       <c r="I82" s="57"/>
       <c r="J82" s="61"/>
@@ -9998,13 +9998,13 @@
     <row r="84" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" s="91"/>
       <c r="B84" s="88"/>
-      <c r="C84" s="148" t="s">
+      <c r="C84" s="194" t="s">
         <v>48</v>
       </c>
-      <c r="D84" s="149"/>
-      <c r="E84" s="149"/>
-      <c r="F84" s="149"/>
-      <c r="G84" s="150"/>
+      <c r="D84" s="195"/>
+      <c r="E84" s="195"/>
+      <c r="F84" s="195"/>
+      <c r="G84" s="196"/>
       <c r="H84" s="34"/>
       <c r="I84" s="57"/>
       <c r="J84" s="61"/>
@@ -10120,13 +10120,13 @@
     <row r="86" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="91"/>
       <c r="B86" s="89"/>
-      <c r="C86" s="148" t="s">
+      <c r="C86" s="194" t="s">
         <v>48</v>
       </c>
-      <c r="D86" s="149"/>
-      <c r="E86" s="149"/>
-      <c r="F86" s="149"/>
-      <c r="G86" s="150"/>
+      <c r="D86" s="195"/>
+      <c r="E86" s="195"/>
+      <c r="F86" s="195"/>
+      <c r="G86" s="196"/>
       <c r="H86" s="34"/>
       <c r="I86" s="57"/>
       <c r="J86" s="61"/>
@@ -10248,13 +10248,13 @@
     <row r="88" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="91"/>
       <c r="B88" s="89"/>
-      <c r="C88" s="148" t="s">
+      <c r="C88" s="194" t="s">
         <v>48</v>
       </c>
-      <c r="D88" s="149"/>
-      <c r="E88" s="149"/>
-      <c r="F88" s="149"/>
-      <c r="G88" s="150"/>
+      <c r="D88" s="195"/>
+      <c r="E88" s="195"/>
+      <c r="F88" s="195"/>
+      <c r="G88" s="196"/>
       <c r="H88" s="34"/>
       <c r="I88" s="57"/>
       <c r="J88" s="61"/>
@@ -10376,13 +10376,13 @@
     <row r="90" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" s="59"/>
       <c r="B90" s="64"/>
-      <c r="C90" s="148" t="s">
+      <c r="C90" s="194" t="s">
         <v>48</v>
       </c>
-      <c r="D90" s="149"/>
-      <c r="E90" s="149"/>
-      <c r="F90" s="149"/>
-      <c r="G90" s="150"/>
+      <c r="D90" s="195"/>
+      <c r="E90" s="195"/>
+      <c r="F90" s="195"/>
+      <c r="G90" s="196"/>
       <c r="H90" s="34"/>
       <c r="I90" s="57"/>
       <c r="J90" s="61"/>
@@ -10423,37 +10423,30 @@
     </row>
   </sheetData>
   <mergeCells count="71">
-    <mergeCell ref="AC1:AD1"/>
-    <mergeCell ref="AE1:AG1"/>
-    <mergeCell ref="X2:Y2"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="H1:J1"/>
-    <mergeCell ref="L1:N1"/>
-    <mergeCell ref="Z1:AA1"/>
-    <mergeCell ref="Z2:AA2"/>
-    <mergeCell ref="AC2:AD2"/>
-    <mergeCell ref="AE2:AG2"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:H3"/>
-    <mergeCell ref="I3:M3"/>
-    <mergeCell ref="N3:N4"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="P2:T2"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="AK3:AK4"/>
-    <mergeCell ref="AL3:AL4"/>
-    <mergeCell ref="AM3:AM4"/>
-    <mergeCell ref="AO3:AO4"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="U3:AH3"/>
-    <mergeCell ref="AJ3:AJ4"/>
-    <mergeCell ref="O3:O4"/>
-    <mergeCell ref="P3:T3"/>
-    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="C88:G88"/>
+    <mergeCell ref="C90:G90"/>
+    <mergeCell ref="C74:G74"/>
+    <mergeCell ref="C76:G76"/>
+    <mergeCell ref="C78:G78"/>
+    <mergeCell ref="C80:G80"/>
+    <mergeCell ref="C82:G82"/>
+    <mergeCell ref="C84:G84"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="C86:G86"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="C68:G68"/>
+    <mergeCell ref="C70:G70"/>
+    <mergeCell ref="C54:G54"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="C72:G72"/>
+    <mergeCell ref="C62:G62"/>
+    <mergeCell ref="C64:G64"/>
+    <mergeCell ref="C66:G66"/>
+    <mergeCell ref="C58:G58"/>
     <mergeCell ref="C60:G60"/>
     <mergeCell ref="C14:G14"/>
     <mergeCell ref="C10:G10"/>
@@ -10470,30 +10463,37 @@
     <mergeCell ref="C32:G32"/>
     <mergeCell ref="C34:G34"/>
     <mergeCell ref="C36:G36"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="C86:G86"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="C68:G68"/>
-    <mergeCell ref="C70:G70"/>
-    <mergeCell ref="C54:G54"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="C72:G72"/>
-    <mergeCell ref="C62:G62"/>
-    <mergeCell ref="C64:G64"/>
-    <mergeCell ref="C66:G66"/>
-    <mergeCell ref="C58:G58"/>
-    <mergeCell ref="C88:G88"/>
-    <mergeCell ref="C90:G90"/>
-    <mergeCell ref="C74:G74"/>
-    <mergeCell ref="C76:G76"/>
-    <mergeCell ref="C78:G78"/>
-    <mergeCell ref="C80:G80"/>
-    <mergeCell ref="C82:G82"/>
-    <mergeCell ref="C84:G84"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="AK3:AK4"/>
+    <mergeCell ref="AL3:AL4"/>
+    <mergeCell ref="AM3:AM4"/>
+    <mergeCell ref="AO3:AO4"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="U3:AH3"/>
+    <mergeCell ref="AJ3:AJ4"/>
+    <mergeCell ref="O3:O4"/>
+    <mergeCell ref="P3:T3"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="P2:T2"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:H3"/>
+    <mergeCell ref="I3:M3"/>
+    <mergeCell ref="N3:N4"/>
+    <mergeCell ref="AC1:AD1"/>
+    <mergeCell ref="AE1:AG1"/>
+    <mergeCell ref="X2:Y2"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="L1:N1"/>
+    <mergeCell ref="Z1:AA1"/>
+    <mergeCell ref="Z2:AA2"/>
+    <mergeCell ref="AC2:AD2"/>
+    <mergeCell ref="AE2:AG2"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <printOptions horizontalCentered="1"/>

--- a/템플릿/LH간이종심100-300억_템플릿.xlsx
+++ b/템플릿/LH간이종심100-300억_템플릿.xlsx
@@ -2442,7 +2442,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="53">
   <si>
     <t>시공비율계산</t>
   </si>
@@ -2451,11 +2451,6 @@
   </si>
   <si>
     <t>구성원4</t>
-  </si>
-  <si>
-    <t>동가
-주의</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>추정가격</t>
@@ -3670,7 +3665,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="202">
+  <cellXfs count="174">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3833,9 +3828,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
@@ -3872,15 +3864,9 @@
     <xf numFmtId="176" fontId="7" fillId="0" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -3911,15 +3897,9 @@
     <xf numFmtId="181" fontId="10" fillId="0" borderId="43" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -3932,9 +3912,6 @@
     <xf numFmtId="176" fontId="7" fillId="0" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3947,21 +3924,12 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="176" fontId="7" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="7" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
@@ -3971,30 +3939,9 @@
     <xf numFmtId="10" fontId="7" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
@@ -4031,9 +3978,6 @@
     <xf numFmtId="0" fontId="21" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="176" fontId="7" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4052,18 +3996,6 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="10" fontId="7" fillId="0" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4073,36 +4005,9 @@
     <xf numFmtId="0" fontId="7" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="10" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="178" fontId="7" fillId="10" borderId="46" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -4115,6 +4020,114 @@
     <xf numFmtId="177" fontId="7" fillId="10" borderId="43" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="7" fillId="5" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="7" fillId="5" borderId="41" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="7" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="6" fillId="2" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4169,113 +4182,11 @@
     <xf numFmtId="180" fontId="9" fillId="2" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="7" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="22" fontId="6" fillId="2" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="7" fillId="5" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="7" fillId="5" borderId="41" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -4602,8 +4513,8 @@
   <dimension ref="A1:AO90"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.88671875" style="71" customWidth="1"/>
-    <col min="2" max="2" width="8.44140625" style="72" customWidth="1"/>
+    <col min="1" max="1" width="2.88671875" style="68" customWidth="1"/>
+    <col min="2" max="2" width="8.44140625" style="69" customWidth="1"/>
     <col min="3" max="3" width="8.88671875" style="17" customWidth="1"/>
     <col min="4" max="4" width="8.88671875" style="1" customWidth="1"/>
     <col min="5" max="6" width="10" style="1" customWidth="1"/>
@@ -4614,14 +4525,14 @@
     <col min="15" max="15" width="6.21875" style="1" customWidth="1"/>
     <col min="16" max="20" width="7.5546875" style="1" customWidth="1"/>
     <col min="21" max="21" width="9.33203125" style="1" customWidth="1"/>
-    <col min="22" max="22" width="7.44140625" style="70" customWidth="1"/>
+    <col min="22" max="22" width="7.44140625" style="67" customWidth="1"/>
     <col min="23" max="27" width="8.109375" style="1" customWidth="1"/>
     <col min="28" max="28" width="8.44140625" style="1" customWidth="1"/>
     <col min="29" max="29" width="8.77734375" style="1" customWidth="1"/>
     <col min="30" max="30" width="8.88671875" style="1" customWidth="1"/>
     <col min="31" max="31" width="7" style="1" customWidth="1"/>
     <col min="32" max="32" width="7.21875" style="1" customWidth="1"/>
-    <col min="33" max="33" width="7.6640625" style="76" customWidth="1"/>
+    <col min="33" max="33" width="7.6640625" style="73" customWidth="1"/>
     <col min="34" max="34" width="7.88671875" style="1" customWidth="1"/>
     <col min="35" max="35" width="7.5546875" style="1" customWidth="1"/>
     <col min="36" max="36" width="8.44140625" style="1" customWidth="1"/>
@@ -4634,34 +4545,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:41" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="118"/>
-      <c r="B1" s="119" t="s">
+      <c r="A1" s="102"/>
+      <c r="B1" s="103" t="s">
+        <v>48</v>
+      </c>
+      <c r="C1" s="103" t="s">
         <v>49</v>
       </c>
-      <c r="C1" s="119" t="s">
-        <v>50</v>
-      </c>
       <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="159"/>
+      <c r="F1" s="160"/>
+      <c r="G1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="153"/>
-      <c r="F1" s="154"/>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="161"/>
+      <c r="I1" s="162"/>
+      <c r="J1" s="163"/>
+      <c r="K1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="155"/>
-      <c r="I1" s="156"/>
-      <c r="J1" s="157"/>
-      <c r="K1" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="L1" s="155">
-        <v>0</v>
-      </c>
-      <c r="M1" s="156"/>
-      <c r="N1" s="158"/>
+      <c r="L1" s="161">
+        <v>0</v>
+      </c>
+      <c r="M1" s="162"/>
+      <c r="N1" s="164"/>
       <c r="O1" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="P1" s="6"/>
       <c r="Q1" s="6"/>
@@ -4673,20 +4584,20 @@
       <c r="W1" s="6"/>
       <c r="X1" s="6"/>
       <c r="Y1" s="6"/>
-      <c r="Z1" s="148" t="s">
+      <c r="Z1" s="154" t="s">
+        <v>6</v>
+      </c>
+      <c r="AA1" s="154"/>
+      <c r="AB1" s="7"/>
+      <c r="AC1" s="154" t="s">
         <v>7</v>
       </c>
-      <c r="AA1" s="148"/>
-      <c r="AB1" s="7"/>
-      <c r="AC1" s="148" t="s">
+      <c r="AD1" s="154"/>
+      <c r="AE1" s="155" t="s">
         <v>8</v>
       </c>
-      <c r="AD1" s="148"/>
-      <c r="AE1" s="149" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF1" s="150"/>
-      <c r="AG1" s="151"/>
+      <c r="AF1" s="156"/>
+      <c r="AG1" s="157"/>
       <c r="AH1" s="6"/>
       <c r="AI1" s="6"/>
       <c r="AJ1" s="6"/>
@@ -4697,214 +4608,214 @@
       <c r="AO1" s="8"/>
     </row>
     <row r="2" spans="1:41" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="175" t="s">
+      <c r="A2" s="139" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="139"/>
+      <c r="C2" s="140"/>
+      <c r="D2" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="175"/>
-      <c r="C2" s="176"/>
-      <c r="D2" s="9" t="s">
+      <c r="E2" s="141"/>
+      <c r="F2" s="142"/>
+      <c r="G2" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="177"/>
-      <c r="F2" s="178"/>
-      <c r="G2" s="10" t="s">
+      <c r="H2" s="141">
+        <f>E2</f>
+        <v>0</v>
+      </c>
+      <c r="I2" s="143"/>
+      <c r="J2" s="142"/>
+      <c r="K2" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="177">
-        <f>E2</f>
-        <v>0</v>
-      </c>
-      <c r="I2" s="179"/>
-      <c r="J2" s="178"/>
-      <c r="K2" s="11" t="s">
+      <c r="L2" s="144">
+        <f>H2*3</f>
+        <v>0</v>
+      </c>
+      <c r="M2" s="145"/>
+      <c r="N2" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="L2" s="180">
-        <f>H2*3</f>
-        <v>0</v>
-      </c>
-      <c r="M2" s="181"/>
-      <c r="N2" s="12" t="s">
+      <c r="O2" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="O2" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="P2" s="182" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q2" s="182"/>
-      <c r="R2" s="182"/>
-      <c r="S2" s="182"/>
-      <c r="T2" s="182"/>
-      <c r="U2" s="84" t="s">
-        <v>51</v>
+      <c r="P2" s="146" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q2" s="146"/>
+      <c r="R2" s="146"/>
+      <c r="S2" s="146"/>
+      <c r="T2" s="146"/>
+      <c r="U2" s="79" t="s">
+        <v>50</v>
       </c>
       <c r="V2" s="14"/>
       <c r="W2" s="15"/>
-      <c r="X2" s="152" t="s">
-        <v>0</v>
-      </c>
-      <c r="Y2" s="152"/>
-      <c r="Z2" s="159"/>
-      <c r="AA2" s="160"/>
-      <c r="AB2" s="83"/>
-      <c r="AC2" s="161">
+      <c r="X2" s="158" t="s">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="158"/>
+      <c r="Z2" s="165"/>
+      <c r="AA2" s="166"/>
+      <c r="AB2" s="78"/>
+      <c r="AC2" s="167">
         <f>H1</f>
         <v>0</v>
       </c>
-      <c r="AD2" s="162"/>
-      <c r="AE2" s="163" t="e">
+      <c r="AD2" s="168"/>
+      <c r="AE2" s="169" t="e">
         <f>Z2/AC2</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AF2" s="164"/>
-      <c r="AG2" s="165"/>
+      <c r="AF2" s="170"/>
+      <c r="AG2" s="171"/>
       <c r="AI2" s="16"/>
       <c r="AJ2" s="17"/>
       <c r="AK2" s="17"/>
       <c r="AL2" s="17"/>
       <c r="AM2" s="18"/>
       <c r="AN2" s="19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:41" s="22" customFormat="1" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="166" t="s">
+      <c r="A3" s="147" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="149" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="168" t="s">
+      <c r="C3" s="137" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="170" t="s">
+      <c r="D3" s="137"/>
+      <c r="E3" s="137"/>
+      <c r="F3" s="137"/>
+      <c r="G3" s="137"/>
+      <c r="H3" s="137"/>
+      <c r="I3" s="151" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="170"/>
-      <c r="E3" s="170"/>
-      <c r="F3" s="170"/>
-      <c r="G3" s="170"/>
-      <c r="H3" s="170"/>
-      <c r="I3" s="171" t="s">
+      <c r="J3" s="133"/>
+      <c r="K3" s="137"/>
+      <c r="L3" s="133"/>
+      <c r="M3" s="152"/>
+      <c r="N3" s="137" t="s">
         <v>20</v>
       </c>
-      <c r="J3" s="172"/>
-      <c r="K3" s="170"/>
-      <c r="L3" s="172"/>
-      <c r="M3" s="173"/>
-      <c r="N3" s="170" t="s">
+      <c r="O3" s="124"/>
+      <c r="P3" s="137" t="s">
         <v>21</v>
       </c>
-      <c r="O3" s="186"/>
-      <c r="P3" s="170" t="s">
+      <c r="Q3" s="137"/>
+      <c r="R3" s="137"/>
+      <c r="S3" s="137"/>
+      <c r="T3" s="138"/>
+      <c r="U3" s="132" t="s">
         <v>22</v>
       </c>
-      <c r="Q3" s="170"/>
-      <c r="R3" s="170"/>
-      <c r="S3" s="170"/>
-      <c r="T3" s="201"/>
-      <c r="U3" s="197" t="s">
+      <c r="V3" s="133"/>
+      <c r="W3" s="133"/>
+      <c r="X3" s="133"/>
+      <c r="Y3" s="133"/>
+      <c r="Z3" s="133"/>
+      <c r="AA3" s="133"/>
+      <c r="AB3" s="133"/>
+      <c r="AC3" s="133"/>
+      <c r="AD3" s="133"/>
+      <c r="AE3" s="133"/>
+      <c r="AF3" s="133"/>
+      <c r="AG3" s="133"/>
+      <c r="AH3" s="134"/>
+      <c r="AI3" s="26"/>
+      <c r="AJ3" s="135" t="s">
         <v>23</v>
       </c>
-      <c r="V3" s="172"/>
-      <c r="W3" s="172"/>
-      <c r="X3" s="172"/>
-      <c r="Y3" s="172"/>
-      <c r="Z3" s="172"/>
-      <c r="AA3" s="172"/>
-      <c r="AB3" s="172"/>
-      <c r="AC3" s="172"/>
-      <c r="AD3" s="172"/>
-      <c r="AE3" s="172"/>
-      <c r="AF3" s="172"/>
-      <c r="AG3" s="172"/>
-      <c r="AH3" s="198"/>
-      <c r="AI3" s="26"/>
-      <c r="AJ3" s="199" t="s">
+      <c r="AK3" s="124" t="s">
         <v>24</v>
       </c>
-      <c r="AK3" s="186" t="s">
+      <c r="AL3" s="126" t="s">
         <v>25</v>
       </c>
-      <c r="AL3" s="188" t="s">
+      <c r="AM3" s="128" t="s">
         <v>26</v>
       </c>
-      <c r="AM3" s="190" t="s">
+      <c r="AN3" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="AN3" s="21" t="s">
+      <c r="AO3" s="130" t="s">
         <v>28</v>
-      </c>
-      <c r="AO3" s="192" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:41" s="22" customFormat="1" ht="41.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="167"/>
-      <c r="B4" s="169"/>
+      <c r="A4" s="148"/>
+      <c r="B4" s="150"/>
       <c r="C4" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="D4" s="24" t="s">
+      <c r="E4" s="108" t="s">
         <v>31</v>
       </c>
-      <c r="E4" s="125" t="s">
+      <c r="F4" s="108" t="s">
         <v>32</v>
       </c>
-      <c r="F4" s="125" t="s">
+      <c r="G4" s="108" t="s">
         <v>33</v>
       </c>
-      <c r="G4" s="125" t="s">
+      <c r="H4" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="H4" s="25" t="s">
+      <c r="I4" s="109" t="s">
+        <v>29</v>
+      </c>
+      <c r="J4" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="I4" s="126" t="s">
-        <v>30</v>
-      </c>
-      <c r="J4" s="24" t="s">
-        <v>36</v>
-      </c>
       <c r="K4" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="L4" s="126" t="s">
+        <v>31</v>
+      </c>
+      <c r="L4" s="109" t="s">
         <v>1</v>
       </c>
       <c r="M4" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="N4" s="174"/>
-      <c r="O4" s="187"/>
+      <c r="N4" s="153"/>
+      <c r="O4" s="125"/>
       <c r="P4" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q4" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="R4" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="S4" s="109" t="s">
+        <v>1</v>
+      </c>
+      <c r="T4" s="108" t="s">
+        <v>2</v>
+      </c>
+      <c r="U4" s="92" t="s">
         <v>37</v>
       </c>
-      <c r="Q4" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="R4" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="S4" s="126" t="s">
-        <v>1</v>
-      </c>
-      <c r="T4" s="125" t="s">
-        <v>2</v>
-      </c>
-      <c r="U4" s="108" t="s">
+      <c r="V4" s="93" t="s">
         <v>38</v>
       </c>
-      <c r="V4" s="109" t="s">
-        <v>39</v>
-      </c>
       <c r="W4" s="27" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X4" s="28" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Y4" s="28" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="Z4" s="29" t="s">
         <v>1</v>
@@ -4913,62 +4824,60 @@
         <v>2</v>
       </c>
       <c r="AB4" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC4" s="94" t="s">
         <v>40</v>
       </c>
-      <c r="AC4" s="110" t="s">
+      <c r="AD4" s="93" t="s">
         <v>41</v>
       </c>
-      <c r="AD4" s="109" t="s">
+      <c r="AE4" s="95" t="s">
         <v>42</v>
       </c>
-      <c r="AE4" s="111" t="s">
+      <c r="AF4" s="96" t="s">
         <v>43</v>
       </c>
-      <c r="AF4" s="112" t="s">
+      <c r="AG4" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="AG4" s="113" t="s">
+      <c r="AH4" s="98" t="s">
         <v>45</v>
       </c>
-      <c r="AH4" s="114" t="s">
+      <c r="AI4" s="99" t="s">
         <v>46</v>
       </c>
-      <c r="AI4" s="115" t="s">
-        <v>47</v>
-      </c>
-      <c r="AJ4" s="200"/>
-      <c r="AK4" s="187"/>
-      <c r="AL4" s="189"/>
-      <c r="AM4" s="191"/>
+      <c r="AJ4" s="136"/>
+      <c r="AK4" s="125"/>
+      <c r="AL4" s="127"/>
+      <c r="AM4" s="129"/>
       <c r="AN4" s="31"/>
-      <c r="AO4" s="193"/>
+      <c r="AO4" s="131"/>
     </row>
     <row r="5" spans="1:41" s="22" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="90">
-        <v>1</v>
-      </c>
-      <c r="B5" s="132"/>
-      <c r="C5" s="135"/>
-      <c r="D5" s="134"/>
-      <c r="E5" s="135"/>
-      <c r="F5" s="135"/>
-      <c r="G5" s="136"/>
+      <c r="A5" s="84"/>
+      <c r="B5" s="111"/>
+      <c r="C5" s="173"/>
+      <c r="D5" s="172"/>
+      <c r="E5" s="173"/>
+      <c r="F5" s="173"/>
+      <c r="G5" s="113"/>
       <c r="H5" s="34"/>
       <c r="I5" s="35"/>
       <c r="J5" s="36"/>
       <c r="K5" s="36"/>
       <c r="L5" s="36"/>
-      <c r="M5" s="86"/>
-      <c r="N5" s="62">
+      <c r="M5" s="81"/>
+      <c r="N5" s="61">
         <f>SUM(I5:M5)</f>
         <v>0</v>
       </c>
       <c r="O5" s="37"/>
-      <c r="P5" s="144"/>
-      <c r="Q5" s="145"/>
-      <c r="R5" s="145"/>
-      <c r="S5" s="145"/>
-      <c r="T5" s="145"/>
+      <c r="P5" s="114"/>
+      <c r="Q5" s="115"/>
+      <c r="R5" s="115"/>
+      <c r="S5" s="115"/>
+      <c r="T5" s="115"/>
       <c r="U5" s="40">
         <f>ROUND(((P5*I5)+(Q5*J5)+(R5*K5)+(S5*L5)+(T5*M5)),3)</f>
         <v>0</v>
@@ -4982,26 +4891,26 @@
       <c r="Y5" s="42"/>
       <c r="Z5" s="42"/>
       <c r="AA5" s="42"/>
-      <c r="AB5" s="73" t="e">
+      <c r="AB5" s="70" t="e">
         <f>(((((W5*I5)+(X5*J5)+(Y5*K5)+(Z5*L5)+(AA5*M5))/$L$2)))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AC5" s="78" t="e">
+      <c r="AC5" s="75" t="e">
         <f t="shared" ref="AC5" si="0">ROUND(11*AB5,3)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD5" s="75" t="e">
+      <c r="AD5" s="72" t="e">
         <f t="shared" ref="AD5" si="1">IF(AC5&gt;=11,11,AC5)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE5" s="116">
+      <c r="AE5" s="100">
         <f>IF(U6&gt;=94,4,IF(U6&gt;=91,3.9,IF(U6&gt;=88,3.8,IF(U6&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF5" s="43">
         <v>0.3</v>
       </c>
-      <c r="AG5" s="117">
+      <c r="AG5" s="101">
         <v>17</v>
       </c>
       <c r="AH5" s="44" t="e">
@@ -5026,29 +4935,29 @@
       <c r="AO5" s="50"/>
     </row>
     <row r="6" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="91"/>
-      <c r="B6" s="133"/>
-      <c r="C6" s="194" t="s">
-        <v>48</v>
-      </c>
-      <c r="D6" s="195"/>
-      <c r="E6" s="195"/>
-      <c r="F6" s="195"/>
-      <c r="G6" s="196"/>
+      <c r="A6" s="85"/>
+      <c r="B6" s="112"/>
+      <c r="C6" s="118" t="s">
+        <v>47</v>
+      </c>
+      <c r="D6" s="119"/>
+      <c r="E6" s="119"/>
+      <c r="F6" s="119"/>
+      <c r="G6" s="120"/>
       <c r="H6" s="34"/>
-      <c r="I6" s="57"/>
-      <c r="J6" s="61"/>
-      <c r="K6" s="61"/>
-      <c r="L6" s="61"/>
-      <c r="M6" s="85"/>
-      <c r="N6" s="62"/>
+      <c r="I6" s="56"/>
+      <c r="J6" s="60"/>
+      <c r="K6" s="60"/>
+      <c r="L6" s="60"/>
+      <c r="M6" s="80"/>
+      <c r="N6" s="61"/>
       <c r="O6" s="37"/>
-      <c r="P6" s="146"/>
-      <c r="Q6" s="147"/>
-      <c r="R6" s="147"/>
-      <c r="S6" s="147"/>
-      <c r="T6" s="147"/>
-      <c r="U6" s="77">
+      <c r="P6" s="116"/>
+      <c r="Q6" s="117"/>
+      <c r="R6" s="117"/>
+      <c r="S6" s="117"/>
+      <c r="T6" s="117"/>
+      <c r="U6" s="74">
         <f>(I5*P6)+(J5*Q6)+(K5*R6)+(L5*S6)+(M5*T6)</f>
         <v>0</v>
       </c>
@@ -5058,12 +4967,12 @@
       <c r="Y6" s="42"/>
       <c r="Z6" s="42"/>
       <c r="AA6" s="42"/>
-      <c r="AB6" s="73"/>
-      <c r="AC6" s="78"/>
-      <c r="AD6" s="74"/>
-      <c r="AE6" s="116"/>
+      <c r="AB6" s="70"/>
+      <c r="AC6" s="75"/>
+      <c r="AD6" s="71"/>
+      <c r="AE6" s="100"/>
       <c r="AF6" s="43"/>
-      <c r="AG6" s="65"/>
+      <c r="AG6" s="64"/>
       <c r="AH6" s="44"/>
       <c r="AI6" s="41"/>
       <c r="AJ6" s="45"/>
@@ -5074,31 +4983,29 @@
       <c r="AO6" s="50"/>
     </row>
     <row r="7" spans="1:41" s="22" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="90">
-        <v>2</v>
-      </c>
-      <c r="B7" s="132"/>
-      <c r="C7" s="137"/>
-      <c r="D7" s="138"/>
-      <c r="E7" s="134"/>
-      <c r="F7" s="137"/>
-      <c r="G7" s="139"/>
+      <c r="A7" s="84"/>
+      <c r="B7" s="111"/>
+      <c r="C7" s="173"/>
+      <c r="D7" s="172"/>
+      <c r="E7" s="173"/>
+      <c r="F7" s="173"/>
+      <c r="G7" s="113"/>
       <c r="H7" s="34"/>
       <c r="I7" s="35"/>
       <c r="J7" s="36"/>
       <c r="K7" s="36"/>
       <c r="L7" s="36"/>
-      <c r="M7" s="86"/>
-      <c r="N7" s="62">
+      <c r="M7" s="81"/>
+      <c r="N7" s="61">
         <f>SUM(I7:M7)</f>
         <v>0</v>
       </c>
       <c r="O7" s="37"/>
-      <c r="P7" s="144"/>
-      <c r="Q7" s="145"/>
-      <c r="R7" s="145"/>
-      <c r="S7" s="145"/>
-      <c r="T7" s="145"/>
+      <c r="P7" s="114"/>
+      <c r="Q7" s="115"/>
+      <c r="R7" s="115"/>
+      <c r="S7" s="115"/>
+      <c r="T7" s="115"/>
       <c r="U7" s="40">
         <f>ROUND(((P7*I7)+(Q7*J7)+(R7*K7)+(S7*L7)+(T7*M7)),3)</f>
         <v>0</v>
@@ -5112,26 +5019,26 @@
       <c r="Y7" s="42"/>
       <c r="Z7" s="42"/>
       <c r="AA7" s="42"/>
-      <c r="AB7" s="73" t="e">
+      <c r="AB7" s="70" t="e">
         <f>(((((W7*I7)+(X7*J7)+(Y7*K7)+(Z7*L7)+(AA7*M7))/$L$2)))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AC7" s="78" t="e">
+      <c r="AC7" s="75" t="e">
         <f>ROUND(11*AB7,3)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD7" s="75" t="e">
+      <c r="AD7" s="72" t="e">
         <f>IF(AC7&gt;=11,11,AC7)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE7" s="116">
+      <c r="AE7" s="100">
         <f>IF(U8&gt;=94,4,IF(U8&gt;=91,3.9,IF(U8&gt;=88,3.8,IF(U8&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF7" s="43">
         <v>0.1</v>
       </c>
-      <c r="AG7" s="117">
+      <c r="AG7" s="101">
         <v>17</v>
       </c>
       <c r="AH7" s="44" t="e">
@@ -5156,29 +5063,29 @@
       <c r="AO7" s="50"/>
     </row>
     <row r="8" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="91"/>
-      <c r="B8" s="132"/>
-      <c r="C8" s="194" t="s">
-        <v>48</v>
-      </c>
-      <c r="D8" s="195"/>
-      <c r="E8" s="195"/>
-      <c r="F8" s="195"/>
-      <c r="G8" s="196"/>
+      <c r="A8" s="85"/>
+      <c r="B8" s="111"/>
+      <c r="C8" s="118" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" s="119"/>
+      <c r="E8" s="119"/>
+      <c r="F8" s="119"/>
+      <c r="G8" s="120"/>
       <c r="H8" s="34"/>
-      <c r="I8" s="57"/>
-      <c r="J8" s="61"/>
-      <c r="K8" s="61"/>
-      <c r="L8" s="61"/>
-      <c r="M8" s="85"/>
-      <c r="N8" s="62"/>
+      <c r="I8" s="56"/>
+      <c r="J8" s="60"/>
+      <c r="K8" s="60"/>
+      <c r="L8" s="60"/>
+      <c r="M8" s="80"/>
+      <c r="N8" s="61"/>
       <c r="O8" s="37"/>
-      <c r="P8" s="146"/>
-      <c r="Q8" s="147"/>
-      <c r="R8" s="147"/>
-      <c r="S8" s="147"/>
-      <c r="T8" s="147"/>
-      <c r="U8" s="77">
+      <c r="P8" s="116"/>
+      <c r="Q8" s="117"/>
+      <c r="R8" s="117"/>
+      <c r="S8" s="117"/>
+      <c r="T8" s="117"/>
+      <c r="U8" s="74">
         <f>(I7*P8)+(J7*Q8)+(K7*R8)+(L7*S8)+(M7*T8)</f>
         <v>0</v>
       </c>
@@ -5188,12 +5095,12 @@
       <c r="Y8" s="42"/>
       <c r="Z8" s="42"/>
       <c r="AA8" s="42"/>
-      <c r="AB8" s="73"/>
-      <c r="AC8" s="78"/>
-      <c r="AD8" s="74"/>
-      <c r="AE8" s="116"/>
+      <c r="AB8" s="70"/>
+      <c r="AC8" s="75"/>
+      <c r="AD8" s="71"/>
+      <c r="AE8" s="100"/>
       <c r="AF8" s="43"/>
-      <c r="AG8" s="65"/>
+      <c r="AG8" s="64"/>
       <c r="AH8" s="44"/>
       <c r="AI8" s="41"/>
       <c r="AJ8" s="45"/>
@@ -5204,31 +5111,29 @@
       <c r="AO8" s="50"/>
     </row>
     <row r="9" spans="1:41" s="22" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="90">
-        <v>3</v>
-      </c>
-      <c r="B9" s="132"/>
-      <c r="C9" s="134"/>
-      <c r="D9" s="134"/>
-      <c r="E9" s="140"/>
-      <c r="F9" s="134"/>
-      <c r="G9" s="139"/>
+      <c r="A9" s="84"/>
+      <c r="B9" s="111"/>
+      <c r="C9" s="173"/>
+      <c r="D9" s="172"/>
+      <c r="E9" s="173"/>
+      <c r="F9" s="173"/>
+      <c r="G9" s="113"/>
       <c r="H9" s="34"/>
       <c r="I9" s="35"/>
-      <c r="J9" s="61"/>
-      <c r="K9" s="61"/>
+      <c r="J9" s="60"/>
+      <c r="K9" s="60"/>
       <c r="L9" s="36"/>
-      <c r="M9" s="86"/>
-      <c r="N9" s="62">
+      <c r="M9" s="81"/>
+      <c r="N9" s="61">
         <f>SUM(I9:M9)</f>
         <v>0</v>
       </c>
       <c r="O9" s="37"/>
-      <c r="P9" s="144"/>
-      <c r="Q9" s="145"/>
-      <c r="R9" s="145"/>
-      <c r="S9" s="145"/>
-      <c r="T9" s="145"/>
+      <c r="P9" s="114"/>
+      <c r="Q9" s="115"/>
+      <c r="R9" s="115"/>
+      <c r="S9" s="115"/>
+      <c r="T9" s="115"/>
       <c r="U9" s="40">
         <f>ROUND(((P9*I9)+(Q9*J9)+(R9*K9)+(S9*L9)+(T9*M9)),3)</f>
         <v>0</v>
@@ -5242,26 +5147,26 @@
       <c r="Y9" s="42"/>
       <c r="Z9" s="42"/>
       <c r="AA9" s="42"/>
-      <c r="AB9" s="73" t="e">
+      <c r="AB9" s="70" t="e">
         <f>(((((W9*I9)+(X9*J9)+(Y9*K9)+(Z9*L9)+(AA9*M9))/$L$2)))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AC9" s="78" t="e">
+      <c r="AC9" s="75" t="e">
         <f t="shared" ref="AC9" si="2">ROUND(11*AB9,3)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD9" s="75" t="e">
+      <c r="AD9" s="72" t="e">
         <f t="shared" ref="AD9" si="3">IF(AC9&gt;=11,11,AC9)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE9" s="116">
+      <c r="AE9" s="100">
         <f>IF(U10&gt;=94,4,IF(U10&gt;=91,3.9,IF(U10&gt;=88,3.8,IF(U10&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF9" s="43">
         <v>0.3</v>
       </c>
-      <c r="AG9" s="117">
+      <c r="AG9" s="101">
         <v>17</v>
       </c>
       <c r="AH9" s="44" t="e">
@@ -5286,29 +5191,29 @@
       <c r="AO9" s="50"/>
     </row>
     <row r="10" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="91"/>
-      <c r="B10" s="133"/>
-      <c r="C10" s="194" t="s">
-        <v>48</v>
-      </c>
-      <c r="D10" s="195"/>
-      <c r="E10" s="195"/>
-      <c r="F10" s="195"/>
-      <c r="G10" s="196"/>
+      <c r="A10" s="85"/>
+      <c r="B10" s="112"/>
+      <c r="C10" s="118" t="s">
+        <v>47</v>
+      </c>
+      <c r="D10" s="119"/>
+      <c r="E10" s="119"/>
+      <c r="F10" s="119"/>
+      <c r="G10" s="120"/>
       <c r="H10" s="34"/>
-      <c r="I10" s="57"/>
-      <c r="J10" s="61"/>
-      <c r="K10" s="61"/>
-      <c r="L10" s="61"/>
-      <c r="M10" s="85"/>
-      <c r="N10" s="62"/>
+      <c r="I10" s="56"/>
+      <c r="J10" s="60"/>
+      <c r="K10" s="60"/>
+      <c r="L10" s="60"/>
+      <c r="M10" s="80"/>
+      <c r="N10" s="61"/>
       <c r="O10" s="37"/>
-      <c r="P10" s="146"/>
-      <c r="Q10" s="147"/>
-      <c r="R10" s="147"/>
-      <c r="S10" s="147"/>
-      <c r="T10" s="147"/>
-      <c r="U10" s="77">
+      <c r="P10" s="116"/>
+      <c r="Q10" s="117"/>
+      <c r="R10" s="117"/>
+      <c r="S10" s="117"/>
+      <c r="T10" s="117"/>
+      <c r="U10" s="74">
         <f>(I9*P10)+(J9*Q10)+(K9*R10)+(L9*S10)+(M9*T10)</f>
         <v>0</v>
       </c>
@@ -5318,12 +5223,12 @@
       <c r="Y10" s="42"/>
       <c r="Z10" s="42"/>
       <c r="AA10" s="42"/>
-      <c r="AB10" s="73"/>
-      <c r="AC10" s="78"/>
-      <c r="AD10" s="74"/>
-      <c r="AE10" s="116"/>
+      <c r="AB10" s="70"/>
+      <c r="AC10" s="75"/>
+      <c r="AD10" s="71"/>
+      <c r="AE10" s="100"/>
       <c r="AF10" s="43"/>
-      <c r="AG10" s="65"/>
+      <c r="AG10" s="64"/>
       <c r="AH10" s="44"/>
       <c r="AI10" s="41"/>
       <c r="AJ10" s="45"/>
@@ -5334,31 +5239,29 @@
       <c r="AO10" s="50"/>
     </row>
     <row r="11" spans="1:41" s="22" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="90">
-        <v>4</v>
-      </c>
-      <c r="B11" s="132"/>
-      <c r="C11" s="141"/>
-      <c r="D11" s="134"/>
-      <c r="E11" s="138"/>
-      <c r="F11" s="134"/>
-      <c r="G11" s="142"/>
+      <c r="A11" s="84"/>
+      <c r="B11" s="111"/>
+      <c r="C11" s="173"/>
+      <c r="D11" s="172"/>
+      <c r="E11" s="173"/>
+      <c r="F11" s="173"/>
+      <c r="G11" s="113"/>
       <c r="H11" s="34"/>
       <c r="I11" s="35"/>
       <c r="J11" s="36"/>
       <c r="K11" s="36"/>
       <c r="L11" s="36"/>
-      <c r="M11" s="86"/>
-      <c r="N11" s="62">
+      <c r="M11" s="81"/>
+      <c r="N11" s="61">
         <f>SUM(I11:M11)</f>
         <v>0</v>
       </c>
       <c r="O11" s="37"/>
-      <c r="P11" s="144"/>
-      <c r="Q11" s="145"/>
-      <c r="R11" s="145"/>
-      <c r="S11" s="145"/>
-      <c r="T11" s="145"/>
+      <c r="P11" s="114"/>
+      <c r="Q11" s="115"/>
+      <c r="R11" s="115"/>
+      <c r="S11" s="115"/>
+      <c r="T11" s="115"/>
       <c r="U11" s="40">
         <f>ROUND(((P11*I11)+(Q11*J11)+(R11*K11)+(S11*L11)+(T11*M11)),3)</f>
         <v>0</v>
@@ -5372,26 +5275,26 @@
       <c r="Y11" s="42"/>
       <c r="Z11" s="42"/>
       <c r="AA11" s="42"/>
-      <c r="AB11" s="73" t="e">
+      <c r="AB11" s="70" t="e">
         <f>(((((W11*I11)+(X11*J11)+(Y11*K11)+(Z11*L11)+(AA11*M11))/$L$2)))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AC11" s="78" t="e">
+      <c r="AC11" s="75" t="e">
         <f t="shared" ref="AC11" si="4">ROUND(11*AB11,3)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD11" s="75" t="e">
+      <c r="AD11" s="72" t="e">
         <f t="shared" ref="AD11" si="5">IF(AC11&gt;=11,11,AC11)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE11" s="116">
+      <c r="AE11" s="100">
         <f>IF(U12&gt;=94,4,IF(U12&gt;=91,3.9,IF(U12&gt;=88,3.8,IF(U12&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF11" s="43">
         <v>0.3</v>
       </c>
-      <c r="AG11" s="117">
+      <c r="AG11" s="101">
         <v>17</v>
       </c>
       <c r="AH11" s="44" t="e">
@@ -5416,29 +5319,29 @@
       <c r="AO11" s="50"/>
     </row>
     <row r="12" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="91"/>
-      <c r="B12" s="133"/>
-      <c r="C12" s="194" t="s">
-        <v>48</v>
-      </c>
-      <c r="D12" s="195"/>
-      <c r="E12" s="195"/>
-      <c r="F12" s="195"/>
-      <c r="G12" s="196"/>
+      <c r="A12" s="85"/>
+      <c r="B12" s="112"/>
+      <c r="C12" s="118" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" s="119"/>
+      <c r="E12" s="119"/>
+      <c r="F12" s="119"/>
+      <c r="G12" s="120"/>
       <c r="H12" s="34"/>
-      <c r="I12" s="57"/>
-      <c r="J12" s="61"/>
-      <c r="K12" s="61"/>
-      <c r="L12" s="61"/>
-      <c r="M12" s="85"/>
-      <c r="N12" s="62"/>
+      <c r="I12" s="56"/>
+      <c r="J12" s="60"/>
+      <c r="K12" s="60"/>
+      <c r="L12" s="60"/>
+      <c r="M12" s="80"/>
+      <c r="N12" s="61"/>
       <c r="O12" s="37"/>
-      <c r="P12" s="146"/>
-      <c r="Q12" s="147"/>
-      <c r="R12" s="147"/>
-      <c r="S12" s="147"/>
-      <c r="T12" s="147"/>
-      <c r="U12" s="77">
+      <c r="P12" s="116"/>
+      <c r="Q12" s="117"/>
+      <c r="R12" s="117"/>
+      <c r="S12" s="117"/>
+      <c r="T12" s="117"/>
+      <c r="U12" s="74">
         <f>(I11*P12)+(J11*Q12)+(K11*R12)+(L11*S12)+(M11*T12)</f>
         <v>0</v>
       </c>
@@ -5448,12 +5351,12 @@
       <c r="Y12" s="42"/>
       <c r="Z12" s="42"/>
       <c r="AA12" s="42"/>
-      <c r="AB12" s="73"/>
-      <c r="AC12" s="78"/>
-      <c r="AD12" s="74"/>
-      <c r="AE12" s="116"/>
+      <c r="AB12" s="70"/>
+      <c r="AC12" s="75"/>
+      <c r="AD12" s="71"/>
+      <c r="AE12" s="100"/>
       <c r="AF12" s="43"/>
-      <c r="AG12" s="65"/>
+      <c r="AG12" s="64"/>
       <c r="AH12" s="44"/>
       <c r="AI12" s="41"/>
       <c r="AJ12" s="45"/>
@@ -5464,31 +5367,29 @@
       <c r="AO12" s="50"/>
     </row>
     <row r="13" spans="1:41" s="22" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="90">
-        <v>5</v>
-      </c>
-      <c r="B13" s="132"/>
-      <c r="C13" s="143"/>
-      <c r="D13" s="138"/>
-      <c r="E13" s="134"/>
-      <c r="F13" s="138"/>
-      <c r="G13" s="139"/>
+      <c r="A13" s="84"/>
+      <c r="B13" s="111"/>
+      <c r="C13" s="173"/>
+      <c r="D13" s="172"/>
+      <c r="E13" s="173"/>
+      <c r="F13" s="173"/>
+      <c r="G13" s="113"/>
       <c r="H13" s="34"/>
       <c r="I13" s="35"/>
       <c r="J13" s="36"/>
       <c r="K13" s="36"/>
       <c r="L13" s="36"/>
-      <c r="M13" s="86"/>
-      <c r="N13" s="62">
+      <c r="M13" s="81"/>
+      <c r="N13" s="61">
         <f>SUM(I13:M13)</f>
         <v>0</v>
       </c>
       <c r="O13" s="37"/>
-      <c r="P13" s="144"/>
-      <c r="Q13" s="145"/>
-      <c r="R13" s="145"/>
-      <c r="S13" s="145"/>
-      <c r="T13" s="145"/>
+      <c r="P13" s="114"/>
+      <c r="Q13" s="115"/>
+      <c r="R13" s="115"/>
+      <c r="S13" s="115"/>
+      <c r="T13" s="115"/>
       <c r="U13" s="40">
         <f>ROUND(((P13*I13)+(Q13*J13)+(R13*K13)+(S13*L13)+(T13*M13)),3)</f>
         <v>0</v>
@@ -5502,26 +5403,26 @@
       <c r="Y13" s="42"/>
       <c r="Z13" s="51"/>
       <c r="AA13" s="42"/>
-      <c r="AB13" s="73" t="e">
+      <c r="AB13" s="70" t="e">
         <f>(((((W13*I13)+(X13*J13)+(Y13*K13)+(Z13*L13)+(AA13*M13))/$L$2)))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AC13" s="78" t="e">
+      <c r="AC13" s="75" t="e">
         <f>ROUND(11*AB13,3)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD13" s="75" t="e">
+      <c r="AD13" s="72" t="e">
         <f>IF(AC13&gt;=11,11,AC13)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE13" s="116">
+      <c r="AE13" s="100">
         <f>IF(U14&gt;=94,4,IF(U14&gt;=91,3.9,IF(U14&gt;=88,3.8,IF(U14&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF13" s="43">
         <v>0.2</v>
       </c>
-      <c r="AG13" s="117">
+      <c r="AG13" s="101">
         <v>17</v>
       </c>
       <c r="AH13" s="44" t="e">
@@ -5546,29 +5447,29 @@
       <c r="AO13" s="50"/>
     </row>
     <row r="14" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="91"/>
-      <c r="B14" s="89"/>
-      <c r="C14" s="194" t="s">
-        <v>48</v>
-      </c>
-      <c r="D14" s="195"/>
-      <c r="E14" s="195"/>
-      <c r="F14" s="195"/>
-      <c r="G14" s="196"/>
+      <c r="A14" s="85"/>
+      <c r="B14" s="83"/>
+      <c r="C14" s="118" t="s">
+        <v>47</v>
+      </c>
+      <c r="D14" s="119"/>
+      <c r="E14" s="119"/>
+      <c r="F14" s="119"/>
+      <c r="G14" s="120"/>
       <c r="H14" s="34"/>
-      <c r="I14" s="57"/>
-      <c r="J14" s="61"/>
-      <c r="K14" s="61"/>
-      <c r="L14" s="61"/>
-      <c r="M14" s="85"/>
-      <c r="N14" s="62"/>
+      <c r="I14" s="56"/>
+      <c r="J14" s="60"/>
+      <c r="K14" s="60"/>
+      <c r="L14" s="60"/>
+      <c r="M14" s="80"/>
+      <c r="N14" s="61"/>
       <c r="O14" s="37"/>
-      <c r="P14" s="145"/>
-      <c r="Q14" s="145"/>
-      <c r="R14" s="145"/>
-      <c r="S14" s="145"/>
-      <c r="T14" s="147"/>
-      <c r="U14" s="77">
+      <c r="P14" s="115"/>
+      <c r="Q14" s="115"/>
+      <c r="R14" s="115"/>
+      <c r="S14" s="115"/>
+      <c r="T14" s="117"/>
+      <c r="U14" s="74">
         <f>(I13*P14)+(J13*Q14)+(K13*R14)+(L13*S14)+(M13*T14)</f>
         <v>0</v>
       </c>
@@ -5578,12 +5479,12 @@
       <c r="Y14" s="42"/>
       <c r="Z14" s="42"/>
       <c r="AA14" s="42"/>
-      <c r="AB14" s="73"/>
-      <c r="AC14" s="78"/>
-      <c r="AD14" s="74"/>
-      <c r="AE14" s="116"/>
+      <c r="AB14" s="70"/>
+      <c r="AC14" s="75"/>
+      <c r="AD14" s="71"/>
+      <c r="AE14" s="100"/>
       <c r="AF14" s="43"/>
-      <c r="AG14" s="65"/>
+      <c r="AG14" s="64"/>
       <c r="AH14" s="44"/>
       <c r="AI14" s="41"/>
       <c r="AJ14" s="45"/>
@@ -5594,29 +5495,29 @@
       <c r="AO14" s="50"/>
     </row>
     <row r="15" spans="1:41" s="22" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="90"/>
-      <c r="B15" s="88"/>
-      <c r="C15" s="135"/>
-      <c r="D15" s="135"/>
-      <c r="E15" s="137"/>
-      <c r="F15" s="138"/>
-      <c r="G15" s="139"/>
+      <c r="A15" s="84"/>
+      <c r="B15" s="82"/>
+      <c r="C15" s="173"/>
+      <c r="D15" s="172"/>
+      <c r="E15" s="173"/>
+      <c r="F15" s="173"/>
+      <c r="G15" s="113"/>
       <c r="H15" s="34"/>
       <c r="I15" s="35"/>
       <c r="J15" s="36"/>
       <c r="K15" s="36"/>
       <c r="L15" s="36"/>
-      <c r="M15" s="86"/>
-      <c r="N15" s="62">
+      <c r="M15" s="81"/>
+      <c r="N15" s="61">
         <f>SUM(I15:M15)</f>
         <v>0</v>
       </c>
       <c r="O15" s="37"/>
-      <c r="P15" s="144"/>
-      <c r="Q15" s="145"/>
-      <c r="R15" s="145"/>
-      <c r="S15" s="145"/>
-      <c r="T15" s="145"/>
+      <c r="P15" s="114"/>
+      <c r="Q15" s="115"/>
+      <c r="R15" s="115"/>
+      <c r="S15" s="115"/>
+      <c r="T15" s="115"/>
       <c r="U15" s="40">
         <f>ROUND(((P15*I15)+(Q15*J15)+(R15*K15)+(S15*L15)+(T15*M15)),3)</f>
         <v>0</v>
@@ -5630,26 +5531,26 @@
       <c r="Y15" s="42"/>
       <c r="Z15" s="42"/>
       <c r="AA15" s="42"/>
-      <c r="AB15" s="73" t="e">
+      <c r="AB15" s="70" t="e">
         <f>(((((W15*I15)+(X15*J15)+(Y15*K15)+(Z15*L15)+(AA15*M15))/$L$2)))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AC15" s="78" t="e">
+      <c r="AC15" s="75" t="e">
         <f t="shared" ref="AC15" si="6">ROUND(11*AB15,3)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD15" s="75" t="e">
+      <c r="AD15" s="72" t="e">
         <f t="shared" ref="AD15" si="7">IF(AC15&gt;=11,11,AC15)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE15" s="116">
+      <c r="AE15" s="100">
         <f>IF(U16&gt;=94,4,IF(U16&gt;=91,3.9,IF(U16&gt;=88,3.8,IF(U16&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF15" s="43">
         <v>0.3</v>
       </c>
-      <c r="AG15" s="117">
+      <c r="AG15" s="101">
         <v>17</v>
       </c>
       <c r="AH15" s="44" t="e">
@@ -5674,29 +5575,29 @@
       <c r="AO15" s="50"/>
     </row>
     <row r="16" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="91"/>
-      <c r="B16" s="89"/>
-      <c r="C16" s="194" t="s">
-        <v>48</v>
-      </c>
-      <c r="D16" s="195"/>
-      <c r="E16" s="195"/>
-      <c r="F16" s="195"/>
-      <c r="G16" s="196"/>
+      <c r="A16" s="85"/>
+      <c r="B16" s="83"/>
+      <c r="C16" s="118" t="s">
+        <v>47</v>
+      </c>
+      <c r="D16" s="119"/>
+      <c r="E16" s="119"/>
+      <c r="F16" s="119"/>
+      <c r="G16" s="120"/>
       <c r="H16" s="34"/>
-      <c r="I16" s="57"/>
-      <c r="J16" s="61"/>
-      <c r="K16" s="61"/>
-      <c r="L16" s="61"/>
-      <c r="M16" s="85"/>
-      <c r="N16" s="62"/>
+      <c r="I16" s="56"/>
+      <c r="J16" s="60"/>
+      <c r="K16" s="60"/>
+      <c r="L16" s="60"/>
+      <c r="M16" s="80"/>
+      <c r="N16" s="61"/>
       <c r="O16" s="37"/>
-      <c r="P16" s="146"/>
-      <c r="Q16" s="147"/>
-      <c r="R16" s="147"/>
-      <c r="S16" s="147"/>
-      <c r="T16" s="147"/>
-      <c r="U16" s="77">
+      <c r="P16" s="116"/>
+      <c r="Q16" s="117"/>
+      <c r="R16" s="117"/>
+      <c r="S16" s="117"/>
+      <c r="T16" s="117"/>
+      <c r="U16" s="74">
         <f>(I15*P16)+(J15*Q16)+(K15*R16)+(L15*S16)+(M15*T16)</f>
         <v>0</v>
       </c>
@@ -5706,12 +5607,12 @@
       <c r="Y16" s="42"/>
       <c r="Z16" s="42"/>
       <c r="AA16" s="42"/>
-      <c r="AB16" s="73"/>
-      <c r="AC16" s="78"/>
-      <c r="AD16" s="74"/>
-      <c r="AE16" s="116"/>
+      <c r="AB16" s="70"/>
+      <c r="AC16" s="75"/>
+      <c r="AD16" s="71"/>
+      <c r="AE16" s="100"/>
       <c r="AF16" s="43"/>
-      <c r="AG16" s="65"/>
+      <c r="AG16" s="64"/>
       <c r="AH16" s="44"/>
       <c r="AI16" s="41"/>
       <c r="AJ16" s="45"/>
@@ -5722,29 +5623,29 @@
       <c r="AO16" s="50"/>
     </row>
     <row r="17" spans="1:41" s="22" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="90"/>
-      <c r="B17" s="88"/>
-      <c r="C17" s="137"/>
-      <c r="D17" s="138"/>
-      <c r="E17" s="137"/>
-      <c r="F17" s="135"/>
-      <c r="G17" s="136"/>
-      <c r="H17" s="58"/>
+      <c r="A17" s="84"/>
+      <c r="B17" s="82"/>
+      <c r="C17" s="173"/>
+      <c r="D17" s="172"/>
+      <c r="E17" s="173"/>
+      <c r="F17" s="173"/>
+      <c r="G17" s="113"/>
+      <c r="H17" s="57"/>
       <c r="I17" s="35"/>
       <c r="J17" s="36"/>
       <c r="K17" s="36"/>
       <c r="L17" s="36"/>
-      <c r="M17" s="86"/>
-      <c r="N17" s="62">
+      <c r="M17" s="81"/>
+      <c r="N17" s="61">
         <f>SUM(I17:M17)</f>
         <v>0</v>
       </c>
       <c r="O17" s="37"/>
-      <c r="P17" s="144"/>
-      <c r="Q17" s="145"/>
-      <c r="R17" s="145"/>
-      <c r="S17" s="145"/>
-      <c r="T17" s="145"/>
+      <c r="P17" s="114"/>
+      <c r="Q17" s="115"/>
+      <c r="R17" s="115"/>
+      <c r="S17" s="115"/>
+      <c r="T17" s="115"/>
       <c r="U17" s="40">
         <f>ROUND(((P17*I17)+(Q17*J17)+(R17*K17)+(S17*L17)+(T17*M17)),3)</f>
         <v>0</v>
@@ -5758,26 +5659,26 @@
       <c r="Y17" s="42"/>
       <c r="Z17" s="42"/>
       <c r="AA17" s="42"/>
-      <c r="AB17" s="73" t="e">
+      <c r="AB17" s="70" t="e">
         <f>(((((W17*I17)+(X17*J17)+(Y17*K17)+(Z17*L17)+(AA17*M17))/$L$2)))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AC17" s="78" t="e">
+      <c r="AC17" s="75" t="e">
         <f t="shared" ref="AC17" si="8">ROUND(11*AB17,3)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD17" s="75" t="e">
+      <c r="AD17" s="72" t="e">
         <f t="shared" ref="AD17" si="9">IF(AC17&gt;=11,11,AC17)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE17" s="116">
+      <c r="AE17" s="100">
         <f>IF(U18&gt;=94,4,IF(U18&gt;=91,3.9,IF(U18&gt;=88,3.8,IF(U18&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF17" s="43">
         <v>0.3</v>
       </c>
-      <c r="AG17" s="117">
+      <c r="AG17" s="101">
         <v>17</v>
       </c>
       <c r="AH17" s="44" t="e">
@@ -5802,29 +5703,29 @@
       <c r="AO17" s="50"/>
     </row>
     <row r="18" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="91"/>
-      <c r="B18" s="89"/>
-      <c r="C18" s="194" t="s">
-        <v>48</v>
-      </c>
-      <c r="D18" s="195"/>
-      <c r="E18" s="195"/>
-      <c r="F18" s="195"/>
-      <c r="G18" s="196"/>
+      <c r="A18" s="85"/>
+      <c r="B18" s="83"/>
+      <c r="C18" s="118" t="s">
+        <v>47</v>
+      </c>
+      <c r="D18" s="119"/>
+      <c r="E18" s="119"/>
+      <c r="F18" s="119"/>
+      <c r="G18" s="120"/>
       <c r="H18" s="34"/>
-      <c r="I18" s="57"/>
-      <c r="J18" s="61"/>
-      <c r="K18" s="61"/>
-      <c r="L18" s="61"/>
-      <c r="M18" s="85"/>
-      <c r="N18" s="62"/>
+      <c r="I18" s="56"/>
+      <c r="J18" s="60"/>
+      <c r="K18" s="60"/>
+      <c r="L18" s="60"/>
+      <c r="M18" s="80"/>
+      <c r="N18" s="61"/>
       <c r="O18" s="37"/>
-      <c r="P18" s="145"/>
-      <c r="Q18" s="145"/>
-      <c r="R18" s="146"/>
-      <c r="S18" s="147"/>
-      <c r="T18" s="147"/>
-      <c r="U18" s="77">
+      <c r="P18" s="115"/>
+      <c r="Q18" s="115"/>
+      <c r="R18" s="116"/>
+      <c r="S18" s="117"/>
+      <c r="T18" s="117"/>
+      <c r="U18" s="74">
         <f>(I17*P18)+(J17*Q18)+(K17*R18)+(L17*S18)+(M17*T18)</f>
         <v>0</v>
       </c>
@@ -5834,12 +5735,12 @@
       <c r="Y18" s="42"/>
       <c r="Z18" s="42"/>
       <c r="AA18" s="42"/>
-      <c r="AB18" s="73"/>
-      <c r="AC18" s="78"/>
-      <c r="AD18" s="74"/>
-      <c r="AE18" s="116"/>
+      <c r="AB18" s="70"/>
+      <c r="AC18" s="75"/>
+      <c r="AD18" s="71"/>
+      <c r="AE18" s="100"/>
       <c r="AF18" s="43"/>
-      <c r="AG18" s="65"/>
+      <c r="AG18" s="64"/>
       <c r="AH18" s="44"/>
       <c r="AI18" s="41"/>
       <c r="AJ18" s="45"/>
@@ -5850,29 +5751,29 @@
       <c r="AO18" s="50"/>
     </row>
     <row r="19" spans="1:41" s="22" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="90"/>
-      <c r="B19" s="88"/>
-      <c r="C19" s="92"/>
-      <c r="D19" s="102"/>
-      <c r="E19" s="100"/>
-      <c r="F19" s="96"/>
-      <c r="G19" s="107"/>
+      <c r="A19" s="84"/>
+      <c r="B19" s="82"/>
+      <c r="C19" s="173"/>
+      <c r="D19" s="172"/>
+      <c r="E19" s="173"/>
+      <c r="F19" s="173"/>
+      <c r="G19" s="113"/>
       <c r="H19" s="34"/>
       <c r="I19" s="35"/>
       <c r="J19" s="36"/>
       <c r="K19" s="36"/>
       <c r="L19" s="36"/>
-      <c r="M19" s="86"/>
-      <c r="N19" s="62">
+      <c r="M19" s="81"/>
+      <c r="N19" s="61">
         <f>SUM(I19:M19)</f>
         <v>0</v>
       </c>
       <c r="O19" s="37"/>
-      <c r="P19" s="144"/>
-      <c r="Q19" s="145"/>
-      <c r="R19" s="145"/>
-      <c r="S19" s="145"/>
-      <c r="T19" s="145"/>
+      <c r="P19" s="114"/>
+      <c r="Q19" s="115"/>
+      <c r="R19" s="115"/>
+      <c r="S19" s="115"/>
+      <c r="T19" s="115"/>
       <c r="U19" s="40">
         <f>ROUND(((P19*I19)+(Q19*J19)+(R19*K19)+(S19*L19)+(T19*M19)),3)</f>
         <v>0</v>
@@ -5886,26 +5787,26 @@
       <c r="Y19" s="42"/>
       <c r="Z19" s="51"/>
       <c r="AA19" s="42"/>
-      <c r="AB19" s="73" t="e">
+      <c r="AB19" s="70" t="e">
         <f>(((((W19*I19)+(X19*J19)+(Y19*K19)+(Z19*L19)+(AA19*M19))/$L$2)))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AC19" s="78" t="e">
+      <c r="AC19" s="75" t="e">
         <f>ROUND(11*AB19,3)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD19" s="75" t="e">
+      <c r="AD19" s="72" t="e">
         <f t="shared" ref="AD19" si="10">IF(AC19&gt;=11,11,AC19)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE19" s="116">
+      <c r="AE19" s="100">
         <f>IF(U20&gt;=94,4,IF(U20&gt;=91,3.9,IF(U20&gt;=88,3.8,IF(U20&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF19" s="43">
         <v>0.3</v>
       </c>
-      <c r="AG19" s="117">
+      <c r="AG19" s="101">
         <v>17</v>
       </c>
       <c r="AH19" s="44" t="e">
@@ -5930,29 +5831,29 @@
       <c r="AO19" s="50"/>
     </row>
     <row r="20" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="91"/>
-      <c r="B20" s="89"/>
-      <c r="C20" s="183" t="s">
-        <v>48</v>
-      </c>
-      <c r="D20" s="184"/>
-      <c r="E20" s="184"/>
-      <c r="F20" s="184"/>
-      <c r="G20" s="185"/>
+      <c r="A20" s="85"/>
+      <c r="B20" s="83"/>
+      <c r="C20" s="121" t="s">
+        <v>47</v>
+      </c>
+      <c r="D20" s="122"/>
+      <c r="E20" s="122"/>
+      <c r="F20" s="122"/>
+      <c r="G20" s="123"/>
       <c r="H20" s="34"/>
-      <c r="I20" s="57"/>
-      <c r="J20" s="61"/>
-      <c r="K20" s="61"/>
-      <c r="L20" s="61"/>
-      <c r="M20" s="85"/>
-      <c r="N20" s="62"/>
+      <c r="I20" s="56"/>
+      <c r="J20" s="60"/>
+      <c r="K20" s="60"/>
+      <c r="L20" s="60"/>
+      <c r="M20" s="80"/>
+      <c r="N20" s="61"/>
       <c r="O20" s="37"/>
-      <c r="P20" s="63"/>
-      <c r="Q20" s="63"/>
-      <c r="R20" s="63"/>
-      <c r="S20" s="63"/>
+      <c r="P20" s="62"/>
+      <c r="Q20" s="62"/>
+      <c r="R20" s="62"/>
+      <c r="S20" s="62"/>
       <c r="T20" s="40"/>
-      <c r="U20" s="77">
+      <c r="U20" s="74">
         <f>(I19*P20)+(J19*Q20)+(K19*R20)+(L19*S20)+(M19*T20)</f>
         <v>0</v>
       </c>
@@ -5962,12 +5863,12 @@
       <c r="Y20" s="42"/>
       <c r="Z20" s="42"/>
       <c r="AA20" s="42"/>
-      <c r="AB20" s="73"/>
-      <c r="AC20" s="78"/>
-      <c r="AD20" s="74"/>
-      <c r="AE20" s="116"/>
+      <c r="AB20" s="70"/>
+      <c r="AC20" s="75"/>
+      <c r="AD20" s="71"/>
+      <c r="AE20" s="100"/>
       <c r="AF20" s="43"/>
-      <c r="AG20" s="65"/>
+      <c r="AG20" s="64"/>
       <c r="AH20" s="44"/>
       <c r="AI20" s="41"/>
       <c r="AJ20" s="45"/>
@@ -5978,20 +5879,20 @@
       <c r="AO20" s="50"/>
     </row>
     <row r="21" spans="1:41" s="22" customFormat="1" ht="51.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="90"/>
-      <c r="B21" s="88"/>
-      <c r="C21" s="104"/>
-      <c r="D21" s="92"/>
-      <c r="E21" s="96"/>
-      <c r="F21" s="96"/>
-      <c r="G21" s="120"/>
+      <c r="A21" s="84"/>
+      <c r="B21" s="82"/>
+      <c r="C21" s="173"/>
+      <c r="D21" s="172"/>
+      <c r="E21" s="173"/>
+      <c r="F21" s="173"/>
+      <c r="G21" s="113"/>
       <c r="H21" s="34"/>
-      <c r="I21" s="94"/>
-      <c r="J21" s="95"/>
-      <c r="K21" s="95"/>
-      <c r="L21" s="95"/>
-      <c r="M21" s="122"/>
-      <c r="N21" s="121">
+      <c r="I21" s="86"/>
+      <c r="J21" s="87"/>
+      <c r="K21" s="87"/>
+      <c r="L21" s="87"/>
+      <c r="M21" s="105"/>
+      <c r="N21" s="104">
         <f>SUM(I21:M21)</f>
         <v>0</v>
       </c>
@@ -6014,26 +5915,26 @@
       <c r="Y21" s="51"/>
       <c r="Z21" s="42"/>
       <c r="AA21" s="42"/>
-      <c r="AB21" s="73" t="e">
+      <c r="AB21" s="70" t="e">
         <f>(((((W21*I21)+(X21*J21)+(Y21*K21)+(Z21*L21)+(AA21*M21))/$L$2)))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AC21" s="78" t="e">
+      <c r="AC21" s="75" t="e">
         <f>ROUND(11*AB21,3)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD21" s="75" t="e">
+      <c r="AD21" s="72" t="e">
         <f t="shared" ref="AD21" si="11">IF(AC21&gt;=11,11,AC21)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE21" s="116">
+      <c r="AE21" s="100">
         <f>IF(U22&gt;=94,4,IF(U22&gt;=91,3.9,IF(U22&gt;=88,3.8,IF(U22&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF21" s="43">
         <v>0.3</v>
       </c>
-      <c r="AG21" s="117">
+      <c r="AG21" s="101">
         <v>17</v>
       </c>
       <c r="AH21" s="44" t="e">
@@ -6052,29 +5953,29 @@
       <c r="AO21" s="50"/>
     </row>
     <row r="22" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="91"/>
-      <c r="B22" s="89"/>
-      <c r="C22" s="183" t="s">
-        <v>48</v>
-      </c>
-      <c r="D22" s="184"/>
-      <c r="E22" s="184"/>
-      <c r="F22" s="184"/>
-      <c r="G22" s="185"/>
-      <c r="H22" s="97"/>
-      <c r="I22" s="98"/>
-      <c r="J22" s="99"/>
-      <c r="K22" s="99"/>
-      <c r="L22" s="99"/>
-      <c r="M22" s="123"/>
-      <c r="N22" s="121"/>
+      <c r="A22" s="85"/>
+      <c r="B22" s="83"/>
+      <c r="C22" s="121" t="s">
+        <v>47</v>
+      </c>
+      <c r="D22" s="122"/>
+      <c r="E22" s="122"/>
+      <c r="F22" s="122"/>
+      <c r="G22" s="123"/>
+      <c r="H22" s="88"/>
+      <c r="I22" s="89"/>
+      <c r="J22" s="90"/>
+      <c r="K22" s="90"/>
+      <c r="L22" s="90"/>
+      <c r="M22" s="106"/>
+      <c r="N22" s="104"/>
       <c r="O22" s="37"/>
       <c r="P22" s="40"/>
       <c r="Q22" s="40"/>
       <c r="R22" s="40"/>
       <c r="S22" s="40"/>
       <c r="T22" s="40"/>
-      <c r="U22" s="77">
+      <c r="U22" s="74">
         <f>(I21*P22)+(J21*Q22)+(K21*R22)+(L21*S22)+(M21*T22)</f>
         <v>0</v>
       </c>
@@ -6084,12 +5985,12 @@
       <c r="Y22" s="42"/>
       <c r="Z22" s="42"/>
       <c r="AA22" s="42"/>
-      <c r="AB22" s="73"/>
-      <c r="AC22" s="78"/>
-      <c r="AD22" s="74"/>
-      <c r="AE22" s="116"/>
+      <c r="AB22" s="70"/>
+      <c r="AC22" s="75"/>
+      <c r="AD22" s="71"/>
+      <c r="AE22" s="100"/>
       <c r="AF22" s="43"/>
-      <c r="AG22" s="65"/>
+      <c r="AG22" s="64"/>
       <c r="AH22" s="44"/>
       <c r="AI22" s="41"/>
       <c r="AJ22" s="45"/>
@@ -6100,20 +6001,20 @@
       <c r="AO22" s="50"/>
     </row>
     <row r="23" spans="1:41" s="22" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="90"/>
-      <c r="B23" s="88"/>
-      <c r="C23" s="100"/>
-      <c r="D23" s="96"/>
-      <c r="E23" s="92"/>
-      <c r="F23" s="105"/>
-      <c r="G23" s="128"/>
-      <c r="H23" s="58"/>
+      <c r="A23" s="84"/>
+      <c r="B23" s="82"/>
+      <c r="C23" s="173"/>
+      <c r="D23" s="172"/>
+      <c r="E23" s="173"/>
+      <c r="F23" s="173"/>
+      <c r="G23" s="113"/>
+      <c r="H23" s="57"/>
       <c r="I23" s="35"/>
       <c r="J23" s="36"/>
       <c r="K23" s="36"/>
       <c r="L23" s="36"/>
-      <c r="M23" s="86"/>
-      <c r="N23" s="62">
+      <c r="M23" s="81"/>
+      <c r="N23" s="61">
         <f>SUM(I23:M23)</f>
         <v>0</v>
       </c>
@@ -6136,26 +6037,26 @@
       <c r="Y23" s="42"/>
       <c r="Z23" s="42"/>
       <c r="AA23" s="42"/>
-      <c r="AB23" s="73" t="e">
+      <c r="AB23" s="70" t="e">
         <f>(((((W23*I23)+(X23*J23)+(Y23*K23)+(Z23*L23)+(AA23*M23))/$L$2)))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AC23" s="78" t="e">
+      <c r="AC23" s="75" t="e">
         <f t="shared" ref="AC23" si="12">ROUND(11*AB23,3)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD23" s="75" t="e">
+      <c r="AD23" s="72" t="e">
         <f t="shared" ref="AD23" si="13">IF(AC23&gt;=11,11,AC23)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE23" s="116">
+      <c r="AE23" s="100">
         <f>IF(U24&gt;=94,4,IF(U24&gt;=91,3.9,IF(U24&gt;=88,3.8,IF(U24&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF23" s="43">
         <v>0.3</v>
       </c>
-      <c r="AG23" s="117">
+      <c r="AG23" s="101">
         <v>17</v>
       </c>
       <c r="AH23" s="44" t="e">
@@ -6174,29 +6075,29 @@
       <c r="AO23" s="50"/>
     </row>
     <row r="24" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="91"/>
-      <c r="B24" s="89"/>
-      <c r="C24" s="183" t="s">
-        <v>48</v>
-      </c>
-      <c r="D24" s="184"/>
-      <c r="E24" s="184"/>
-      <c r="F24" s="184"/>
-      <c r="G24" s="185"/>
+      <c r="A24" s="85"/>
+      <c r="B24" s="83"/>
+      <c r="C24" s="121" t="s">
+        <v>47</v>
+      </c>
+      <c r="D24" s="122"/>
+      <c r="E24" s="122"/>
+      <c r="F24" s="122"/>
+      <c r="G24" s="123"/>
       <c r="H24" s="34"/>
-      <c r="I24" s="57"/>
-      <c r="J24" s="61"/>
-      <c r="K24" s="61"/>
-      <c r="L24" s="61"/>
-      <c r="M24" s="85"/>
-      <c r="N24" s="62"/>
+      <c r="I24" s="56"/>
+      <c r="J24" s="60"/>
+      <c r="K24" s="60"/>
+      <c r="L24" s="60"/>
+      <c r="M24" s="80"/>
+      <c r="N24" s="61"/>
       <c r="O24" s="37"/>
-      <c r="P24" s="63"/>
+      <c r="P24" s="62"/>
       <c r="Q24" s="40"/>
       <c r="R24" s="39"/>
       <c r="S24" s="40"/>
       <c r="T24" s="40"/>
-      <c r="U24" s="77">
+      <c r="U24" s="74">
         <f>(I23*P24)+(J23*Q24)+(K23*R24)+(L23*S24)+(M23*T24)</f>
         <v>0</v>
       </c>
@@ -6206,12 +6107,12 @@
       <c r="Y24" s="42"/>
       <c r="Z24" s="42"/>
       <c r="AA24" s="42"/>
-      <c r="AB24" s="73"/>
-      <c r="AC24" s="78"/>
-      <c r="AD24" s="74"/>
-      <c r="AE24" s="116"/>
+      <c r="AB24" s="70"/>
+      <c r="AC24" s="75"/>
+      <c r="AD24" s="71"/>
+      <c r="AE24" s="100"/>
       <c r="AF24" s="43"/>
-      <c r="AG24" s="65"/>
+      <c r="AG24" s="64"/>
       <c r="AH24" s="44"/>
       <c r="AI24" s="41"/>
       <c r="AJ24" s="45"/>
@@ -6222,20 +6123,20 @@
       <c r="AO24" s="50"/>
     </row>
     <row r="25" spans="1:41" s="22" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="90"/>
-      <c r="B25" s="88"/>
-      <c r="C25" s="100"/>
-      <c r="D25" s="101"/>
-      <c r="E25" s="101"/>
-      <c r="F25" s="101"/>
-      <c r="G25" s="120"/>
+      <c r="A25" s="84"/>
+      <c r="B25" s="82"/>
+      <c r="C25" s="173"/>
+      <c r="D25" s="172"/>
+      <c r="E25" s="173"/>
+      <c r="F25" s="173"/>
+      <c r="G25" s="113"/>
       <c r="H25" s="34"/>
       <c r="I25" s="35"/>
       <c r="J25" s="36"/>
       <c r="K25" s="36"/>
       <c r="L25" s="36"/>
-      <c r="M25" s="86"/>
-      <c r="N25" s="62">
+      <c r="M25" s="81"/>
+      <c r="N25" s="61">
         <f>SUM(I25:M25)</f>
         <v>0</v>
       </c>
@@ -6258,26 +6159,26 @@
       <c r="Y25" s="42"/>
       <c r="Z25" s="42"/>
       <c r="AA25" s="42"/>
-      <c r="AB25" s="73" t="e">
+      <c r="AB25" s="70" t="e">
         <f>(((((W25*I25)+(X25*J25)+(Y25*K25)+(Z25*L25)+(AA25*M25))/$L$2)))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AC25" s="78" t="e">
+      <c r="AC25" s="75" t="e">
         <f>ROUND(11*AB25,3)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD25" s="75" t="e">
+      <c r="AD25" s="72" t="e">
         <f>IF(AC25&gt;=11,11,AC25)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE25" s="116">
+      <c r="AE25" s="100">
         <f>IF(U26&gt;=94,4,IF(U26&gt;=91,3.9,IF(U26&gt;=88,3.8,IF(U26&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF25" s="43">
         <v>0.3</v>
       </c>
-      <c r="AG25" s="117">
+      <c r="AG25" s="101">
         <v>17</v>
       </c>
       <c r="AH25" s="44" t="e">
@@ -6296,29 +6197,29 @@
       <c r="AO25" s="50"/>
     </row>
     <row r="26" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="91"/>
-      <c r="B26" s="89"/>
-      <c r="C26" s="183" t="s">
-        <v>48</v>
-      </c>
-      <c r="D26" s="184"/>
-      <c r="E26" s="184"/>
-      <c r="F26" s="184"/>
-      <c r="G26" s="185"/>
+      <c r="A26" s="85"/>
+      <c r="B26" s="83"/>
+      <c r="C26" s="121" t="s">
+        <v>47</v>
+      </c>
+      <c r="D26" s="122"/>
+      <c r="E26" s="122"/>
+      <c r="F26" s="122"/>
+      <c r="G26" s="123"/>
       <c r="H26" s="34"/>
-      <c r="I26" s="57"/>
-      <c r="J26" s="61"/>
-      <c r="K26" s="61"/>
-      <c r="L26" s="61"/>
-      <c r="M26" s="85"/>
-      <c r="N26" s="62"/>
+      <c r="I26" s="56"/>
+      <c r="J26" s="60"/>
+      <c r="K26" s="60"/>
+      <c r="L26" s="60"/>
+      <c r="M26" s="80"/>
+      <c r="N26" s="61"/>
       <c r="O26" s="37"/>
       <c r="P26" s="39"/>
       <c r="Q26" s="39"/>
       <c r="R26" s="39"/>
       <c r="S26" s="39"/>
       <c r="T26" s="40"/>
-      <c r="U26" s="77">
+      <c r="U26" s="74">
         <f>(I25*P26)+(J25*Q26)+(K25*R26)+(L25*S26)+(M25*T26)</f>
         <v>0</v>
       </c>
@@ -6328,12 +6229,12 @@
       <c r="Y26" s="42"/>
       <c r="Z26" s="42"/>
       <c r="AA26" s="42"/>
-      <c r="AB26" s="73"/>
-      <c r="AC26" s="78"/>
-      <c r="AD26" s="74"/>
-      <c r="AE26" s="116"/>
+      <c r="AB26" s="70"/>
+      <c r="AC26" s="75"/>
+      <c r="AD26" s="71"/>
+      <c r="AE26" s="100"/>
       <c r="AF26" s="43"/>
-      <c r="AG26" s="65"/>
+      <c r="AG26" s="64"/>
       <c r="AH26" s="44"/>
       <c r="AI26" s="41"/>
       <c r="AJ26" s="45"/>
@@ -6344,27 +6245,27 @@
       <c r="AO26" s="50"/>
     </row>
     <row r="27" spans="1:41" s="22" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="90"/>
-      <c r="B27" s="88"/>
-      <c r="C27" s="96"/>
-      <c r="D27" s="96"/>
-      <c r="E27" s="96"/>
-      <c r="F27" s="102"/>
-      <c r="G27" s="129"/>
+      <c r="A27" s="84"/>
+      <c r="B27" s="82"/>
+      <c r="C27" s="173"/>
+      <c r="D27" s="172"/>
+      <c r="E27" s="173"/>
+      <c r="F27" s="173"/>
+      <c r="G27" s="113"/>
       <c r="H27" s="34"/>
       <c r="I27" s="35"/>
       <c r="J27" s="36"/>
       <c r="K27" s="36"/>
       <c r="L27" s="36"/>
-      <c r="M27" s="86"/>
-      <c r="N27" s="62">
+      <c r="M27" s="81"/>
+      <c r="N27" s="61">
         <f>SUM(I27:M27)</f>
         <v>0</v>
       </c>
       <c r="O27" s="37"/>
-      <c r="P27" s="144"/>
-      <c r="Q27" s="145"/>
-      <c r="R27" s="145"/>
+      <c r="P27" s="114"/>
+      <c r="Q27" s="115"/>
+      <c r="R27" s="115"/>
       <c r="S27" s="39"/>
       <c r="T27" s="39"/>
       <c r="U27" s="40">
@@ -6380,26 +6281,26 @@
       <c r="Y27" s="51"/>
       <c r="Z27" s="42"/>
       <c r="AA27" s="42"/>
-      <c r="AB27" s="73" t="e">
+      <c r="AB27" s="70" t="e">
         <f>(((((W27*I27)+(X27*J27)+(Y27*K27)+(Z27*L27)+(AA27*M27))/$L$2)))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AC27" s="78" t="e">
+      <c r="AC27" s="75" t="e">
         <f t="shared" ref="AC27" si="14">ROUND(11*AB27,3)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD27" s="75" t="e">
+      <c r="AD27" s="72" t="e">
         <f t="shared" ref="AD27" si="15">IF(AC27&gt;=11,11,AC27)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE27" s="116">
+      <c r="AE27" s="100">
         <f>IF(U28&gt;=94,4,IF(U28&gt;=91,3.9,IF(U28&gt;=88,3.8,IF(U28&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF27" s="43">
         <v>0.3</v>
       </c>
-      <c r="AG27" s="117">
+      <c r="AG27" s="101">
         <v>17</v>
       </c>
       <c r="AH27" s="44" t="e">
@@ -6424,29 +6325,29 @@
       <c r="AO27" s="50"/>
     </row>
     <row r="28" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="91"/>
-      <c r="B28" s="89"/>
-      <c r="C28" s="194" t="s">
-        <v>48</v>
-      </c>
-      <c r="D28" s="195"/>
-      <c r="E28" s="195"/>
-      <c r="F28" s="195"/>
-      <c r="G28" s="196"/>
-      <c r="H28" s="60"/>
-      <c r="I28" s="57"/>
-      <c r="J28" s="61"/>
-      <c r="K28" s="61"/>
-      <c r="L28" s="61"/>
-      <c r="M28" s="131"/>
-      <c r="N28" s="62"/>
+      <c r="A28" s="85"/>
+      <c r="B28" s="83"/>
+      <c r="C28" s="118" t="s">
+        <v>47</v>
+      </c>
+      <c r="D28" s="119"/>
+      <c r="E28" s="119"/>
+      <c r="F28" s="119"/>
+      <c r="G28" s="120"/>
+      <c r="H28" s="59"/>
+      <c r="I28" s="56"/>
+      <c r="J28" s="60"/>
+      <c r="K28" s="60"/>
+      <c r="L28" s="60"/>
+      <c r="M28" s="110"/>
+      <c r="N28" s="61"/>
       <c r="O28" s="37"/>
-      <c r="P28" s="147"/>
-      <c r="Q28" s="147"/>
-      <c r="R28" s="147"/>
+      <c r="P28" s="117"/>
+      <c r="Q28" s="117"/>
+      <c r="R28" s="117"/>
       <c r="S28" s="40"/>
       <c r="T28" s="40"/>
-      <c r="U28" s="77">
+      <c r="U28" s="74">
         <f>(I27*P28)+(J27*Q28)+(K27*R28)+(L27*S28)+(M27*T28)</f>
         <v>0</v>
       </c>
@@ -6456,12 +6357,12 @@
       <c r="Y28" s="42"/>
       <c r="Z28" s="42"/>
       <c r="AA28" s="42"/>
-      <c r="AB28" s="73"/>
-      <c r="AC28" s="78"/>
-      <c r="AD28" s="74"/>
-      <c r="AE28" s="116"/>
+      <c r="AB28" s="70"/>
+      <c r="AC28" s="75"/>
+      <c r="AD28" s="71"/>
+      <c r="AE28" s="100"/>
       <c r="AF28" s="43"/>
-      <c r="AG28" s="65"/>
+      <c r="AG28" s="64"/>
       <c r="AH28" s="44"/>
       <c r="AI28" s="41"/>
       <c r="AJ28" s="45"/>
@@ -6472,27 +6373,27 @@
       <c r="AO28" s="50"/>
     </row>
     <row r="29" spans="1:41" s="22" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="90"/>
-      <c r="B29" s="88"/>
-      <c r="C29" s="135"/>
-      <c r="D29" s="135"/>
-      <c r="E29" s="138"/>
-      <c r="F29" s="134"/>
-      <c r="G29" s="136"/>
+      <c r="A29" s="84"/>
+      <c r="B29" s="82"/>
+      <c r="C29" s="173"/>
+      <c r="D29" s="172"/>
+      <c r="E29" s="173"/>
+      <c r="F29" s="173"/>
+      <c r="G29" s="113"/>
       <c r="H29" s="34"/>
       <c r="I29" s="35"/>
       <c r="J29" s="36"/>
       <c r="K29" s="36"/>
-      <c r="L29" s="61"/>
-      <c r="M29" s="86"/>
-      <c r="N29" s="62">
+      <c r="L29" s="60"/>
+      <c r="M29" s="81"/>
+      <c r="N29" s="61">
         <f>SUM(I29:M29)</f>
         <v>0</v>
       </c>
       <c r="O29" s="37"/>
-      <c r="P29" s="144"/>
-      <c r="Q29" s="145"/>
-      <c r="R29" s="145"/>
+      <c r="P29" s="114"/>
+      <c r="Q29" s="115"/>
+      <c r="R29" s="115"/>
       <c r="S29" s="39"/>
       <c r="T29" s="39"/>
       <c r="U29" s="40">
@@ -6508,26 +6409,26 @@
       <c r="Y29" s="42"/>
       <c r="Z29" s="42"/>
       <c r="AA29" s="42"/>
-      <c r="AB29" s="73" t="e">
+      <c r="AB29" s="70" t="e">
         <f>(((((W29*I29)+(X29*J29)+(Y29*K29)+(Z29*L29)+(AA29*M29))/$L$2)))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AC29" s="78" t="e">
+      <c r="AC29" s="75" t="e">
         <f>ROUND(11*AB29,3)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD29" s="75" t="e">
+      <c r="AD29" s="72" t="e">
         <f>IF(AC29&gt;=11,11,AC29)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE29" s="116">
+      <c r="AE29" s="100">
         <f>IF(U30&gt;=94,4,IF(U30&gt;=91,3.9,IF(U30&gt;=88,3.8,IF(U30&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF29" s="43">
         <v>0.3</v>
       </c>
-      <c r="AG29" s="117">
+      <c r="AG29" s="101">
         <v>17</v>
       </c>
       <c r="AH29" s="44" t="e">
@@ -6552,29 +6453,29 @@
       <c r="AO29" s="50"/>
     </row>
     <row r="30" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="91"/>
-      <c r="B30" s="89"/>
-      <c r="C30" s="183" t="s">
-        <v>48</v>
-      </c>
-      <c r="D30" s="184"/>
-      <c r="E30" s="184"/>
-      <c r="F30" s="184"/>
-      <c r="G30" s="185"/>
+      <c r="A30" s="85"/>
+      <c r="B30" s="83"/>
+      <c r="C30" s="121" t="s">
+        <v>47</v>
+      </c>
+      <c r="D30" s="122"/>
+      <c r="E30" s="122"/>
+      <c r="F30" s="122"/>
+      <c r="G30" s="123"/>
       <c r="H30" s="34"/>
-      <c r="I30" s="57"/>
-      <c r="J30" s="61"/>
-      <c r="K30" s="61"/>
-      <c r="L30" s="61"/>
-      <c r="M30" s="85"/>
-      <c r="N30" s="62"/>
+      <c r="I30" s="56"/>
+      <c r="J30" s="60"/>
+      <c r="K30" s="60"/>
+      <c r="L30" s="60"/>
+      <c r="M30" s="80"/>
+      <c r="N30" s="61"/>
       <c r="O30" s="37"/>
-      <c r="P30" s="146"/>
-      <c r="Q30" s="147"/>
-      <c r="R30" s="147"/>
+      <c r="P30" s="116"/>
+      <c r="Q30" s="117"/>
+      <c r="R30" s="117"/>
       <c r="S30" s="40"/>
       <c r="T30" s="40"/>
-      <c r="U30" s="77">
+      <c r="U30" s="74">
         <f>(I29*P30)+(J29*Q30)+(K29*R30)+(L29*S30)+(M29*T30)</f>
         <v>0</v>
       </c>
@@ -6584,12 +6485,12 @@
       <c r="Y30" s="42"/>
       <c r="Z30" s="42"/>
       <c r="AA30" s="42"/>
-      <c r="AB30" s="73"/>
-      <c r="AC30" s="78"/>
-      <c r="AD30" s="74"/>
-      <c r="AE30" s="116"/>
+      <c r="AB30" s="70"/>
+      <c r="AC30" s="75"/>
+      <c r="AD30" s="71"/>
+      <c r="AE30" s="100"/>
       <c r="AF30" s="43"/>
-      <c r="AG30" s="65"/>
+      <c r="AG30" s="64"/>
       <c r="AH30" s="44"/>
       <c r="AI30" s="41"/>
       <c r="AJ30" s="45"/>
@@ -6600,27 +6501,27 @@
       <c r="AO30" s="50"/>
     </row>
     <row r="31" spans="1:41" s="22" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="90"/>
-      <c r="B31" s="88"/>
-      <c r="C31" s="92"/>
-      <c r="D31" s="96"/>
-      <c r="E31" s="96"/>
-      <c r="F31" s="100"/>
-      <c r="G31" s="120"/>
+      <c r="A31" s="84"/>
+      <c r="B31" s="82"/>
+      <c r="C31" s="173"/>
+      <c r="D31" s="172"/>
+      <c r="E31" s="173"/>
+      <c r="F31" s="173"/>
+      <c r="G31" s="113"/>
       <c r="H31" s="34"/>
-      <c r="I31" s="94"/>
-      <c r="J31" s="95"/>
-      <c r="K31" s="95"/>
-      <c r="L31" s="95"/>
-      <c r="M31" s="122"/>
-      <c r="N31" s="121">
+      <c r="I31" s="86"/>
+      <c r="J31" s="87"/>
+      <c r="K31" s="87"/>
+      <c r="L31" s="87"/>
+      <c r="M31" s="105"/>
+      <c r="N31" s="104">
         <f>SUM(I31:M31)</f>
         <v>0</v>
       </c>
       <c r="O31" s="37"/>
-      <c r="P31" s="144"/>
-      <c r="Q31" s="144"/>
-      <c r="R31" s="145"/>
+      <c r="P31" s="114"/>
+      <c r="Q31" s="114"/>
+      <c r="R31" s="115"/>
       <c r="S31" s="39"/>
       <c r="T31" s="39"/>
       <c r="U31" s="40">
@@ -6636,26 +6537,26 @@
       <c r="Y31" s="42"/>
       <c r="Z31" s="42"/>
       <c r="AA31" s="42"/>
-      <c r="AB31" s="73" t="e">
+      <c r="AB31" s="70" t="e">
         <f>(((((W31*I31)+(X31*J31)+(Y31*K31)+(Z31*L31)+(AA31*M31))/$L$2)))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AC31" s="78" t="e">
+      <c r="AC31" s="75" t="e">
         <f>ROUND(11*AB31,3)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD31" s="75" t="e">
+      <c r="AD31" s="72" t="e">
         <f t="shared" ref="AD31" si="16">IF(AC31&gt;=11,11,AC31)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE31" s="116">
+      <c r="AE31" s="100">
         <f>IF(U32&gt;=94,4,IF(U32&gt;=91,3.9,IF(U32&gt;=88,3.8,IF(U32&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF31" s="43">
         <v>0.3</v>
       </c>
-      <c r="AG31" s="117">
+      <c r="AG31" s="101">
         <v>17</v>
       </c>
       <c r="AH31" s="44" t="e">
@@ -6674,29 +6575,29 @@
       <c r="AO31" s="50"/>
     </row>
     <row r="32" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="91"/>
-      <c r="B32" s="89"/>
-      <c r="C32" s="183" t="s">
-        <v>48</v>
-      </c>
-      <c r="D32" s="184"/>
-      <c r="E32" s="184"/>
-      <c r="F32" s="184"/>
-      <c r="G32" s="185"/>
-      <c r="H32" s="97"/>
-      <c r="I32" s="98"/>
-      <c r="J32" s="99"/>
-      <c r="K32" s="99"/>
-      <c r="L32" s="99"/>
-      <c r="M32" s="123"/>
-      <c r="N32" s="121"/>
+      <c r="A32" s="85"/>
+      <c r="B32" s="83"/>
+      <c r="C32" s="121" t="s">
+        <v>47</v>
+      </c>
+      <c r="D32" s="122"/>
+      <c r="E32" s="122"/>
+      <c r="F32" s="122"/>
+      <c r="G32" s="123"/>
+      <c r="H32" s="88"/>
+      <c r="I32" s="89"/>
+      <c r="J32" s="90"/>
+      <c r="K32" s="90"/>
+      <c r="L32" s="90"/>
+      <c r="M32" s="106"/>
+      <c r="N32" s="104"/>
       <c r="O32" s="37"/>
-      <c r="P32" s="146"/>
-      <c r="Q32" s="147"/>
-      <c r="R32" s="147"/>
+      <c r="P32" s="116"/>
+      <c r="Q32" s="117"/>
+      <c r="R32" s="117"/>
       <c r="S32" s="40"/>
       <c r="T32" s="40"/>
-      <c r="U32" s="77">
+      <c r="U32" s="74">
         <f>(I31*P32)+(J31*Q32)+(K31*R32)+(L31*S32)+(M31*T32)</f>
         <v>0</v>
       </c>
@@ -6706,12 +6607,12 @@
       <c r="Y32" s="42"/>
       <c r="Z32" s="42"/>
       <c r="AA32" s="42"/>
-      <c r="AB32" s="73"/>
-      <c r="AC32" s="78"/>
-      <c r="AD32" s="74"/>
-      <c r="AE32" s="116"/>
+      <c r="AB32" s="70"/>
+      <c r="AC32" s="75"/>
+      <c r="AD32" s="71"/>
+      <c r="AE32" s="100"/>
       <c r="AF32" s="43"/>
-      <c r="AG32" s="65"/>
+      <c r="AG32" s="64"/>
       <c r="AH32" s="44"/>
       <c r="AI32" s="41"/>
       <c r="AJ32" s="45"/>
@@ -6722,20 +6623,20 @@
       <c r="AO32" s="50"/>
     </row>
     <row r="33" spans="1:41" s="22" customFormat="1" ht="52.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="90"/>
-      <c r="B33" s="88"/>
-      <c r="C33" s="96"/>
-      <c r="D33" s="92"/>
-      <c r="E33" s="92"/>
-      <c r="F33" s="92"/>
-      <c r="G33" s="127"/>
+      <c r="A33" s="84"/>
+      <c r="B33" s="82"/>
+      <c r="C33" s="173"/>
+      <c r="D33" s="172"/>
+      <c r="E33" s="173"/>
+      <c r="F33" s="173"/>
+      <c r="G33" s="113"/>
       <c r="H33" s="34"/>
       <c r="I33" s="35"/>
       <c r="J33" s="36"/>
       <c r="K33" s="36"/>
       <c r="L33" s="36"/>
-      <c r="M33" s="66"/>
-      <c r="N33" s="62">
+      <c r="M33" s="65"/>
+      <c r="N33" s="61">
         <f>SUM(I33:M33)</f>
         <v>0</v>
       </c>
@@ -6758,26 +6659,26 @@
       <c r="Y33" s="42"/>
       <c r="Z33" s="42"/>
       <c r="AA33" s="42"/>
-      <c r="AB33" s="73" t="e">
+      <c r="AB33" s="70" t="e">
         <f>(((((W33*I33)+(X33*J33)+(Y33*K33)+(Z33*L33)+(AA33*M33))/$L$2)))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AC33" s="78" t="e">
+      <c r="AC33" s="75" t="e">
         <f>ROUND(11*AB33,3)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD33" s="75" t="e">
+      <c r="AD33" s="72" t="e">
         <f>IF(AC33&gt;=11,11,AC33)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE33" s="116">
+      <c r="AE33" s="100">
         <f>IF(U34&gt;=94,4,IF(U34&gt;=91,3.9,IF(U34&gt;=88,3.8,IF(U34&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF33" s="43">
         <v>0.3</v>
       </c>
-      <c r="AG33" s="117">
+      <c r="AG33" s="101">
         <v>17</v>
       </c>
       <c r="AH33" s="44" t="e">
@@ -6802,29 +6703,29 @@
       <c r="AO33" s="50"/>
     </row>
     <row r="34" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="91"/>
-      <c r="B34" s="89"/>
-      <c r="C34" s="183" t="s">
-        <v>48</v>
-      </c>
-      <c r="D34" s="184"/>
-      <c r="E34" s="184"/>
-      <c r="F34" s="184"/>
-      <c r="G34" s="185"/>
+      <c r="A34" s="85"/>
+      <c r="B34" s="83"/>
+      <c r="C34" s="121" t="s">
+        <v>47</v>
+      </c>
+      <c r="D34" s="122"/>
+      <c r="E34" s="122"/>
+      <c r="F34" s="122"/>
+      <c r="G34" s="123"/>
       <c r="H34" s="34"/>
-      <c r="I34" s="57"/>
-      <c r="J34" s="61"/>
-      <c r="K34" s="61"/>
-      <c r="L34" s="61"/>
-      <c r="M34" s="85"/>
-      <c r="N34" s="62"/>
+      <c r="I34" s="56"/>
+      <c r="J34" s="60"/>
+      <c r="K34" s="60"/>
+      <c r="L34" s="60"/>
+      <c r="M34" s="80"/>
+      <c r="N34" s="61"/>
       <c r="O34" s="37"/>
       <c r="P34" s="40"/>
       <c r="Q34" s="40"/>
       <c r="R34" s="40"/>
       <c r="S34" s="40"/>
       <c r="T34" s="40"/>
-      <c r="U34" s="77">
+      <c r="U34" s="74">
         <f>(I33*P34)+(J33*Q34)+(K33*R34)+(L33*S34)+(M33*T34)</f>
         <v>0</v>
       </c>
@@ -6834,12 +6735,12 @@
       <c r="Y34" s="42"/>
       <c r="Z34" s="42"/>
       <c r="AA34" s="42"/>
-      <c r="AB34" s="73"/>
-      <c r="AC34" s="78"/>
-      <c r="AD34" s="74"/>
-      <c r="AE34" s="116"/>
+      <c r="AB34" s="70"/>
+      <c r="AC34" s="75"/>
+      <c r="AD34" s="71"/>
+      <c r="AE34" s="100"/>
       <c r="AF34" s="43"/>
-      <c r="AG34" s="65"/>
+      <c r="AG34" s="64"/>
       <c r="AH34" s="44"/>
       <c r="AI34" s="41"/>
       <c r="AJ34" s="45"/>
@@ -6850,29 +6751,29 @@
       <c r="AO34" s="50"/>
     </row>
     <row r="35" spans="1:41" s="22" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A35" s="90"/>
-      <c r="B35" s="88"/>
-      <c r="C35" s="96"/>
-      <c r="D35" s="103"/>
-      <c r="E35" s="100"/>
-      <c r="F35" s="92"/>
-      <c r="G35" s="128"/>
+      <c r="A35" s="84"/>
+      <c r="B35" s="82"/>
+      <c r="C35" s="173"/>
+      <c r="D35" s="172"/>
+      <c r="E35" s="173"/>
+      <c r="F35" s="173"/>
+      <c r="G35" s="113"/>
       <c r="H35" s="34"/>
       <c r="I35" s="35"/>
       <c r="J35" s="36"/>
       <c r="K35" s="36"/>
-      <c r="L35" s="61"/>
-      <c r="M35" s="85"/>
-      <c r="N35" s="62">
+      <c r="L35" s="60"/>
+      <c r="M35" s="80"/>
+      <c r="N35" s="61">
         <f>SUM(I35:M35)</f>
         <v>0</v>
       </c>
       <c r="O35" s="37"/>
-      <c r="P35" s="144"/>
-      <c r="Q35" s="145"/>
-      <c r="R35" s="145"/>
-      <c r="S35" s="145"/>
-      <c r="T35" s="145"/>
+      <c r="P35" s="114"/>
+      <c r="Q35" s="115"/>
+      <c r="R35" s="115"/>
+      <c r="S35" s="115"/>
+      <c r="T35" s="115"/>
       <c r="U35" s="40">
         <f>ROUND(((P35*I35)+(Q35*J35)+(R35*K35)+(S35*L35)+(T35*M35)),3)</f>
         <v>0</v>
@@ -6886,26 +6787,26 @@
       <c r="Y35" s="42"/>
       <c r="Z35" s="42"/>
       <c r="AA35" s="42"/>
-      <c r="AB35" s="73" t="e">
+      <c r="AB35" s="70" t="e">
         <f>(((((W35*I35)+(X35*J35)+(Y35*K35)+(Z35*L35)+(AA35*M35))/$L$2)))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AC35" s="78" t="e">
+      <c r="AC35" s="75" t="e">
         <f>ROUND(11*AB35,3)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD35" s="75" t="e">
+      <c r="AD35" s="72" t="e">
         <f t="shared" ref="AD35" si="17">IF(AC35&gt;=11,11,AC35)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE35" s="116">
+      <c r="AE35" s="100">
         <f>IF(U36&gt;=94,4,IF(U36&gt;=91,3.9,IF(U36&gt;=88,3.8,IF(U36&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF35" s="43">
         <v>0.3</v>
       </c>
-      <c r="AG35" s="117">
+      <c r="AG35" s="101">
         <v>17</v>
       </c>
       <c r="AH35" s="44" t="e">
@@ -6930,29 +6831,29 @@
       <c r="AO35" s="50"/>
     </row>
     <row r="36" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="91"/>
-      <c r="B36" s="89"/>
-      <c r="C36" s="183" t="s">
-        <v>48</v>
-      </c>
-      <c r="D36" s="184"/>
-      <c r="E36" s="184"/>
-      <c r="F36" s="184"/>
-      <c r="G36" s="185"/>
+      <c r="A36" s="85"/>
+      <c r="B36" s="83"/>
+      <c r="C36" s="121" t="s">
+        <v>47</v>
+      </c>
+      <c r="D36" s="122"/>
+      <c r="E36" s="122"/>
+      <c r="F36" s="122"/>
+      <c r="G36" s="123"/>
       <c r="H36" s="34"/>
-      <c r="I36" s="57"/>
-      <c r="J36" s="61"/>
-      <c r="K36" s="61"/>
-      <c r="L36" s="61"/>
-      <c r="M36" s="85"/>
-      <c r="N36" s="62"/>
+      <c r="I36" s="56"/>
+      <c r="J36" s="60"/>
+      <c r="K36" s="60"/>
+      <c r="L36" s="60"/>
+      <c r="M36" s="80"/>
+      <c r="N36" s="61"/>
       <c r="O36" s="37"/>
-      <c r="P36" s="147"/>
-      <c r="Q36" s="147"/>
-      <c r="R36" s="147"/>
-      <c r="S36" s="147"/>
-      <c r="T36" s="147"/>
-      <c r="U36" s="77">
+      <c r="P36" s="117"/>
+      <c r="Q36" s="117"/>
+      <c r="R36" s="117"/>
+      <c r="S36" s="117"/>
+      <c r="T36" s="117"/>
+      <c r="U36" s="74">
         <f>(I35*P36)+(J35*Q36)+(K35*R36)+(L35*S36)+(M35*T36)</f>
         <v>0</v>
       </c>
@@ -6962,12 +6863,12 @@
       <c r="Y36" s="42"/>
       <c r="Z36" s="42"/>
       <c r="AA36" s="42"/>
-      <c r="AB36" s="73"/>
-      <c r="AC36" s="78"/>
-      <c r="AD36" s="74"/>
-      <c r="AE36" s="116"/>
+      <c r="AB36" s="70"/>
+      <c r="AC36" s="75"/>
+      <c r="AD36" s="71"/>
+      <c r="AE36" s="100"/>
       <c r="AF36" s="43"/>
-      <c r="AG36" s="65"/>
+      <c r="AG36" s="64"/>
       <c r="AH36" s="44"/>
       <c r="AI36" s="41"/>
       <c r="AJ36" s="45"/>
@@ -6978,29 +6879,29 @@
       <c r="AO36" s="50"/>
     </row>
     <row r="37" spans="1:41" s="22" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="90"/>
-      <c r="B37" s="88"/>
-      <c r="C37" s="96"/>
-      <c r="D37" s="92"/>
-      <c r="E37" s="102"/>
-      <c r="F37" s="102"/>
-      <c r="G37" s="120"/>
+      <c r="A37" s="84"/>
+      <c r="B37" s="82"/>
+      <c r="C37" s="173"/>
+      <c r="D37" s="172"/>
+      <c r="E37" s="173"/>
+      <c r="F37" s="173"/>
+      <c r="G37" s="113"/>
       <c r="H37" s="34"/>
       <c r="I37" s="35"/>
       <c r="J37" s="36"/>
       <c r="K37" s="36"/>
       <c r="L37" s="36"/>
-      <c r="M37" s="86"/>
-      <c r="N37" s="62">
+      <c r="M37" s="81"/>
+      <c r="N37" s="61">
         <f>SUM(I37:M37)</f>
         <v>0</v>
       </c>
       <c r="O37" s="37"/>
-      <c r="P37" s="144"/>
-      <c r="Q37" s="145"/>
-      <c r="R37" s="145"/>
-      <c r="S37" s="145"/>
-      <c r="T37" s="145"/>
+      <c r="P37" s="114"/>
+      <c r="Q37" s="115"/>
+      <c r="R37" s="115"/>
+      <c r="S37" s="115"/>
+      <c r="T37" s="115"/>
       <c r="U37" s="40">
         <f>ROUND(((P37*I37)+(Q37*J37)+(R37*K37)+(S37*L37)+(T37*M37)),3)</f>
         <v>0</v>
@@ -7014,26 +6915,26 @@
       <c r="Y37" s="42"/>
       <c r="Z37" s="42"/>
       <c r="AA37" s="42"/>
-      <c r="AB37" s="73" t="e">
+      <c r="AB37" s="70" t="e">
         <f>(((((W37*I37)+(X37*J37)+(Y37*K37)+(Z37*L37)+(AA37*M37))/$L$2)))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AC37" s="78" t="e">
+      <c r="AC37" s="75" t="e">
         <f>ROUND(11*AB37,3)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD37" s="75" t="e">
+      <c r="AD37" s="72" t="e">
         <f>IF(AC37&gt;=11,11,AC37)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE37" s="116">
+      <c r="AE37" s="100">
         <f>IF(U38&gt;=94,4,IF(U38&gt;=91,3.9,IF(U38&gt;=88,3.8,IF(U38&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF37" s="43">
         <v>0.3</v>
       </c>
-      <c r="AG37" s="117">
+      <c r="AG37" s="101">
         <v>17</v>
       </c>
       <c r="AH37" s="44" t="e">
@@ -7058,29 +6959,29 @@
       <c r="AO37" s="50"/>
     </row>
     <row r="38" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A38" s="91"/>
-      <c r="B38" s="89"/>
-      <c r="C38" s="183" t="s">
-        <v>48</v>
-      </c>
-      <c r="D38" s="184"/>
-      <c r="E38" s="184"/>
-      <c r="F38" s="184"/>
-      <c r="G38" s="185"/>
+      <c r="A38" s="85"/>
+      <c r="B38" s="83"/>
+      <c r="C38" s="121" t="s">
+        <v>47</v>
+      </c>
+      <c r="D38" s="122"/>
+      <c r="E38" s="122"/>
+      <c r="F38" s="122"/>
+      <c r="G38" s="123"/>
       <c r="H38" s="34"/>
-      <c r="I38" s="57"/>
-      <c r="J38" s="61"/>
-      <c r="K38" s="61"/>
-      <c r="L38" s="61"/>
-      <c r="M38" s="85"/>
-      <c r="N38" s="62"/>
+      <c r="I38" s="56"/>
+      <c r="J38" s="60"/>
+      <c r="K38" s="60"/>
+      <c r="L38" s="60"/>
+      <c r="M38" s="80"/>
+      <c r="N38" s="61"/>
       <c r="O38" s="37"/>
-      <c r="P38" s="146"/>
-      <c r="Q38" s="147"/>
-      <c r="R38" s="145"/>
-      <c r="S38" s="147"/>
-      <c r="T38" s="147"/>
-      <c r="U38" s="77">
+      <c r="P38" s="116"/>
+      <c r="Q38" s="117"/>
+      <c r="R38" s="115"/>
+      <c r="S38" s="117"/>
+      <c r="T38" s="117"/>
+      <c r="U38" s="74">
         <f>(I37*P38)+(J37*Q38)+(K37*R38)+(L37*S38)+(M37*T38)</f>
         <v>0</v>
       </c>
@@ -7090,12 +6991,12 @@
       <c r="Y38" s="42"/>
       <c r="Z38" s="42"/>
       <c r="AA38" s="42"/>
-      <c r="AB38" s="73"/>
-      <c r="AC38" s="78"/>
-      <c r="AD38" s="74"/>
-      <c r="AE38" s="116"/>
+      <c r="AB38" s="70"/>
+      <c r="AC38" s="75"/>
+      <c r="AD38" s="71"/>
+      <c r="AE38" s="100"/>
       <c r="AF38" s="43"/>
-      <c r="AG38" s="65"/>
+      <c r="AG38" s="64"/>
       <c r="AH38" s="44"/>
       <c r="AI38" s="41"/>
       <c r="AJ38" s="45"/>
@@ -7106,29 +7007,29 @@
       <c r="AO38" s="50"/>
     </row>
     <row r="39" spans="1:41" s="22" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A39" s="90"/>
-      <c r="B39" s="88"/>
-      <c r="C39" s="96"/>
-      <c r="D39" s="96"/>
-      <c r="E39" s="92"/>
-      <c r="F39" s="102"/>
-      <c r="G39" s="128"/>
+      <c r="A39" s="84"/>
+      <c r="B39" s="82"/>
+      <c r="C39" s="173"/>
+      <c r="D39" s="172"/>
+      <c r="E39" s="173"/>
+      <c r="F39" s="173"/>
+      <c r="G39" s="113"/>
       <c r="H39" s="34"/>
       <c r="I39" s="35"/>
       <c r="J39" s="36"/>
       <c r="K39" s="36"/>
       <c r="L39" s="36"/>
-      <c r="M39" s="86"/>
-      <c r="N39" s="62">
+      <c r="M39" s="81"/>
+      <c r="N39" s="61">
         <f>SUM(I39:M39)</f>
         <v>0</v>
       </c>
       <c r="O39" s="37"/>
-      <c r="P39" s="144"/>
-      <c r="Q39" s="145"/>
-      <c r="R39" s="145"/>
-      <c r="S39" s="145"/>
-      <c r="T39" s="145"/>
+      <c r="P39" s="114"/>
+      <c r="Q39" s="115"/>
+      <c r="R39" s="115"/>
+      <c r="S39" s="115"/>
+      <c r="T39" s="115"/>
       <c r="U39" s="40">
         <f>ROUND(((P39*I39)+(Q39*J39)+(R39*K39)+(S39*L39)+(T39*M39)),3)</f>
         <v>0</v>
@@ -7142,26 +7043,26 @@
       <c r="Y39" s="42"/>
       <c r="Z39" s="42"/>
       <c r="AA39" s="42"/>
-      <c r="AB39" s="73" t="e">
+      <c r="AB39" s="70" t="e">
         <f>(((((W39*I39)+(X39*J39)+(Y39*K39)+(Z39*L39)+(AA39*M39))/$L$2)))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AC39" s="78" t="e">
+      <c r="AC39" s="75" t="e">
         <f t="shared" ref="AC39" si="18">ROUND(11*AB39,3)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD39" s="75" t="e">
+      <c r="AD39" s="72" t="e">
         <f t="shared" ref="AD39" si="19">IF(AC39&gt;=11,11,AC39)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE39" s="116">
+      <c r="AE39" s="100">
         <f>IF(U40&gt;=94,4,IF(U40&gt;=91,3.9,IF(U40&gt;=88,3.8,IF(U40&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF39" s="43">
         <v>0.3</v>
       </c>
-      <c r="AG39" s="117">
+      <c r="AG39" s="101">
         <v>17</v>
       </c>
       <c r="AH39" s="44" t="e">
@@ -7186,29 +7087,29 @@
       <c r="AO39" s="50"/>
     </row>
     <row r="40" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A40" s="91"/>
-      <c r="B40" s="89"/>
-      <c r="C40" s="183" t="s">
-        <v>48</v>
-      </c>
-      <c r="D40" s="184"/>
-      <c r="E40" s="184"/>
-      <c r="F40" s="184"/>
-      <c r="G40" s="185"/>
+      <c r="A40" s="85"/>
+      <c r="B40" s="83"/>
+      <c r="C40" s="121" t="s">
+        <v>47</v>
+      </c>
+      <c r="D40" s="122"/>
+      <c r="E40" s="122"/>
+      <c r="F40" s="122"/>
+      <c r="G40" s="123"/>
       <c r="H40" s="34"/>
-      <c r="I40" s="57"/>
-      <c r="J40" s="61"/>
-      <c r="K40" s="61"/>
-      <c r="L40" s="61"/>
-      <c r="M40" s="85"/>
-      <c r="N40" s="62"/>
+      <c r="I40" s="56"/>
+      <c r="J40" s="60"/>
+      <c r="K40" s="60"/>
+      <c r="L40" s="60"/>
+      <c r="M40" s="80"/>
+      <c r="N40" s="61"/>
       <c r="O40" s="37"/>
-      <c r="P40" s="146"/>
-      <c r="Q40" s="147"/>
-      <c r="R40" s="147"/>
-      <c r="S40" s="147"/>
-      <c r="T40" s="147"/>
-      <c r="U40" s="77">
+      <c r="P40" s="116"/>
+      <c r="Q40" s="117"/>
+      <c r="R40" s="117"/>
+      <c r="S40" s="117"/>
+      <c r="T40" s="117"/>
+      <c r="U40" s="74">
         <f>(I39*P40)+(J39*Q40)+(K39*R40)+(L39*S40)+(M39*T40)</f>
         <v>0</v>
       </c>
@@ -7218,12 +7119,12 @@
       <c r="Y40" s="42"/>
       <c r="Z40" s="42"/>
       <c r="AA40" s="42"/>
-      <c r="AB40" s="73"/>
-      <c r="AC40" s="78"/>
-      <c r="AD40" s="74"/>
-      <c r="AE40" s="116"/>
+      <c r="AB40" s="70"/>
+      <c r="AC40" s="75"/>
+      <c r="AD40" s="71"/>
+      <c r="AE40" s="100"/>
       <c r="AF40" s="43"/>
-      <c r="AG40" s="65"/>
+      <c r="AG40" s="64"/>
       <c r="AH40" s="44"/>
       <c r="AI40" s="41"/>
       <c r="AJ40" s="45"/>
@@ -7234,29 +7135,29 @@
       <c r="AO40" s="50"/>
     </row>
     <row r="41" spans="1:41" s="22" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A41" s="90"/>
-      <c r="B41" s="88"/>
-      <c r="C41" s="92"/>
-      <c r="D41" s="96"/>
-      <c r="E41" s="103"/>
-      <c r="F41" s="96"/>
-      <c r="G41" s="128"/>
+      <c r="A41" s="84"/>
+      <c r="B41" s="82"/>
+      <c r="C41" s="173"/>
+      <c r="D41" s="172"/>
+      <c r="E41" s="173"/>
+      <c r="F41" s="173"/>
+      <c r="G41" s="113"/>
       <c r="H41" s="34"/>
       <c r="I41" s="35"/>
       <c r="J41" s="36"/>
       <c r="K41" s="36"/>
       <c r="L41" s="36"/>
-      <c r="M41" s="86"/>
-      <c r="N41" s="62">
+      <c r="M41" s="81"/>
+      <c r="N41" s="61">
         <f>SUM(I41:M41)</f>
         <v>0</v>
       </c>
       <c r="O41" s="37"/>
-      <c r="P41" s="144"/>
-      <c r="Q41" s="145"/>
-      <c r="R41" s="145"/>
-      <c r="S41" s="145"/>
-      <c r="T41" s="145"/>
+      <c r="P41" s="114"/>
+      <c r="Q41" s="115"/>
+      <c r="R41" s="115"/>
+      <c r="S41" s="115"/>
+      <c r="T41" s="115"/>
       <c r="U41" s="40">
         <f>ROUND(((P41*I41)+(Q41*J41)+(R41*K41)+(S41*L41)+(T41*M41)),3)</f>
         <v>0</v>
@@ -7270,26 +7171,26 @@
       <c r="Y41" s="42"/>
       <c r="Z41" s="42"/>
       <c r="AA41" s="42"/>
-      <c r="AB41" s="79" t="e">
+      <c r="AB41" s="76" t="e">
         <f>(((((W41*I41)+(X41*J41)+(Y41*K41)+(Z41*L41)+(AA41*M41))/$L$2)))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AC41" s="78" t="e">
+      <c r="AC41" s="75" t="e">
         <f t="shared" ref="AC41" si="20">ROUND(11*AB41,3)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD41" s="75" t="e">
+      <c r="AD41" s="72" t="e">
         <f t="shared" ref="AD41" si="21">IF(AC41&gt;=11,11,AC41)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE41" s="116">
+      <c r="AE41" s="100">
         <f>IF(U42&gt;=94,4,IF(U42&gt;=91,3.9,IF(U42&gt;=88,3.8,IF(U42&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF41" s="43">
         <v>0.3</v>
       </c>
-      <c r="AG41" s="117">
+      <c r="AG41" s="101">
         <v>17</v>
       </c>
       <c r="AH41" s="44" t="e">
@@ -7314,29 +7215,29 @@
       <c r="AO41" s="50"/>
     </row>
     <row r="42" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A42" s="91"/>
-      <c r="B42" s="89"/>
-      <c r="C42" s="183" t="s">
-        <v>48</v>
-      </c>
-      <c r="D42" s="184"/>
-      <c r="E42" s="184"/>
-      <c r="F42" s="184"/>
-      <c r="G42" s="185"/>
+      <c r="A42" s="85"/>
+      <c r="B42" s="83"/>
+      <c r="C42" s="121" t="s">
+        <v>47</v>
+      </c>
+      <c r="D42" s="122"/>
+      <c r="E42" s="122"/>
+      <c r="F42" s="122"/>
+      <c r="G42" s="123"/>
       <c r="H42" s="34"/>
-      <c r="I42" s="57"/>
-      <c r="J42" s="61"/>
-      <c r="K42" s="61"/>
-      <c r="L42" s="61"/>
-      <c r="M42" s="85"/>
-      <c r="N42" s="62"/>
+      <c r="I42" s="56"/>
+      <c r="J42" s="60"/>
+      <c r="K42" s="60"/>
+      <c r="L42" s="60"/>
+      <c r="M42" s="80"/>
+      <c r="N42" s="61"/>
       <c r="O42" s="37"/>
-      <c r="P42" s="146"/>
-      <c r="Q42" s="147"/>
-      <c r="R42" s="147"/>
-      <c r="S42" s="147"/>
-      <c r="T42" s="147"/>
-      <c r="U42" s="77">
+      <c r="P42" s="116"/>
+      <c r="Q42" s="117"/>
+      <c r="R42" s="117"/>
+      <c r="S42" s="117"/>
+      <c r="T42" s="117"/>
+      <c r="U42" s="74">
         <f>(I41*P42)+(J41*Q42)+(K41*R42)+(L41*S42)+(M41*T42)</f>
         <v>0</v>
       </c>
@@ -7346,12 +7247,12 @@
       <c r="Y42" s="42"/>
       <c r="Z42" s="42"/>
       <c r="AA42" s="42"/>
-      <c r="AB42" s="73"/>
-      <c r="AC42" s="78"/>
-      <c r="AD42" s="74"/>
-      <c r="AE42" s="116"/>
+      <c r="AB42" s="70"/>
+      <c r="AC42" s="75"/>
+      <c r="AD42" s="71"/>
+      <c r="AE42" s="100"/>
       <c r="AF42" s="43"/>
-      <c r="AG42" s="65"/>
+      <c r="AG42" s="64"/>
       <c r="AH42" s="44"/>
       <c r="AI42" s="41"/>
       <c r="AJ42" s="45"/>
@@ -7362,29 +7263,29 @@
       <c r="AO42" s="50"/>
     </row>
     <row r="43" spans="1:41" s="22" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A43" s="90"/>
-      <c r="B43" s="88"/>
-      <c r="C43" s="103"/>
-      <c r="D43" s="92"/>
-      <c r="E43" s="96"/>
-      <c r="F43" s="92"/>
-      <c r="G43" s="129"/>
-      <c r="H43" s="56"/>
+      <c r="A43" s="84"/>
+      <c r="B43" s="82"/>
+      <c r="C43" s="173"/>
+      <c r="D43" s="172"/>
+      <c r="E43" s="173"/>
+      <c r="F43" s="173"/>
+      <c r="G43" s="113"/>
+      <c r="H43" s="55"/>
       <c r="I43" s="35"/>
       <c r="J43" s="36"/>
       <c r="K43" s="36"/>
       <c r="L43" s="36"/>
-      <c r="M43" s="86"/>
-      <c r="N43" s="62">
+      <c r="M43" s="81"/>
+      <c r="N43" s="61">
         <f>SUM(I43:M43)</f>
         <v>0</v>
       </c>
       <c r="O43" s="37"/>
-      <c r="P43" s="144"/>
-      <c r="Q43" s="145"/>
-      <c r="R43" s="145"/>
-      <c r="S43" s="145"/>
-      <c r="T43" s="145"/>
+      <c r="P43" s="114"/>
+      <c r="Q43" s="115"/>
+      <c r="R43" s="115"/>
+      <c r="S43" s="115"/>
+      <c r="T43" s="115"/>
       <c r="U43" s="40">
         <f>ROUND(((P43*I43)+(Q43*J43)+(R43*K43)+(S43*L43)+(T43*M43)),3)</f>
         <v>0</v>
@@ -7398,26 +7299,26 @@
       <c r="Y43" s="42"/>
       <c r="Z43" s="42"/>
       <c r="AA43" s="42"/>
-      <c r="AB43" s="73" t="e">
+      <c r="AB43" s="70" t="e">
         <f>(((((W43*I43)+(X43*J43)+(Y43*K43)+(Z43*L43)+(AA43*M43))/$L$2)))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AC43" s="78" t="e">
+      <c r="AC43" s="75" t="e">
         <f t="shared" ref="AC43" si="22">ROUND(11*AB43,3)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD43" s="75" t="e">
+      <c r="AD43" s="72" t="e">
         <f t="shared" ref="AD43" si="23">IF(AC43&gt;=11,11,AC43)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE43" s="116">
+      <c r="AE43" s="100">
         <f>IF(U44&gt;=94,4,IF(U44&gt;=91,3.9,IF(U44&gt;=88,3.8,IF(U44&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF43" s="43">
         <v>0.3</v>
       </c>
-      <c r="AG43" s="117">
+      <c r="AG43" s="101">
         <v>17</v>
       </c>
       <c r="AH43" s="44" t="e">
@@ -7442,29 +7343,29 @@
       <c r="AO43" s="50"/>
     </row>
     <row r="44" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A44" s="91"/>
-      <c r="B44" s="89"/>
-      <c r="C44" s="183" t="s">
-        <v>48</v>
-      </c>
-      <c r="D44" s="184"/>
-      <c r="E44" s="184"/>
-      <c r="F44" s="184"/>
-      <c r="G44" s="185"/>
+      <c r="A44" s="85"/>
+      <c r="B44" s="83"/>
+      <c r="C44" s="121" t="s">
+        <v>47</v>
+      </c>
+      <c r="D44" s="122"/>
+      <c r="E44" s="122"/>
+      <c r="F44" s="122"/>
+      <c r="G44" s="123"/>
       <c r="H44" s="34"/>
-      <c r="I44" s="57"/>
-      <c r="J44" s="61"/>
-      <c r="K44" s="61"/>
-      <c r="L44" s="61"/>
-      <c r="M44" s="85"/>
-      <c r="N44" s="62"/>
+      <c r="I44" s="56"/>
+      <c r="J44" s="60"/>
+      <c r="K44" s="60"/>
+      <c r="L44" s="60"/>
+      <c r="M44" s="80"/>
+      <c r="N44" s="61"/>
       <c r="O44" s="37"/>
-      <c r="P44" s="146"/>
-      <c r="Q44" s="145"/>
-      <c r="R44" s="145"/>
-      <c r="S44" s="147"/>
-      <c r="T44" s="147"/>
-      <c r="U44" s="77">
+      <c r="P44" s="116"/>
+      <c r="Q44" s="115"/>
+      <c r="R44" s="115"/>
+      <c r="S44" s="117"/>
+      <c r="T44" s="117"/>
+      <c r="U44" s="74">
         <f>(I43*P44)+(J43*Q44)+(K43*R44)+(L43*S44)+(M43*T44)</f>
         <v>0</v>
       </c>
@@ -7474,12 +7375,12 @@
       <c r="Y44" s="42"/>
       <c r="Z44" s="42"/>
       <c r="AA44" s="42"/>
-      <c r="AB44" s="73"/>
-      <c r="AC44" s="78"/>
-      <c r="AD44" s="74"/>
-      <c r="AE44" s="116"/>
+      <c r="AB44" s="70"/>
+      <c r="AC44" s="75"/>
+      <c r="AD44" s="71"/>
+      <c r="AE44" s="100"/>
       <c r="AF44" s="43"/>
-      <c r="AG44" s="65"/>
+      <c r="AG44" s="64"/>
       <c r="AH44" s="44"/>
       <c r="AI44" s="41"/>
       <c r="AJ44" s="45"/>
@@ -7490,29 +7391,29 @@
       <c r="AO44" s="50"/>
     </row>
     <row r="45" spans="1:41" s="22" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A45" s="90"/>
-      <c r="B45" s="88"/>
-      <c r="C45" s="96"/>
-      <c r="D45" s="96"/>
-      <c r="E45" s="96"/>
-      <c r="F45" s="96"/>
-      <c r="G45" s="128"/>
+      <c r="A45" s="84"/>
+      <c r="B45" s="82"/>
+      <c r="C45" s="173"/>
+      <c r="D45" s="172"/>
+      <c r="E45" s="173"/>
+      <c r="F45" s="173"/>
+      <c r="G45" s="113"/>
       <c r="H45" s="34"/>
       <c r="I45" s="35"/>
       <c r="J45" s="36"/>
       <c r="K45" s="36"/>
       <c r="L45" s="36"/>
-      <c r="M45" s="86"/>
-      <c r="N45" s="62">
+      <c r="M45" s="81"/>
+      <c r="N45" s="61">
         <f>SUM(I45:M45)</f>
         <v>0</v>
       </c>
       <c r="O45" s="37"/>
-      <c r="P45" s="144"/>
-      <c r="Q45" s="145"/>
-      <c r="R45" s="145"/>
-      <c r="S45" s="145"/>
-      <c r="T45" s="145"/>
+      <c r="P45" s="114"/>
+      <c r="Q45" s="115"/>
+      <c r="R45" s="115"/>
+      <c r="S45" s="115"/>
+      <c r="T45" s="115"/>
       <c r="U45" s="40">
         <f>ROUND(((P45*I45)+(Q45*J45)+(R45*K45)+(S45*L45)+(T45*M45)),3)</f>
         <v>0</v>
@@ -7526,26 +7427,26 @@
       <c r="Y45" s="42"/>
       <c r="Z45" s="42"/>
       <c r="AA45" s="42"/>
-      <c r="AB45" s="73" t="e">
+      <c r="AB45" s="70" t="e">
         <f>(((((W45*I45)+(X45*J45)+(Y45*K45)+(Z45*L45)+(AA45*M45))/$L$2)))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AC45" s="78" t="e">
+      <c r="AC45" s="75" t="e">
         <f t="shared" ref="AC45" si="24">ROUND(11*AB45,3)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD45" s="75" t="e">
+      <c r="AD45" s="72" t="e">
         <f t="shared" ref="AD45" si="25">IF(AC45&gt;=11,11,AC45)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE45" s="116">
+      <c r="AE45" s="100">
         <f>IF(U46&gt;=94,4,IF(U46&gt;=91,3.9,IF(U46&gt;=88,3.8,IF(U46&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF45" s="43">
         <v>0.3</v>
       </c>
-      <c r="AG45" s="117">
+      <c r="AG45" s="101">
         <v>17</v>
       </c>
       <c r="AH45" s="44" t="e">
@@ -7570,29 +7471,29 @@
       <c r="AO45" s="50"/>
     </row>
     <row r="46" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A46" s="91"/>
-      <c r="B46" s="89"/>
-      <c r="C46" s="183" t="s">
-        <v>48</v>
-      </c>
-      <c r="D46" s="184"/>
-      <c r="E46" s="184"/>
-      <c r="F46" s="184"/>
-      <c r="G46" s="185"/>
+      <c r="A46" s="85"/>
+      <c r="B46" s="83"/>
+      <c r="C46" s="121" t="s">
+        <v>47</v>
+      </c>
+      <c r="D46" s="122"/>
+      <c r="E46" s="122"/>
+      <c r="F46" s="122"/>
+      <c r="G46" s="123"/>
       <c r="H46" s="34"/>
-      <c r="I46" s="57"/>
-      <c r="J46" s="61"/>
-      <c r="K46" s="61"/>
-      <c r="L46" s="61"/>
-      <c r="M46" s="85"/>
-      <c r="N46" s="62"/>
+      <c r="I46" s="56"/>
+      <c r="J46" s="60"/>
+      <c r="K46" s="60"/>
+      <c r="L46" s="60"/>
+      <c r="M46" s="80"/>
+      <c r="N46" s="61"/>
       <c r="O46" s="37"/>
-      <c r="P46" s="146"/>
-      <c r="Q46" s="147"/>
-      <c r="R46" s="147"/>
-      <c r="S46" s="147"/>
-      <c r="T46" s="147"/>
-      <c r="U46" s="77">
+      <c r="P46" s="116"/>
+      <c r="Q46" s="117"/>
+      <c r="R46" s="117"/>
+      <c r="S46" s="117"/>
+      <c r="T46" s="117"/>
+      <c r="U46" s="74">
         <f>(I45*P46)+(J45*Q46)+(K45*R46)+(L45*S46)+(M45*T46)</f>
         <v>0</v>
       </c>
@@ -7602,12 +7503,12 @@
       <c r="Y46" s="42"/>
       <c r="Z46" s="42"/>
       <c r="AA46" s="42"/>
-      <c r="AB46" s="73"/>
-      <c r="AC46" s="78"/>
-      <c r="AD46" s="74"/>
-      <c r="AE46" s="116"/>
+      <c r="AB46" s="70"/>
+      <c r="AC46" s="75"/>
+      <c r="AD46" s="71"/>
+      <c r="AE46" s="100"/>
       <c r="AF46" s="43"/>
-      <c r="AG46" s="65"/>
+      <c r="AG46" s="64"/>
       <c r="AH46" s="44"/>
       <c r="AI46" s="41"/>
       <c r="AJ46" s="45"/>
@@ -7618,29 +7519,29 @@
       <c r="AO46" s="50"/>
     </row>
     <row r="47" spans="1:41" s="22" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A47" s="90"/>
-      <c r="B47" s="88"/>
-      <c r="C47" s="96"/>
-      <c r="D47" s="96"/>
-      <c r="E47" s="92"/>
-      <c r="F47" s="96"/>
-      <c r="G47" s="120"/>
+      <c r="A47" s="84"/>
+      <c r="B47" s="82"/>
+      <c r="C47" s="173"/>
+      <c r="D47" s="172"/>
+      <c r="E47" s="173"/>
+      <c r="F47" s="173"/>
+      <c r="G47" s="113"/>
       <c r="H47" s="34"/>
       <c r="I47" s="35"/>
       <c r="J47" s="36"/>
       <c r="K47" s="36"/>
-      <c r="L47" s="61"/>
-      <c r="M47" s="86"/>
-      <c r="N47" s="62">
+      <c r="L47" s="60"/>
+      <c r="M47" s="81"/>
+      <c r="N47" s="61">
         <f>SUM(I47:M47)</f>
         <v>0</v>
       </c>
       <c r="O47" s="37"/>
-      <c r="P47" s="144"/>
-      <c r="Q47" s="145"/>
-      <c r="R47" s="145"/>
-      <c r="S47" s="145"/>
-      <c r="T47" s="145"/>
+      <c r="P47" s="114"/>
+      <c r="Q47" s="115"/>
+      <c r="R47" s="115"/>
+      <c r="S47" s="115"/>
+      <c r="T47" s="115"/>
       <c r="U47" s="40">
         <f>ROUND(((P47*I47)+(Q47*J47)+(R47*K47)+(S47*L47)+(T47*M47)),3)</f>
         <v>0</v>
@@ -7654,26 +7555,26 @@
       <c r="Y47" s="42"/>
       <c r="Z47" s="42"/>
       <c r="AA47" s="42"/>
-      <c r="AB47" s="73" t="e">
+      <c r="AB47" s="70" t="e">
         <f>(((((W47*I47)+(X47*J47)+(Y47*K47)+(Z47*L47)+(AA47*M47))/$L$2)))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AC47" s="78" t="e">
+      <c r="AC47" s="75" t="e">
         <f>ROUND(11*AB47,3)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD47" s="75" t="e">
+      <c r="AD47" s="72" t="e">
         <f>IF(AC47&gt;=11,11,AC47)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE47" s="116">
+      <c r="AE47" s="100">
         <f>IF(U48&gt;=94,4,IF(U48&gt;=91,3.9,IF(U48&gt;=88,3.8,IF(U48&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF47" s="43">
         <v>0.3</v>
       </c>
-      <c r="AG47" s="117">
+      <c r="AG47" s="101">
         <v>17</v>
       </c>
       <c r="AH47" s="44" t="e">
@@ -7698,29 +7599,29 @@
       <c r="AO47" s="50"/>
     </row>
     <row r="48" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A48" s="91"/>
-      <c r="B48" s="89"/>
-      <c r="C48" s="183" t="s">
-        <v>48</v>
-      </c>
-      <c r="D48" s="184"/>
-      <c r="E48" s="184"/>
-      <c r="F48" s="184"/>
-      <c r="G48" s="185"/>
+      <c r="A48" s="85"/>
+      <c r="B48" s="83"/>
+      <c r="C48" s="121" t="s">
+        <v>47</v>
+      </c>
+      <c r="D48" s="122"/>
+      <c r="E48" s="122"/>
+      <c r="F48" s="122"/>
+      <c r="G48" s="123"/>
       <c r="H48" s="34"/>
-      <c r="I48" s="57"/>
-      <c r="J48" s="61"/>
-      <c r="K48" s="61"/>
-      <c r="L48" s="61"/>
-      <c r="M48" s="85"/>
-      <c r="N48" s="62"/>
+      <c r="I48" s="56"/>
+      <c r="J48" s="60"/>
+      <c r="K48" s="60"/>
+      <c r="L48" s="60"/>
+      <c r="M48" s="80"/>
+      <c r="N48" s="61"/>
       <c r="O48" s="37"/>
-      <c r="P48" s="146"/>
-      <c r="Q48" s="145"/>
-      <c r="R48" s="145"/>
-      <c r="S48" s="147"/>
-      <c r="T48" s="147"/>
-      <c r="U48" s="77">
+      <c r="P48" s="116"/>
+      <c r="Q48" s="115"/>
+      <c r="R48" s="115"/>
+      <c r="S48" s="117"/>
+      <c r="T48" s="117"/>
+      <c r="U48" s="74">
         <f>(I47*P48)+(J47*Q48)+(K47*R48)+(L47*S48)+(M47*T48)</f>
         <v>0</v>
       </c>
@@ -7730,12 +7631,12 @@
       <c r="Y48" s="42"/>
       <c r="Z48" s="42"/>
       <c r="AA48" s="42"/>
-      <c r="AB48" s="73"/>
-      <c r="AC48" s="78"/>
-      <c r="AD48" s="74"/>
-      <c r="AE48" s="116"/>
+      <c r="AB48" s="70"/>
+      <c r="AC48" s="75"/>
+      <c r="AD48" s="71"/>
+      <c r="AE48" s="100"/>
       <c r="AF48" s="43"/>
-      <c r="AG48" s="65"/>
+      <c r="AG48" s="64"/>
       <c r="AH48" s="44"/>
       <c r="AI48" s="41"/>
       <c r="AJ48" s="45"/>
@@ -7746,29 +7647,29 @@
       <c r="AO48" s="50"/>
     </row>
     <row r="49" spans="1:41" s="22" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A49" s="90"/>
-      <c r="B49" s="88"/>
-      <c r="C49" s="96"/>
-      <c r="D49" s="92"/>
-      <c r="E49" s="92"/>
-      <c r="F49" s="92"/>
-      <c r="G49" s="120"/>
+      <c r="A49" s="84"/>
+      <c r="B49" s="82"/>
+      <c r="C49" s="173"/>
+      <c r="D49" s="172"/>
+      <c r="E49" s="173"/>
+      <c r="F49" s="173"/>
+      <c r="G49" s="113"/>
       <c r="H49" s="34"/>
       <c r="I49" s="36"/>
       <c r="J49" s="35"/>
       <c r="K49" s="36"/>
       <c r="L49" s="36"/>
-      <c r="M49" s="86"/>
-      <c r="N49" s="62">
+      <c r="M49" s="81"/>
+      <c r="N49" s="61">
         <f>SUM(I49:M49)</f>
         <v>0</v>
       </c>
       <c r="O49" s="37"/>
-      <c r="P49" s="144"/>
-      <c r="Q49" s="145"/>
-      <c r="R49" s="145"/>
-      <c r="S49" s="145"/>
-      <c r="T49" s="145"/>
+      <c r="P49" s="114"/>
+      <c r="Q49" s="115"/>
+      <c r="R49" s="115"/>
+      <c r="S49" s="115"/>
+      <c r="T49" s="115"/>
       <c r="U49" s="40">
         <f>ROUND(((P49*I49)+(Q49*J49)+(R49*K49)+(S49*L49)+(T49*M49)),3)</f>
         <v>0</v>
@@ -7782,26 +7683,26 @@
       <c r="Y49" s="42"/>
       <c r="Z49" s="42"/>
       <c r="AA49" s="42"/>
-      <c r="AB49" s="73" t="e">
+      <c r="AB49" s="70" t="e">
         <f>(((((W49*I49)+(X49*J49)+(Y49*K49)+(Z49*L49)+(AA49*M49))/$L$2)))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AC49" s="78" t="e">
+      <c r="AC49" s="75" t="e">
         <f t="shared" ref="AC49" si="26">ROUND(11*AB49,3)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD49" s="75" t="e">
+      <c r="AD49" s="72" t="e">
         <f t="shared" ref="AD49" si="27">IF(AC49&gt;=11,11,AC49)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE49" s="116">
+      <c r="AE49" s="100">
         <f>IF(U50&gt;=94,4,IF(U50&gt;=91,3.9,IF(U50&gt;=88,3.8,IF(U50&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF49" s="43">
         <v>0.3</v>
       </c>
-      <c r="AG49" s="117">
+      <c r="AG49" s="101">
         <v>17</v>
       </c>
       <c r="AH49" s="44" t="e">
@@ -7826,29 +7727,29 @@
       <c r="AO49" s="50"/>
     </row>
     <row r="50" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A50" s="91"/>
-      <c r="B50" s="89"/>
-      <c r="C50" s="183" t="s">
-        <v>48</v>
-      </c>
-      <c r="D50" s="184"/>
-      <c r="E50" s="184"/>
-      <c r="F50" s="184"/>
-      <c r="G50" s="185"/>
+      <c r="A50" s="85"/>
+      <c r="B50" s="83"/>
+      <c r="C50" s="121" t="s">
+        <v>47</v>
+      </c>
+      <c r="D50" s="122"/>
+      <c r="E50" s="122"/>
+      <c r="F50" s="122"/>
+      <c r="G50" s="123"/>
       <c r="H50" s="34"/>
-      <c r="I50" s="57"/>
-      <c r="J50" s="61"/>
-      <c r="K50" s="61"/>
-      <c r="L50" s="61"/>
-      <c r="M50" s="85"/>
-      <c r="N50" s="62"/>
+      <c r="I50" s="56"/>
+      <c r="J50" s="60"/>
+      <c r="K50" s="60"/>
+      <c r="L50" s="60"/>
+      <c r="M50" s="80"/>
+      <c r="N50" s="61"/>
       <c r="O50" s="37"/>
-      <c r="P50" s="146"/>
-      <c r="Q50" s="147"/>
-      <c r="R50" s="147"/>
-      <c r="S50" s="147"/>
-      <c r="T50" s="147"/>
-      <c r="U50" s="77">
+      <c r="P50" s="116"/>
+      <c r="Q50" s="117"/>
+      <c r="R50" s="117"/>
+      <c r="S50" s="117"/>
+      <c r="T50" s="117"/>
+      <c r="U50" s="74">
         <f>(I49*P50)+(J49*Q50)+(K49*R50)+(L49*S50)+(M49*T50)</f>
         <v>0</v>
       </c>
@@ -7858,12 +7759,12 @@
       <c r="Y50" s="42"/>
       <c r="Z50" s="42"/>
       <c r="AA50" s="42"/>
-      <c r="AB50" s="73"/>
-      <c r="AC50" s="78"/>
-      <c r="AD50" s="74"/>
-      <c r="AE50" s="116"/>
+      <c r="AB50" s="70"/>
+      <c r="AC50" s="75"/>
+      <c r="AD50" s="71"/>
+      <c r="AE50" s="100"/>
       <c r="AF50" s="43"/>
-      <c r="AG50" s="65"/>
+      <c r="AG50" s="64"/>
       <c r="AH50" s="44"/>
       <c r="AI50" s="41"/>
       <c r="AJ50" s="45"/>
@@ -7874,31 +7775,29 @@
       <c r="AO50" s="50"/>
     </row>
     <row r="51" spans="1:41" s="22" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A51" s="90"/>
-      <c r="B51" s="88"/>
-      <c r="C51" s="100"/>
-      <c r="D51" s="102"/>
-      <c r="E51" s="102"/>
-      <c r="F51" s="92"/>
-      <c r="G51" s="127"/>
-      <c r="H51" s="58" t="s">
-        <v>3</v>
-      </c>
+      <c r="A51" s="84"/>
+      <c r="B51" s="82"/>
+      <c r="C51" s="173"/>
+      <c r="D51" s="172"/>
+      <c r="E51" s="173"/>
+      <c r="F51" s="173"/>
+      <c r="G51" s="113"/>
+      <c r="H51" s="57"/>
       <c r="I51" s="35"/>
       <c r="J51" s="36"/>
       <c r="K51" s="36"/>
       <c r="L51" s="36"/>
-      <c r="M51" s="86"/>
-      <c r="N51" s="62">
+      <c r="M51" s="81"/>
+      <c r="N51" s="61">
         <f>SUM(I51:M51)</f>
         <v>0</v>
       </c>
       <c r="O51" s="37"/>
-      <c r="P51" s="144"/>
-      <c r="Q51" s="145"/>
-      <c r="R51" s="145"/>
-      <c r="S51" s="145"/>
-      <c r="T51" s="145"/>
+      <c r="P51" s="114"/>
+      <c r="Q51" s="115"/>
+      <c r="R51" s="115"/>
+      <c r="S51" s="115"/>
+      <c r="T51" s="115"/>
       <c r="U51" s="40">
         <f>ROUND(((P51*I51)+(Q51*J51)+(R51*K51)+(S51*L51)+(T51*M51)),3)</f>
         <v>0</v>
@@ -7912,26 +7811,26 @@
       <c r="Y51" s="42"/>
       <c r="Z51" s="42"/>
       <c r="AA51" s="42"/>
-      <c r="AB51" s="73" t="e">
+      <c r="AB51" s="70" t="e">
         <f>(((((W51*I51)+(X51*J51)+(Y51*K51)+(Z51*L51)+(AA51*M51))/$L$2)))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AC51" s="78" t="e">
+      <c r="AC51" s="75" t="e">
         <f t="shared" ref="AC51" si="28">ROUND(11*AB51,3)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD51" s="75" t="e">
+      <c r="AD51" s="72" t="e">
         <f t="shared" ref="AD51" si="29">IF(AC51&gt;=11,11,AC51)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE51" s="116">
+      <c r="AE51" s="100">
         <f>IF(U52&gt;=94,4,IF(U52&gt;=91,3.9,IF(U52&gt;=88,3.8,IF(U52&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF51" s="43">
         <v>0.3</v>
       </c>
-      <c r="AG51" s="117">
+      <c r="AG51" s="101">
         <v>17</v>
       </c>
       <c r="AH51" s="44" t="e">
@@ -7956,29 +7855,29 @@
       <c r="AO51" s="50"/>
     </row>
     <row r="52" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A52" s="91"/>
-      <c r="B52" s="89"/>
-      <c r="C52" s="183" t="s">
-        <v>48</v>
-      </c>
-      <c r="D52" s="184"/>
-      <c r="E52" s="184"/>
-      <c r="F52" s="184"/>
-      <c r="G52" s="185"/>
+      <c r="A52" s="85"/>
+      <c r="B52" s="83"/>
+      <c r="C52" s="121" t="s">
+        <v>47</v>
+      </c>
+      <c r="D52" s="122"/>
+      <c r="E52" s="122"/>
+      <c r="F52" s="122"/>
+      <c r="G52" s="123"/>
       <c r="H52" s="34"/>
-      <c r="I52" s="57"/>
-      <c r="J52" s="61"/>
-      <c r="K52" s="61"/>
-      <c r="L52" s="61"/>
-      <c r="M52" s="85"/>
-      <c r="N52" s="62"/>
+      <c r="I52" s="56"/>
+      <c r="J52" s="60"/>
+      <c r="K52" s="60"/>
+      <c r="L52" s="60"/>
+      <c r="M52" s="80"/>
+      <c r="N52" s="61"/>
       <c r="O52" s="37"/>
-      <c r="P52" s="146"/>
-      <c r="Q52" s="145"/>
-      <c r="R52" s="147"/>
-      <c r="S52" s="147"/>
-      <c r="T52" s="147"/>
-      <c r="U52" s="77">
+      <c r="P52" s="116"/>
+      <c r="Q52" s="115"/>
+      <c r="R52" s="117"/>
+      <c r="S52" s="117"/>
+      <c r="T52" s="117"/>
+      <c r="U52" s="74">
         <f>(I51*P52)+(J51*Q52)+(K51*R52)+(L51*S52)+(M51*T52)</f>
         <v>0</v>
       </c>
@@ -7988,12 +7887,12 @@
       <c r="Y52" s="42"/>
       <c r="Z52" s="42"/>
       <c r="AA52" s="42"/>
-      <c r="AB52" s="73"/>
-      <c r="AC52" s="78"/>
-      <c r="AD52" s="74"/>
-      <c r="AE52" s="116"/>
+      <c r="AB52" s="70"/>
+      <c r="AC52" s="75"/>
+      <c r="AD52" s="71"/>
+      <c r="AE52" s="100"/>
       <c r="AF52" s="43"/>
-      <c r="AG52" s="65"/>
+      <c r="AG52" s="64"/>
       <c r="AH52" s="44"/>
       <c r="AI52" s="41"/>
       <c r="AJ52" s="45"/>
@@ -8004,31 +7903,29 @@
       <c r="AO52" s="50"/>
     </row>
     <row r="53" spans="1:41" s="22" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A53" s="90"/>
-      <c r="B53" s="88"/>
-      <c r="C53" s="87"/>
-      <c r="D53" s="100"/>
-      <c r="E53" s="102"/>
-      <c r="F53" s="92"/>
-      <c r="G53" s="107"/>
-      <c r="H53" s="58" t="s">
-        <v>3</v>
-      </c>
+      <c r="A53" s="84"/>
+      <c r="B53" s="82"/>
+      <c r="C53" s="173"/>
+      <c r="D53" s="172"/>
+      <c r="E53" s="173"/>
+      <c r="F53" s="173"/>
+      <c r="G53" s="113"/>
+      <c r="H53" s="57"/>
       <c r="I53" s="35"/>
       <c r="J53" s="36"/>
       <c r="K53" s="36"/>
       <c r="L53" s="36"/>
-      <c r="M53" s="86"/>
-      <c r="N53" s="62">
+      <c r="M53" s="81"/>
+      <c r="N53" s="61">
         <f>SUM(I53:M53)</f>
         <v>0</v>
       </c>
       <c r="O53" s="37"/>
-      <c r="P53" s="144"/>
-      <c r="Q53" s="145"/>
-      <c r="R53" s="145"/>
-      <c r="S53" s="145"/>
-      <c r="T53" s="145"/>
+      <c r="P53" s="114"/>
+      <c r="Q53" s="115"/>
+      <c r="R53" s="115"/>
+      <c r="S53" s="115"/>
+      <c r="T53" s="115"/>
       <c r="U53" s="40">
         <f>ROUND(((P53*I53)+(Q53*J53)+(R53*K53)+(S53*L53)+(T53*M53)),3)</f>
         <v>0</v>
@@ -8042,26 +7939,26 @@
       <c r="Y53" s="42"/>
       <c r="Z53" s="42"/>
       <c r="AA53" s="42"/>
-      <c r="AB53" s="73" t="e">
+      <c r="AB53" s="70" t="e">
         <f>(((((W53*I53)+(X53*J53)+(Y53*K53)+(Z53*L53)+(AA53*M53))/$L$2)))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AC53" s="78" t="e">
+      <c r="AC53" s="75" t="e">
         <f t="shared" ref="AC53" si="30">ROUND(11*AB53,3)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD53" s="75" t="e">
+      <c r="AD53" s="72" t="e">
         <f t="shared" ref="AD53" si="31">IF(AC53&gt;=11,11,AC53)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE53" s="116">
+      <c r="AE53" s="100">
         <f>IF(U54&gt;=94,4,IF(U54&gt;=91,3.9,IF(U54&gt;=88,3.8,IF(U54&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF53" s="43">
         <v>0.3</v>
       </c>
-      <c r="AG53" s="117">
+      <c r="AG53" s="101">
         <v>17</v>
       </c>
       <c r="AH53" s="44" t="e">
@@ -8086,29 +7983,29 @@
       <c r="AO53" s="50"/>
     </row>
     <row r="54" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A54" s="91"/>
-      <c r="B54" s="89"/>
-      <c r="C54" s="183" t="s">
-        <v>48</v>
-      </c>
-      <c r="D54" s="184"/>
-      <c r="E54" s="184"/>
-      <c r="F54" s="184"/>
-      <c r="G54" s="185"/>
+      <c r="A54" s="85"/>
+      <c r="B54" s="83"/>
+      <c r="C54" s="121" t="s">
+        <v>47</v>
+      </c>
+      <c r="D54" s="122"/>
+      <c r="E54" s="122"/>
+      <c r="F54" s="122"/>
+      <c r="G54" s="123"/>
       <c r="H54" s="34"/>
-      <c r="I54" s="57"/>
-      <c r="J54" s="61"/>
-      <c r="K54" s="61"/>
-      <c r="L54" s="61"/>
-      <c r="M54" s="85"/>
-      <c r="N54" s="62"/>
+      <c r="I54" s="56"/>
+      <c r="J54" s="60"/>
+      <c r="K54" s="60"/>
+      <c r="L54" s="60"/>
+      <c r="M54" s="80"/>
+      <c r="N54" s="61"/>
       <c r="O54" s="37"/>
-      <c r="P54" s="146"/>
-      <c r="Q54" s="146"/>
-      <c r="R54" s="147"/>
-      <c r="S54" s="147"/>
-      <c r="T54" s="147"/>
-      <c r="U54" s="77">
+      <c r="P54" s="116"/>
+      <c r="Q54" s="116"/>
+      <c r="R54" s="117"/>
+      <c r="S54" s="117"/>
+      <c r="T54" s="117"/>
+      <c r="U54" s="74">
         <f>(I53*P54)+(J53*Q54)+(K53*R54)+(L53*S54)+(M53*T54)</f>
         <v>0</v>
       </c>
@@ -8118,12 +8015,12 @@
       <c r="Y54" s="42"/>
       <c r="Z54" s="42"/>
       <c r="AA54" s="42"/>
-      <c r="AB54" s="73"/>
-      <c r="AC54" s="78"/>
-      <c r="AD54" s="74"/>
-      <c r="AE54" s="116"/>
+      <c r="AB54" s="70"/>
+      <c r="AC54" s="75"/>
+      <c r="AD54" s="71"/>
+      <c r="AE54" s="100"/>
       <c r="AF54" s="43"/>
-      <c r="AG54" s="65"/>
+      <c r="AG54" s="64"/>
       <c r="AH54" s="44"/>
       <c r="AI54" s="41"/>
       <c r="AJ54" s="45"/>
@@ -8134,31 +8031,29 @@
       <c r="AO54" s="50"/>
     </row>
     <row r="55" spans="1:41" s="22" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A55" s="90"/>
-      <c r="B55" s="88"/>
-      <c r="C55" s="96"/>
-      <c r="D55" s="102"/>
-      <c r="E55" s="96"/>
-      <c r="F55" s="92"/>
-      <c r="G55" s="120"/>
-      <c r="H55" s="58" t="s">
-        <v>3</v>
-      </c>
+      <c r="A55" s="84"/>
+      <c r="B55" s="82"/>
+      <c r="C55" s="173"/>
+      <c r="D55" s="172"/>
+      <c r="E55" s="173"/>
+      <c r="F55" s="173"/>
+      <c r="G55" s="113"/>
+      <c r="H55" s="57"/>
       <c r="I55" s="35"/>
       <c r="J55" s="36"/>
       <c r="K55" s="36"/>
-      <c r="L55" s="61"/>
-      <c r="M55" s="86"/>
-      <c r="N55" s="62">
+      <c r="L55" s="60"/>
+      <c r="M55" s="81"/>
+      <c r="N55" s="61">
         <f>SUM(I55:M55)</f>
         <v>0</v>
       </c>
       <c r="O55" s="37"/>
-      <c r="P55" s="144"/>
-      <c r="Q55" s="145"/>
-      <c r="R55" s="145"/>
-      <c r="S55" s="145"/>
-      <c r="T55" s="145"/>
+      <c r="P55" s="114"/>
+      <c r="Q55" s="115"/>
+      <c r="R55" s="115"/>
+      <c r="S55" s="115"/>
+      <c r="T55" s="115"/>
       <c r="U55" s="40">
         <f>ROUND(((P55*I55)+(Q55*J55)+(R55*K55)+(S55*L55)+(T55*M55)),3)</f>
         <v>0</v>
@@ -8172,26 +8067,26 @@
       <c r="Y55" s="42"/>
       <c r="Z55" s="42"/>
       <c r="AA55" s="42"/>
-      <c r="AB55" s="73" t="e">
+      <c r="AB55" s="70" t="e">
         <f>(((((W55*I55)+(X55*J55)+(Y55*K55)+(Z55*L55)+(AA55*M55))/$L$2)))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AC55" s="78" t="e">
+      <c r="AC55" s="75" t="e">
         <f t="shared" ref="AC55" si="32">ROUND(11*AB55,3)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD55" s="75" t="e">
+      <c r="AD55" s="72" t="e">
         <f t="shared" ref="AD55" si="33">IF(AC55&gt;=11,11,AC55)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE55" s="116">
+      <c r="AE55" s="100">
         <f>IF(U56&gt;=94,4,IF(U56&gt;=91,3.9,IF(U56&gt;=88,3.8,IF(U56&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF55" s="43">
         <v>0.3</v>
       </c>
-      <c r="AG55" s="117">
+      <c r="AG55" s="101">
         <v>17</v>
       </c>
       <c r="AH55" s="44" t="e">
@@ -8216,29 +8111,29 @@
       <c r="AO55" s="50"/>
     </row>
     <row r="56" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A56" s="91"/>
-      <c r="B56" s="89"/>
-      <c r="C56" s="183" t="s">
-        <v>48</v>
-      </c>
-      <c r="D56" s="184"/>
-      <c r="E56" s="184"/>
-      <c r="F56" s="184"/>
-      <c r="G56" s="185"/>
+      <c r="A56" s="85"/>
+      <c r="B56" s="83"/>
+      <c r="C56" s="121" t="s">
+        <v>47</v>
+      </c>
+      <c r="D56" s="122"/>
+      <c r="E56" s="122"/>
+      <c r="F56" s="122"/>
+      <c r="G56" s="123"/>
       <c r="H56" s="34"/>
-      <c r="I56" s="57"/>
-      <c r="J56" s="61"/>
-      <c r="K56" s="61"/>
-      <c r="L56" s="61"/>
-      <c r="M56" s="85"/>
-      <c r="N56" s="62"/>
+      <c r="I56" s="56"/>
+      <c r="J56" s="60"/>
+      <c r="K56" s="60"/>
+      <c r="L56" s="60"/>
+      <c r="M56" s="80"/>
+      <c r="N56" s="61"/>
       <c r="O56" s="37"/>
-      <c r="P56" s="146"/>
-      <c r="Q56" s="146"/>
-      <c r="R56" s="146"/>
-      <c r="S56" s="147"/>
-      <c r="T56" s="147"/>
-      <c r="U56" s="77">
+      <c r="P56" s="116"/>
+      <c r="Q56" s="116"/>
+      <c r="R56" s="116"/>
+      <c r="S56" s="117"/>
+      <c r="T56" s="117"/>
+      <c r="U56" s="74">
         <f>(I55*P56)+(J55*Q56)+(K55*R56)+(L55*S56)+(M55*T56)</f>
         <v>0</v>
       </c>
@@ -8248,12 +8143,12 @@
       <c r="Y56" s="42"/>
       <c r="Z56" s="42"/>
       <c r="AA56" s="42"/>
-      <c r="AB56" s="73"/>
-      <c r="AC56" s="78"/>
-      <c r="AD56" s="74"/>
-      <c r="AE56" s="116"/>
+      <c r="AB56" s="70"/>
+      <c r="AC56" s="75"/>
+      <c r="AD56" s="71"/>
+      <c r="AE56" s="100"/>
       <c r="AF56" s="43"/>
-      <c r="AG56" s="65"/>
+      <c r="AG56" s="64"/>
       <c r="AH56" s="44"/>
       <c r="AI56" s="41"/>
       <c r="AJ56" s="45"/>
@@ -8264,29 +8159,29 @@
       <c r="AO56" s="50"/>
     </row>
     <row r="57" spans="1:41" s="22" customFormat="1" ht="51.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A57" s="90"/>
-      <c r="B57" s="88"/>
-      <c r="C57" s="52"/>
-      <c r="D57" s="92"/>
-      <c r="E57" s="130"/>
-      <c r="F57" s="92"/>
-      <c r="G57" s="128"/>
+      <c r="A57" s="84"/>
+      <c r="B57" s="82"/>
+      <c r="C57" s="173"/>
+      <c r="D57" s="172"/>
+      <c r="E57" s="173"/>
+      <c r="F57" s="173"/>
+      <c r="G57" s="113"/>
       <c r="H57" s="34"/>
-      <c r="I57" s="94"/>
-      <c r="J57" s="95"/>
-      <c r="K57" s="95"/>
-      <c r="L57" s="95"/>
-      <c r="M57" s="122"/>
-      <c r="N57" s="121">
+      <c r="I57" s="86"/>
+      <c r="J57" s="87"/>
+      <c r="K57" s="87"/>
+      <c r="L57" s="87"/>
+      <c r="M57" s="105"/>
+      <c r="N57" s="104">
         <f>SUM(I57:M57)</f>
         <v>0</v>
       </c>
       <c r="O57" s="37"/>
-      <c r="P57" s="144"/>
-      <c r="Q57" s="144"/>
-      <c r="R57" s="145"/>
-      <c r="S57" s="145"/>
-      <c r="T57" s="145"/>
+      <c r="P57" s="114"/>
+      <c r="Q57" s="114"/>
+      <c r="R57" s="115"/>
+      <c r="S57" s="115"/>
+      <c r="T57" s="115"/>
       <c r="U57" s="40">
         <f>ROUND(((P57*I57)+(Q57*J57)+(R57*K57)+(S57*L57)+(T57*M57)),3)</f>
         <v>0</v>
@@ -8300,26 +8195,26 @@
       <c r="Y57" s="42"/>
       <c r="Z57" s="42"/>
       <c r="AA57" s="42"/>
-      <c r="AB57" s="73" t="e">
+      <c r="AB57" s="70" t="e">
         <f>(((((W57*I57)+(X57*J57)+(Y57*K57)+(Z57*L57)+(AA57*M57))/$L$2)))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AC57" s="78" t="e">
+      <c r="AC57" s="75" t="e">
         <f t="shared" ref="AC57" si="34">ROUND(11*AB57,3)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD57" s="75" t="e">
+      <c r="AD57" s="72" t="e">
         <f t="shared" ref="AD57" si="35">IF(AC57&gt;=11,11,AC57)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE57" s="116">
+      <c r="AE57" s="100">
         <f>IF(U58&gt;=94,4,IF(U58&gt;=91,3.9,IF(U58&gt;=88,3.8,IF(U58&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF57" s="43">
         <v>0.3</v>
       </c>
-      <c r="AG57" s="117">
+      <c r="AG57" s="101">
         <v>17</v>
       </c>
       <c r="AH57" s="44" t="e">
@@ -8338,29 +8233,29 @@
       <c r="AO57" s="50"/>
     </row>
     <row r="58" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A58" s="91"/>
-      <c r="B58" s="89"/>
-      <c r="C58" s="183" t="s">
-        <v>48</v>
-      </c>
-      <c r="D58" s="184"/>
-      <c r="E58" s="184"/>
-      <c r="F58" s="184"/>
-      <c r="G58" s="185"/>
-      <c r="H58" s="97"/>
-      <c r="I58" s="98"/>
-      <c r="J58" s="99"/>
-      <c r="K58" s="99"/>
-      <c r="L58" s="99"/>
-      <c r="M58" s="123"/>
-      <c r="N58" s="121"/>
+      <c r="A58" s="85"/>
+      <c r="B58" s="83"/>
+      <c r="C58" s="121" t="s">
+        <v>47</v>
+      </c>
+      <c r="D58" s="122"/>
+      <c r="E58" s="122"/>
+      <c r="F58" s="122"/>
+      <c r="G58" s="123"/>
+      <c r="H58" s="88"/>
+      <c r="I58" s="89"/>
+      <c r="J58" s="90"/>
+      <c r="K58" s="90"/>
+      <c r="L58" s="90"/>
+      <c r="M58" s="106"/>
+      <c r="N58" s="104"/>
       <c r="O58" s="37"/>
-      <c r="P58" s="147"/>
-      <c r="Q58" s="147"/>
-      <c r="R58" s="147"/>
-      <c r="S58" s="147"/>
-      <c r="T58" s="147"/>
-      <c r="U58" s="77">
+      <c r="P58" s="117"/>
+      <c r="Q58" s="117"/>
+      <c r="R58" s="117"/>
+      <c r="S58" s="117"/>
+      <c r="T58" s="117"/>
+      <c r="U58" s="74">
         <f>(I57*P58)+(J57*Q58)+(K57*R58)+(L57*S58)+(M57*T58)</f>
         <v>0</v>
       </c>
@@ -8370,12 +8265,12 @@
       <c r="Y58" s="42"/>
       <c r="Z58" s="42"/>
       <c r="AA58" s="42"/>
-      <c r="AB58" s="73"/>
-      <c r="AC58" s="78"/>
-      <c r="AD58" s="74"/>
-      <c r="AE58" s="116"/>
+      <c r="AB58" s="70"/>
+      <c r="AC58" s="75"/>
+      <c r="AD58" s="71"/>
+      <c r="AE58" s="100"/>
       <c r="AF58" s="43"/>
-      <c r="AG58" s="65"/>
+      <c r="AG58" s="64"/>
       <c r="AH58" s="44"/>
       <c r="AI58" s="41"/>
       <c r="AJ58" s="45"/>
@@ -8386,29 +8281,29 @@
       <c r="AO58" s="50"/>
     </row>
     <row r="59" spans="1:41" s="22" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A59" s="90"/>
-      <c r="B59" s="88"/>
-      <c r="C59" s="103"/>
-      <c r="D59" s="92"/>
-      <c r="E59" s="130"/>
-      <c r="F59" s="92"/>
-      <c r="G59" s="128"/>
+      <c r="A59" s="84"/>
+      <c r="B59" s="82"/>
+      <c r="C59" s="173"/>
+      <c r="D59" s="172"/>
+      <c r="E59" s="173"/>
+      <c r="F59" s="173"/>
+      <c r="G59" s="113"/>
       <c r="H59" s="34"/>
       <c r="I59" s="35"/>
       <c r="J59" s="36"/>
       <c r="K59" s="36"/>
       <c r="L59" s="36"/>
-      <c r="M59" s="86"/>
-      <c r="N59" s="62">
+      <c r="M59" s="81"/>
+      <c r="N59" s="61">
         <f>SUM(I59:M59)</f>
         <v>0</v>
       </c>
       <c r="O59" s="37"/>
-      <c r="P59" s="144"/>
-      <c r="Q59" s="145"/>
-      <c r="R59" s="145"/>
-      <c r="S59" s="145"/>
-      <c r="T59" s="145"/>
+      <c r="P59" s="114"/>
+      <c r="Q59" s="115"/>
+      <c r="R59" s="115"/>
+      <c r="S59" s="115"/>
+      <c r="T59" s="115"/>
       <c r="U59" s="40">
         <f>ROUND(((P59*I59)+(Q59*J59)+(R59*K59)+(S59*L59)+(T59*M59)),3)</f>
         <v>0</v>
@@ -8422,26 +8317,26 @@
       <c r="Y59" s="42"/>
       <c r="Z59" s="42"/>
       <c r="AA59" s="42"/>
-      <c r="AB59" s="73" t="e">
+      <c r="AB59" s="70" t="e">
         <f>(((((W59*I59)+(X59*J59)+(Y59*K59)+(Z59*L59)+(AA59*M59))/$L$2)))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AC59" s="78" t="e">
+      <c r="AC59" s="75" t="e">
         <f t="shared" ref="AC59" si="36">ROUND(11*AB59,3)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD59" s="75" t="e">
+      <c r="AD59" s="72" t="e">
         <f t="shared" ref="AD59" si="37">IF(AC59&gt;=11,11,AC59)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE59" s="116">
+      <c r="AE59" s="100">
         <f>IF(U60&gt;=94,4,IF(U60&gt;=91,3.9,IF(U60&gt;=88,3.8,IF(U60&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF59" s="43">
         <v>0.2</v>
       </c>
-      <c r="AG59" s="117">
+      <c r="AG59" s="101">
         <v>17</v>
       </c>
       <c r="AH59" s="44" t="e">
@@ -8466,29 +8361,29 @@
       <c r="AO59" s="50"/>
     </row>
     <row r="60" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A60" s="91"/>
-      <c r="B60" s="89"/>
-      <c r="C60" s="183" t="s">
-        <v>48</v>
-      </c>
-      <c r="D60" s="184"/>
-      <c r="E60" s="184"/>
-      <c r="F60" s="184"/>
-      <c r="G60" s="185"/>
+      <c r="A60" s="85"/>
+      <c r="B60" s="83"/>
+      <c r="C60" s="121" t="s">
+        <v>47</v>
+      </c>
+      <c r="D60" s="122"/>
+      <c r="E60" s="122"/>
+      <c r="F60" s="122"/>
+      <c r="G60" s="123"/>
       <c r="H60" s="34"/>
-      <c r="I60" s="57"/>
-      <c r="J60" s="61"/>
-      <c r="K60" s="61"/>
-      <c r="L60" s="61"/>
-      <c r="M60" s="85"/>
-      <c r="N60" s="62"/>
+      <c r="I60" s="56"/>
+      <c r="J60" s="60"/>
+      <c r="K60" s="60"/>
+      <c r="L60" s="60"/>
+      <c r="M60" s="80"/>
+      <c r="N60" s="61"/>
       <c r="O60" s="37"/>
-      <c r="P60" s="146"/>
-      <c r="Q60" s="147"/>
-      <c r="R60" s="147"/>
-      <c r="S60" s="147"/>
-      <c r="T60" s="147"/>
-      <c r="U60" s="77">
+      <c r="P60" s="116"/>
+      <c r="Q60" s="117"/>
+      <c r="R60" s="117"/>
+      <c r="S60" s="117"/>
+      <c r="T60" s="117"/>
+      <c r="U60" s="74">
         <f>(I59*P60)+(J59*Q60)+(K59*R60)+(L59*S60)+(M59*T60)</f>
         <v>0</v>
       </c>
@@ -8498,12 +8393,12 @@
       <c r="Y60" s="42"/>
       <c r="Z60" s="42"/>
       <c r="AA60" s="42"/>
-      <c r="AB60" s="73"/>
-      <c r="AC60" s="78"/>
-      <c r="AD60" s="74"/>
-      <c r="AE60" s="116"/>
+      <c r="AB60" s="70"/>
+      <c r="AC60" s="75"/>
+      <c r="AD60" s="71"/>
+      <c r="AE60" s="100"/>
       <c r="AF60" s="43"/>
-      <c r="AG60" s="65"/>
+      <c r="AG60" s="64"/>
       <c r="AH60" s="44"/>
       <c r="AI60" s="41"/>
       <c r="AJ60" s="45"/>
@@ -8514,29 +8409,29 @@
       <c r="AO60" s="50"/>
     </row>
     <row r="61" spans="1:41" s="22" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A61" s="90"/>
-      <c r="B61" s="88"/>
-      <c r="C61" s="92"/>
-      <c r="D61" s="96"/>
-      <c r="E61" s="130"/>
-      <c r="F61" s="92"/>
-      <c r="G61" s="128"/>
+      <c r="A61" s="84"/>
+      <c r="B61" s="82"/>
+      <c r="C61" s="173"/>
+      <c r="D61" s="172"/>
+      <c r="E61" s="173"/>
+      <c r="F61" s="173"/>
+      <c r="G61" s="113"/>
       <c r="H61" s="34"/>
       <c r="I61" s="35"/>
       <c r="J61" s="36"/>
       <c r="K61" s="36"/>
       <c r="L61" s="36"/>
-      <c r="M61" s="86"/>
-      <c r="N61" s="62">
+      <c r="M61" s="81"/>
+      <c r="N61" s="61">
         <f>SUM(I61:M61)</f>
         <v>0</v>
       </c>
       <c r="O61" s="37"/>
-      <c r="P61" s="144"/>
-      <c r="Q61" s="145"/>
-      <c r="R61" s="145"/>
-      <c r="S61" s="145"/>
-      <c r="T61" s="145"/>
+      <c r="P61" s="114"/>
+      <c r="Q61" s="115"/>
+      <c r="R61" s="115"/>
+      <c r="S61" s="115"/>
+      <c r="T61" s="115"/>
       <c r="U61" s="40">
         <f>ROUND(((P61*I61)+(Q61*J61)+(R61*K61)+(S61*L61)+(T61*M61)),3)</f>
         <v>0</v>
@@ -8550,26 +8445,26 @@
       <c r="Y61" s="42"/>
       <c r="Z61" s="42"/>
       <c r="AA61" s="42"/>
-      <c r="AB61" s="73" t="e">
+      <c r="AB61" s="70" t="e">
         <f>(((((W61*I61)+(X61*J61)+(Y61*K61)+(Z61*L61)+(AA61*M61))/$L$2)))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AC61" s="78" t="e">
+      <c r="AC61" s="75" t="e">
         <f>ROUND(11*AB61,3)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD61" s="75" t="e">
+      <c r="AD61" s="72" t="e">
         <f>IF(AC61&gt;=11,11,AC61)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE61" s="116">
+      <c r="AE61" s="100">
         <f>IF(U62&gt;=94,4,IF(U62&gt;=91,3.9,IF(U62&gt;=88,3.8,IF(U62&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF61" s="43">
         <v>0.2</v>
       </c>
-      <c r="AG61" s="117">
+      <c r="AG61" s="101">
         <v>17</v>
       </c>
       <c r="AH61" s="44" t="e">
@@ -8594,29 +8489,29 @@
       <c r="AO61" s="50"/>
     </row>
     <row r="62" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A62" s="91"/>
-      <c r="B62" s="89"/>
-      <c r="C62" s="183" t="s">
-        <v>48</v>
-      </c>
-      <c r="D62" s="184"/>
-      <c r="E62" s="184"/>
-      <c r="F62" s="184"/>
-      <c r="G62" s="185"/>
+      <c r="A62" s="85"/>
+      <c r="B62" s="83"/>
+      <c r="C62" s="121" t="s">
+        <v>47</v>
+      </c>
+      <c r="D62" s="122"/>
+      <c r="E62" s="122"/>
+      <c r="F62" s="122"/>
+      <c r="G62" s="123"/>
       <c r="H62" s="34"/>
-      <c r="I62" s="57"/>
-      <c r="J62" s="61"/>
-      <c r="K62" s="61"/>
-      <c r="L62" s="61"/>
-      <c r="M62" s="85"/>
-      <c r="N62" s="62"/>
+      <c r="I62" s="56"/>
+      <c r="J62" s="60"/>
+      <c r="K62" s="60"/>
+      <c r="L62" s="60"/>
+      <c r="M62" s="80"/>
+      <c r="N62" s="61"/>
       <c r="O62" s="37"/>
-      <c r="P62" s="147"/>
-      <c r="Q62" s="147"/>
-      <c r="R62" s="147"/>
-      <c r="S62" s="147"/>
-      <c r="T62" s="147"/>
-      <c r="U62" s="77">
+      <c r="P62" s="117"/>
+      <c r="Q62" s="117"/>
+      <c r="R62" s="117"/>
+      <c r="S62" s="117"/>
+      <c r="T62" s="117"/>
+      <c r="U62" s="74">
         <f>(I61*P62)+(J61*Q62)+(K61*R62)+(L61*S62)+(M61*T62)</f>
         <v>0</v>
       </c>
@@ -8626,12 +8521,12 @@
       <c r="Y62" s="42"/>
       <c r="Z62" s="42"/>
       <c r="AA62" s="42"/>
-      <c r="AB62" s="73"/>
-      <c r="AC62" s="78"/>
-      <c r="AD62" s="74"/>
-      <c r="AE62" s="116"/>
+      <c r="AB62" s="70"/>
+      <c r="AC62" s="75"/>
+      <c r="AD62" s="71"/>
+      <c r="AE62" s="100"/>
       <c r="AF62" s="43"/>
-      <c r="AG62" s="65"/>
+      <c r="AG62" s="64"/>
       <c r="AH62" s="44"/>
       <c r="AI62" s="41"/>
       <c r="AJ62" s="45"/>
@@ -8642,29 +8537,29 @@
       <c r="AO62" s="50"/>
     </row>
     <row r="63" spans="1:41" s="22" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A63" s="90"/>
-      <c r="B63" s="105"/>
-      <c r="C63" s="96"/>
-      <c r="D63" s="92"/>
-      <c r="E63" s="96"/>
-      <c r="F63" s="93"/>
-      <c r="G63" s="127"/>
-      <c r="H63" s="58"/>
+      <c r="A63" s="84"/>
+      <c r="B63" s="91"/>
+      <c r="C63" s="173"/>
+      <c r="D63" s="172"/>
+      <c r="E63" s="173"/>
+      <c r="F63" s="173"/>
+      <c r="G63" s="113"/>
+      <c r="H63" s="57"/>
       <c r="I63" s="35"/>
       <c r="J63" s="36"/>
       <c r="K63" s="36"/>
       <c r="L63" s="36"/>
-      <c r="M63" s="86"/>
-      <c r="N63" s="62">
+      <c r="M63" s="81"/>
+      <c r="N63" s="61">
         <f>SUM(I63:M63)</f>
         <v>0</v>
       </c>
       <c r="O63" s="37"/>
-      <c r="P63" s="144"/>
-      <c r="Q63" s="145"/>
-      <c r="R63" s="145"/>
-      <c r="S63" s="145"/>
-      <c r="T63" s="145"/>
+      <c r="P63" s="114"/>
+      <c r="Q63" s="115"/>
+      <c r="R63" s="115"/>
+      <c r="S63" s="115"/>
+      <c r="T63" s="115"/>
       <c r="U63" s="40">
         <f>ROUND(((P63*I63)+(Q63*J63)+(R63*K63)+(S63*L63)+(T63*M63)),3)</f>
         <v>0</v>
@@ -8678,26 +8573,26 @@
       <c r="Y63" s="42"/>
       <c r="Z63" s="42"/>
       <c r="AA63" s="42"/>
-      <c r="AB63" s="73" t="e">
+      <c r="AB63" s="70" t="e">
         <f>(((((W63*I63)+(X63*J63)+(Y63*K63)+(Z63*L63)+(AA63*M63))/$L$2)))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AC63" s="78" t="e">
+      <c r="AC63" s="75" t="e">
         <f>ROUND(11*AB63,3)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD63" s="75" t="e">
+      <c r="AD63" s="72" t="e">
         <f>IF(AC63&gt;=11,11,AC63)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE63" s="116">
+      <c r="AE63" s="100">
         <f>IF(U64&gt;=94,4,IF(U64&gt;=91,3.9,IF(U64&gt;=88,3.8,IF(U64&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF63" s="43">
         <v>0.3</v>
       </c>
-      <c r="AG63" s="117">
+      <c r="AG63" s="101">
         <v>17</v>
       </c>
       <c r="AH63" s="44" t="e">
@@ -8722,29 +8617,29 @@
       <c r="AO63" s="50"/>
     </row>
     <row r="64" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A64" s="91"/>
-      <c r="B64" s="89"/>
-      <c r="C64" s="183" t="s">
-        <v>48</v>
-      </c>
-      <c r="D64" s="184"/>
-      <c r="E64" s="184"/>
-      <c r="F64" s="184"/>
-      <c r="G64" s="185"/>
+      <c r="A64" s="85"/>
+      <c r="B64" s="83"/>
+      <c r="C64" s="121" t="s">
+        <v>47</v>
+      </c>
+      <c r="D64" s="122"/>
+      <c r="E64" s="122"/>
+      <c r="F64" s="122"/>
+      <c r="G64" s="123"/>
       <c r="H64" s="34"/>
-      <c r="I64" s="57"/>
-      <c r="J64" s="61"/>
-      <c r="K64" s="61"/>
-      <c r="L64" s="61"/>
-      <c r="M64" s="85"/>
-      <c r="N64" s="62"/>
+      <c r="I64" s="56"/>
+      <c r="J64" s="60"/>
+      <c r="K64" s="60"/>
+      <c r="L64" s="60"/>
+      <c r="M64" s="80"/>
+      <c r="N64" s="61"/>
       <c r="O64" s="37"/>
-      <c r="P64" s="147"/>
-      <c r="Q64" s="147"/>
-      <c r="R64" s="147"/>
-      <c r="S64" s="147"/>
-      <c r="T64" s="147"/>
-      <c r="U64" s="77">
+      <c r="P64" s="117"/>
+      <c r="Q64" s="117"/>
+      <c r="R64" s="117"/>
+      <c r="S64" s="117"/>
+      <c r="T64" s="117"/>
+      <c r="U64" s="74">
         <f>(I63*P64)+(J63*Q64)+(K63*R64)+(L63*S64)+(M63*T64)</f>
         <v>0</v>
       </c>
@@ -8754,12 +8649,12 @@
       <c r="Y64" s="42"/>
       <c r="Z64" s="42"/>
       <c r="AA64" s="42"/>
-      <c r="AB64" s="73"/>
-      <c r="AC64" s="78"/>
-      <c r="AD64" s="74"/>
-      <c r="AE64" s="116"/>
+      <c r="AB64" s="70"/>
+      <c r="AC64" s="75"/>
+      <c r="AD64" s="71"/>
+      <c r="AE64" s="100"/>
       <c r="AF64" s="43"/>
-      <c r="AG64" s="65"/>
+      <c r="AG64" s="64"/>
       <c r="AH64" s="44"/>
       <c r="AI64" s="41"/>
       <c r="AJ64" s="45"/>
@@ -8770,29 +8665,29 @@
       <c r="AO64" s="50"/>
     </row>
     <row r="65" spans="1:41" s="22" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A65" s="90"/>
-      <c r="B65" s="88"/>
-      <c r="C65" s="96"/>
-      <c r="D65" s="92"/>
-      <c r="E65" s="96"/>
-      <c r="F65" s="92"/>
-      <c r="G65" s="128"/>
-      <c r="H65" s="58"/>
+      <c r="A65" s="84"/>
+      <c r="B65" s="82"/>
+      <c r="C65" s="173"/>
+      <c r="D65" s="172"/>
+      <c r="E65" s="173"/>
+      <c r="F65" s="173"/>
+      <c r="G65" s="113"/>
+      <c r="H65" s="57"/>
       <c r="I65" s="35"/>
       <c r="J65" s="36"/>
       <c r="K65" s="36"/>
       <c r="L65" s="36"/>
-      <c r="M65" s="86"/>
-      <c r="N65" s="62">
+      <c r="M65" s="81"/>
+      <c r="N65" s="61">
         <f>SUM(I65:M65)</f>
         <v>0</v>
       </c>
       <c r="O65" s="37"/>
-      <c r="P65" s="144"/>
-      <c r="Q65" s="145"/>
-      <c r="R65" s="145"/>
-      <c r="S65" s="145"/>
-      <c r="T65" s="145"/>
+      <c r="P65" s="114"/>
+      <c r="Q65" s="115"/>
+      <c r="R65" s="115"/>
+      <c r="S65" s="115"/>
+      <c r="T65" s="115"/>
       <c r="U65" s="40">
         <f>ROUND(((P65*I65)+(Q65*J65)+(R65*K65)+(S65*L65)+(T65*M65)),3)</f>
         <v>0</v>
@@ -8806,26 +8701,26 @@
       <c r="Y65" s="42"/>
       <c r="Z65" s="42"/>
       <c r="AA65" s="42"/>
-      <c r="AB65" s="73" t="e">
+      <c r="AB65" s="70" t="e">
         <f>(((((W65*I65)+(X65*J65)+(Y65*K65)+(Z65*L65)+(AA65*M65))/$L$2)))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AC65" s="78" t="e">
+      <c r="AC65" s="75" t="e">
         <f t="shared" ref="AC65" si="38">ROUND(11*AB65,3)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD65" s="75" t="e">
+      <c r="AD65" s="72" t="e">
         <f t="shared" ref="AD65" si="39">IF(AC65&gt;=11,11,AC65)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE65" s="116">
+      <c r="AE65" s="100">
         <f>IF(U66&gt;=94,4,IF(U66&gt;=91,3.9,IF(U66&gt;=88,3.8,IF(U66&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF65" s="43">
         <v>0.3</v>
       </c>
-      <c r="AG65" s="117">
+      <c r="AG65" s="101">
         <v>17</v>
       </c>
       <c r="AH65" s="44" t="e">
@@ -8850,29 +8745,29 @@
       <c r="AO65" s="50"/>
     </row>
     <row r="66" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A66" s="91"/>
-      <c r="B66" s="89"/>
-      <c r="C66" s="183" t="s">
-        <v>48</v>
-      </c>
-      <c r="D66" s="184"/>
-      <c r="E66" s="184"/>
-      <c r="F66" s="184"/>
-      <c r="G66" s="185"/>
+      <c r="A66" s="85"/>
+      <c r="B66" s="83"/>
+      <c r="C66" s="121" t="s">
+        <v>47</v>
+      </c>
+      <c r="D66" s="122"/>
+      <c r="E66" s="122"/>
+      <c r="F66" s="122"/>
+      <c r="G66" s="123"/>
       <c r="H66" s="34"/>
-      <c r="I66" s="57"/>
-      <c r="J66" s="61"/>
-      <c r="K66" s="61"/>
-      <c r="L66" s="61"/>
-      <c r="M66" s="85"/>
-      <c r="N66" s="62"/>
+      <c r="I66" s="56"/>
+      <c r="J66" s="60"/>
+      <c r="K66" s="60"/>
+      <c r="L66" s="60"/>
+      <c r="M66" s="80"/>
+      <c r="N66" s="61"/>
       <c r="O66" s="37"/>
-      <c r="P66" s="146"/>
-      <c r="Q66" s="147"/>
-      <c r="R66" s="147"/>
-      <c r="S66" s="147"/>
-      <c r="T66" s="147"/>
-      <c r="U66" s="77">
+      <c r="P66" s="116"/>
+      <c r="Q66" s="117"/>
+      <c r="R66" s="117"/>
+      <c r="S66" s="117"/>
+      <c r="T66" s="117"/>
+      <c r="U66" s="74">
         <f>(I65*P66)+(J65*Q66)+(K65*R66)+(L65*S66)+(M65*T66)</f>
         <v>0</v>
       </c>
@@ -8882,12 +8777,12 @@
       <c r="Y66" s="42"/>
       <c r="Z66" s="42"/>
       <c r="AA66" s="42"/>
-      <c r="AB66" s="73"/>
-      <c r="AC66" s="78"/>
-      <c r="AD66" s="74"/>
-      <c r="AE66" s="116"/>
+      <c r="AB66" s="70"/>
+      <c r="AC66" s="75"/>
+      <c r="AD66" s="71"/>
+      <c r="AE66" s="100"/>
       <c r="AF66" s="43"/>
-      <c r="AG66" s="65"/>
+      <c r="AG66" s="64"/>
       <c r="AH66" s="44"/>
       <c r="AI66" s="41"/>
       <c r="AJ66" s="45"/>
@@ -8898,29 +8793,29 @@
       <c r="AO66" s="50"/>
     </row>
     <row r="67" spans="1:41" s="22" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A67" s="90"/>
-      <c r="B67" s="88"/>
-      <c r="C67" s="96"/>
-      <c r="D67" s="87"/>
-      <c r="E67" s="92"/>
-      <c r="F67" s="92"/>
-      <c r="G67" s="128"/>
-      <c r="H67" s="58"/>
+      <c r="A67" s="84"/>
+      <c r="B67" s="82"/>
+      <c r="C67" s="173"/>
+      <c r="D67" s="172"/>
+      <c r="E67" s="173"/>
+      <c r="F67" s="173"/>
+      <c r="G67" s="113"/>
+      <c r="H67" s="57"/>
       <c r="I67" s="35"/>
       <c r="J67" s="36"/>
       <c r="K67" s="36"/>
-      <c r="L67" s="61"/>
-      <c r="M67" s="86"/>
-      <c r="N67" s="62">
+      <c r="L67" s="60"/>
+      <c r="M67" s="81"/>
+      <c r="N67" s="61">
         <f>SUM(I67:M67)</f>
         <v>0</v>
       </c>
       <c r="O67" s="37"/>
-      <c r="P67" s="144"/>
-      <c r="Q67" s="145"/>
-      <c r="R67" s="145"/>
-      <c r="S67" s="145"/>
-      <c r="T67" s="145"/>
+      <c r="P67" s="114"/>
+      <c r="Q67" s="115"/>
+      <c r="R67" s="115"/>
+      <c r="S67" s="115"/>
+      <c r="T67" s="115"/>
       <c r="U67" s="40">
         <f>ROUND(((P67*I67)+(Q67*J67)+(R67*K67)+(S67*L67)+(T67*M67)),3)</f>
         <v>0</v>
@@ -8934,26 +8829,26 @@
       <c r="Y67" s="42"/>
       <c r="Z67" s="42"/>
       <c r="AA67" s="42"/>
-      <c r="AB67" s="73" t="e">
+      <c r="AB67" s="70" t="e">
         <f>(((((W67*I67)+(X67*J67)+(Y67*K67)+(Z67*L67)+(AA67*M67))/$L$2)))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AC67" s="78" t="e">
+      <c r="AC67" s="75" t="e">
         <f t="shared" ref="AC67" si="40">ROUND(11*AB67,3)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD67" s="75" t="e">
+      <c r="AD67" s="72" t="e">
         <f t="shared" ref="AD67" si="41">IF(AC67&gt;=11,11,AC67)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE67" s="116">
+      <c r="AE67" s="100">
         <f>IF(U68&gt;=94,4,IF(U68&gt;=91,3.9,IF(U68&gt;=88,3.8,IF(U68&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF67" s="43">
         <v>0.3</v>
       </c>
-      <c r="AG67" s="117">
+      <c r="AG67" s="101">
         <v>17</v>
       </c>
       <c r="AH67" s="44" t="e">
@@ -8978,29 +8873,29 @@
       <c r="AO67" s="50"/>
     </row>
     <row r="68" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A68" s="91"/>
-      <c r="B68" s="89"/>
-      <c r="C68" s="183" t="s">
-        <v>48</v>
-      </c>
-      <c r="D68" s="184"/>
-      <c r="E68" s="184"/>
-      <c r="F68" s="184"/>
-      <c r="G68" s="185"/>
+      <c r="A68" s="85"/>
+      <c r="B68" s="83"/>
+      <c r="C68" s="121" t="s">
+        <v>47</v>
+      </c>
+      <c r="D68" s="122"/>
+      <c r="E68" s="122"/>
+      <c r="F68" s="122"/>
+      <c r="G68" s="123"/>
       <c r="H68" s="34"/>
-      <c r="I68" s="57"/>
-      <c r="J68" s="61"/>
-      <c r="K68" s="61"/>
-      <c r="L68" s="61"/>
-      <c r="M68" s="85"/>
-      <c r="N68" s="62"/>
+      <c r="I68" s="56"/>
+      <c r="J68" s="60"/>
+      <c r="K68" s="60"/>
+      <c r="L68" s="60"/>
+      <c r="M68" s="80"/>
+      <c r="N68" s="61"/>
       <c r="O68" s="37"/>
-      <c r="P68" s="146"/>
-      <c r="Q68" s="145"/>
-      <c r="R68" s="145"/>
-      <c r="S68" s="147"/>
-      <c r="T68" s="147"/>
-      <c r="U68" s="77">
+      <c r="P68" s="116"/>
+      <c r="Q68" s="115"/>
+      <c r="R68" s="115"/>
+      <c r="S68" s="117"/>
+      <c r="T68" s="117"/>
+      <c r="U68" s="74">
         <f>(I67*P68)+(J67*Q68)+(K67*R68)+(L67*S68)+(M67*T68)</f>
         <v>0</v>
       </c>
@@ -9010,12 +8905,12 @@
       <c r="Y68" s="42"/>
       <c r="Z68" s="42"/>
       <c r="AA68" s="42"/>
-      <c r="AB68" s="73"/>
-      <c r="AC68" s="78"/>
-      <c r="AD68" s="74"/>
-      <c r="AE68" s="116"/>
+      <c r="AB68" s="70"/>
+      <c r="AC68" s="75"/>
+      <c r="AD68" s="71"/>
+      <c r="AE68" s="100"/>
       <c r="AF68" s="43"/>
-      <c r="AG68" s="65"/>
+      <c r="AG68" s="64"/>
       <c r="AH68" s="44"/>
       <c r="AI68" s="41"/>
       <c r="AJ68" s="45"/>
@@ -9026,29 +8921,29 @@
       <c r="AO68" s="50"/>
     </row>
     <row r="69" spans="1:41" s="22" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A69" s="90"/>
-      <c r="B69" s="88"/>
-      <c r="C69" s="92"/>
-      <c r="D69" s="92"/>
-      <c r="E69" s="92"/>
-      <c r="F69" s="106"/>
-      <c r="G69" s="107"/>
-      <c r="H69" s="58"/>
+      <c r="A69" s="84"/>
+      <c r="B69" s="82"/>
+      <c r="C69" s="173"/>
+      <c r="D69" s="172"/>
+      <c r="E69" s="173"/>
+      <c r="F69" s="173"/>
+      <c r="G69" s="113"/>
+      <c r="H69" s="57"/>
       <c r="I69" s="35"/>
       <c r="J69" s="36"/>
       <c r="K69" s="36"/>
       <c r="L69" s="36"/>
-      <c r="M69" s="86"/>
-      <c r="N69" s="62">
+      <c r="M69" s="81"/>
+      <c r="N69" s="61">
         <f>SUM(I69:M69)</f>
         <v>0</v>
       </c>
       <c r="O69" s="37"/>
-      <c r="P69" s="144"/>
-      <c r="Q69" s="145"/>
-      <c r="R69" s="145"/>
-      <c r="S69" s="145"/>
-      <c r="T69" s="145"/>
+      <c r="P69" s="114"/>
+      <c r="Q69" s="115"/>
+      <c r="R69" s="115"/>
+      <c r="S69" s="115"/>
+      <c r="T69" s="115"/>
       <c r="U69" s="40">
         <f>ROUND(((P69*I69)+(Q69*J69)+(R69*K69)+(S69*L69)+(T69*M69)),3)</f>
         <v>0</v>
@@ -9062,26 +8957,26 @@
       <c r="Y69" s="42"/>
       <c r="Z69" s="42"/>
       <c r="AA69" s="42"/>
-      <c r="AB69" s="73" t="e">
+      <c r="AB69" s="70" t="e">
         <f>(((((W69*I69)+(X69*J69)+(Y69*K69)+(Z69*L69)+(AA69*M69))/$L$2)))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AC69" s="78" t="e">
+      <c r="AC69" s="75" t="e">
         <f t="shared" ref="AC69" si="42">ROUND(11*AB69,3)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD69" s="75" t="e">
+      <c r="AD69" s="72" t="e">
         <f t="shared" ref="AD69" si="43">IF(AC69&gt;=11,11,AC69)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE69" s="116">
+      <c r="AE69" s="100">
         <f>IF(U70&gt;=94,4,IF(U70&gt;=91,3.9,IF(U70&gt;=88,3.8,IF(U70&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF69" s="43">
         <v>0.3</v>
       </c>
-      <c r="AG69" s="117">
+      <c r="AG69" s="101">
         <v>17</v>
       </c>
       <c r="AH69" s="44" t="e">
@@ -9106,29 +9001,29 @@
       <c r="AO69" s="50"/>
     </row>
     <row r="70" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A70" s="91"/>
-      <c r="B70" s="89"/>
-      <c r="C70" s="194" t="s">
-        <v>48</v>
-      </c>
-      <c r="D70" s="195"/>
-      <c r="E70" s="195"/>
-      <c r="F70" s="195"/>
-      <c r="G70" s="196"/>
+      <c r="A70" s="85"/>
+      <c r="B70" s="83"/>
+      <c r="C70" s="118" t="s">
+        <v>47</v>
+      </c>
+      <c r="D70" s="119"/>
+      <c r="E70" s="119"/>
+      <c r="F70" s="119"/>
+      <c r="G70" s="120"/>
       <c r="H70" s="34"/>
-      <c r="I70" s="57"/>
-      <c r="J70" s="61"/>
-      <c r="K70" s="61"/>
-      <c r="L70" s="61"/>
-      <c r="M70" s="85"/>
-      <c r="N70" s="62"/>
+      <c r="I70" s="56"/>
+      <c r="J70" s="60"/>
+      <c r="K70" s="60"/>
+      <c r="L70" s="60"/>
+      <c r="M70" s="80"/>
+      <c r="N70" s="61"/>
       <c r="O70" s="37"/>
-      <c r="P70" s="146"/>
-      <c r="Q70" s="146"/>
-      <c r="R70" s="146"/>
-      <c r="S70" s="147"/>
-      <c r="T70" s="147"/>
-      <c r="U70" s="77">
+      <c r="P70" s="116"/>
+      <c r="Q70" s="116"/>
+      <c r="R70" s="116"/>
+      <c r="S70" s="117"/>
+      <c r="T70" s="117"/>
+      <c r="U70" s="74">
         <f>(I69*P70)+(J69*Q70)+(K69*R70)+(L69*S70)+(M69*T70)</f>
         <v>0</v>
       </c>
@@ -9138,12 +9033,12 @@
       <c r="Y70" s="42"/>
       <c r="Z70" s="42"/>
       <c r="AA70" s="42"/>
-      <c r="AB70" s="73"/>
-      <c r="AC70" s="78"/>
-      <c r="AD70" s="74"/>
-      <c r="AE70" s="116"/>
+      <c r="AB70" s="70"/>
+      <c r="AC70" s="75"/>
+      <c r="AD70" s="71"/>
+      <c r="AE70" s="100"/>
       <c r="AF70" s="43"/>
-      <c r="AG70" s="65"/>
+      <c r="AG70" s="64"/>
       <c r="AH70" s="44"/>
       <c r="AI70" s="41"/>
       <c r="AJ70" s="45"/>
@@ -9154,29 +9049,29 @@
       <c r="AO70" s="50"/>
     </row>
     <row r="71" spans="1:41" s="22" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A71" s="90"/>
-      <c r="B71" s="88"/>
-      <c r="C71" s="53"/>
-      <c r="D71" s="33"/>
-      <c r="E71" s="33"/>
-      <c r="F71" s="54"/>
-      <c r="G71" s="81"/>
+      <c r="A71" s="84"/>
+      <c r="B71" s="82"/>
+      <c r="C71" s="173"/>
+      <c r="D71" s="172"/>
+      <c r="E71" s="173"/>
+      <c r="F71" s="173"/>
+      <c r="G71" s="113"/>
       <c r="H71" s="34"/>
       <c r="I71" s="35"/>
       <c r="J71" s="36"/>
       <c r="K71" s="36"/>
       <c r="L71" s="36"/>
-      <c r="M71" s="86"/>
-      <c r="N71" s="62">
+      <c r="M71" s="81"/>
+      <c r="N71" s="61">
         <f>SUM(I71:M71)</f>
         <v>0</v>
       </c>
       <c r="O71" s="37"/>
-      <c r="P71" s="144"/>
-      <c r="Q71" s="145"/>
-      <c r="R71" s="145"/>
-      <c r="S71" s="145"/>
-      <c r="T71" s="145"/>
+      <c r="P71" s="114"/>
+      <c r="Q71" s="115"/>
+      <c r="R71" s="115"/>
+      <c r="S71" s="115"/>
+      <c r="T71" s="115"/>
       <c r="U71" s="40">
         <f>ROUND(((P71*I71)+(Q71*J71)+(R71*K71)+(S71*L71)+(T71*M71)),2)</f>
         <v>0</v>
@@ -9190,26 +9085,26 @@
       <c r="Y71" s="42"/>
       <c r="Z71" s="42"/>
       <c r="AA71" s="42"/>
-      <c r="AB71" s="73" t="e">
+      <c r="AB71" s="70" t="e">
         <f>(((((W71*I71)+(X71*J71)+(Y71*K71)+(Z71*L71)+(AA71*M71))/$L$2)))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AC71" s="78" t="e">
+      <c r="AC71" s="75" t="e">
         <f t="shared" ref="AC71" si="44">ROUND(11*AB71,3)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD71" s="75" t="e">
+      <c r="AD71" s="72" t="e">
         <f t="shared" ref="AD71" si="45">IF(AC71&gt;=11,11,AC71)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE71" s="116">
+      <c r="AE71" s="100">
         <f>IF(U72&gt;=94,4,IF(U72&gt;=91,3.9,IF(U72&gt;=88,3.8,IF(U72&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF71" s="43">
         <v>0.3</v>
       </c>
-      <c r="AG71" s="117">
+      <c r="AG71" s="101">
         <v>17</v>
       </c>
       <c r="AH71" s="44" t="e">
@@ -9228,29 +9123,29 @@
       <c r="AO71" s="50"/>
     </row>
     <row r="72" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A72" s="91"/>
-      <c r="B72" s="89"/>
-      <c r="C72" s="194" t="s">
-        <v>48</v>
-      </c>
-      <c r="D72" s="195"/>
-      <c r="E72" s="195"/>
-      <c r="F72" s="195"/>
-      <c r="G72" s="196"/>
+      <c r="A72" s="85"/>
+      <c r="B72" s="83"/>
+      <c r="C72" s="118" t="s">
+        <v>47</v>
+      </c>
+      <c r="D72" s="119"/>
+      <c r="E72" s="119"/>
+      <c r="F72" s="119"/>
+      <c r="G72" s="120"/>
       <c r="H72" s="34"/>
-      <c r="I72" s="57"/>
-      <c r="J72" s="61"/>
-      <c r="K72" s="61"/>
-      <c r="L72" s="61"/>
-      <c r="M72" s="85"/>
-      <c r="N72" s="62"/>
+      <c r="I72" s="56"/>
+      <c r="J72" s="60"/>
+      <c r="K72" s="60"/>
+      <c r="L72" s="60"/>
+      <c r="M72" s="80"/>
+      <c r="N72" s="61"/>
       <c r="O72" s="37"/>
-      <c r="P72" s="147"/>
-      <c r="Q72" s="147"/>
-      <c r="R72" s="147"/>
-      <c r="S72" s="147"/>
-      <c r="T72" s="147"/>
-      <c r="U72" s="77">
+      <c r="P72" s="117"/>
+      <c r="Q72" s="117"/>
+      <c r="R72" s="117"/>
+      <c r="S72" s="117"/>
+      <c r="T72" s="117"/>
+      <c r="U72" s="74">
         <f>(I71*P72)+(J71*Q72)+(K71*R72)+(L71*S72)+(M71*T72)</f>
         <v>0</v>
       </c>
@@ -9260,12 +9155,12 @@
       <c r="Y72" s="42"/>
       <c r="Z72" s="42"/>
       <c r="AA72" s="42"/>
-      <c r="AB72" s="73"/>
-      <c r="AC72" s="78"/>
-      <c r="AD72" s="74"/>
-      <c r="AE72" s="116"/>
+      <c r="AB72" s="70"/>
+      <c r="AC72" s="75"/>
+      <c r="AD72" s="71"/>
+      <c r="AE72" s="100"/>
       <c r="AF72" s="43"/>
-      <c r="AG72" s="65"/>
+      <c r="AG72" s="64"/>
       <c r="AH72" s="44"/>
       <c r="AI72" s="41"/>
       <c r="AJ72" s="45"/>
@@ -9276,29 +9171,29 @@
       <c r="AO72" s="50"/>
     </row>
     <row r="73" spans="1:41" s="22" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A73" s="90"/>
-      <c r="B73" s="88"/>
-      <c r="C73" s="53"/>
-      <c r="D73" s="33"/>
-      <c r="E73" s="33"/>
-      <c r="F73" s="54"/>
-      <c r="G73" s="81"/>
+      <c r="A73" s="84"/>
+      <c r="B73" s="82"/>
+      <c r="C73" s="173"/>
+      <c r="D73" s="172"/>
+      <c r="E73" s="173"/>
+      <c r="F73" s="173"/>
+      <c r="G73" s="113"/>
       <c r="H73" s="34"/>
       <c r="I73" s="35"/>
       <c r="J73" s="36"/>
       <c r="K73" s="36"/>
       <c r="L73" s="36"/>
-      <c r="M73" s="86"/>
-      <c r="N73" s="62">
+      <c r="M73" s="81"/>
+      <c r="N73" s="61">
         <f>SUM(I73:M73)</f>
         <v>0</v>
       </c>
       <c r="O73" s="37"/>
-      <c r="P73" s="144"/>
-      <c r="Q73" s="145"/>
-      <c r="R73" s="145"/>
-      <c r="S73" s="145"/>
-      <c r="T73" s="145"/>
+      <c r="P73" s="114"/>
+      <c r="Q73" s="115"/>
+      <c r="R73" s="115"/>
+      <c r="S73" s="115"/>
+      <c r="T73" s="115"/>
       <c r="U73" s="40">
         <f>ROUND(((P73*I73)+(Q73*J73)+(R73*K73)+(S73*L73)+(T73*M73)),3)</f>
         <v>0</v>
@@ -9312,26 +9207,26 @@
       <c r="Y73" s="42"/>
       <c r="Z73" s="42"/>
       <c r="AA73" s="42"/>
-      <c r="AB73" s="73" t="e">
+      <c r="AB73" s="70" t="e">
         <f>(((((W73*I73)+(X73*J73)+(Y73*K73)+(Z73*L73)+(AA73*M73))/$L$2)))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AC73" s="78" t="e">
+      <c r="AC73" s="75" t="e">
         <f t="shared" ref="AC73" si="46">ROUND(11*AB73,3)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD73" s="75" t="e">
+      <c r="AD73" s="72" t="e">
         <f t="shared" ref="AD73" si="47">IF(AC73&gt;=11,11,AC73)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE73" s="116">
+      <c r="AE73" s="100">
         <f>IF(U74&gt;=94,4,IF(U74&gt;=91,3.9,IF(U74&gt;=88,3.8,IF(U74&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF73" s="43">
         <v>0.3</v>
       </c>
-      <c r="AG73" s="117">
+      <c r="AG73" s="101">
         <v>17</v>
       </c>
       <c r="AH73" s="44" t="e">
@@ -9356,29 +9251,29 @@
       <c r="AO73" s="50"/>
     </row>
     <row r="74" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A74" s="91"/>
-      <c r="B74" s="89"/>
-      <c r="C74" s="194" t="s">
-        <v>48</v>
-      </c>
-      <c r="D74" s="195"/>
-      <c r="E74" s="195"/>
-      <c r="F74" s="195"/>
-      <c r="G74" s="196"/>
+      <c r="A74" s="85"/>
+      <c r="B74" s="83"/>
+      <c r="C74" s="118" t="s">
+        <v>47</v>
+      </c>
+      <c r="D74" s="119"/>
+      <c r="E74" s="119"/>
+      <c r="F74" s="119"/>
+      <c r="G74" s="120"/>
       <c r="H74" s="34"/>
-      <c r="I74" s="57"/>
-      <c r="J74" s="61"/>
-      <c r="K74" s="61"/>
-      <c r="L74" s="61"/>
-      <c r="M74" s="85"/>
-      <c r="N74" s="62"/>
+      <c r="I74" s="56"/>
+      <c r="J74" s="60"/>
+      <c r="K74" s="60"/>
+      <c r="L74" s="60"/>
+      <c r="M74" s="80"/>
+      <c r="N74" s="61"/>
       <c r="O74" s="37"/>
-      <c r="P74" s="146"/>
-      <c r="Q74" s="147"/>
-      <c r="R74" s="147"/>
-      <c r="S74" s="147"/>
-      <c r="T74" s="147"/>
-      <c r="U74" s="77">
+      <c r="P74" s="116"/>
+      <c r="Q74" s="117"/>
+      <c r="R74" s="117"/>
+      <c r="S74" s="117"/>
+      <c r="T74" s="117"/>
+      <c r="U74" s="74">
         <f>(I73*P74)+(J73*Q74)+(K73*R74)+(L73*S74)+(M73*T74)</f>
         <v>0</v>
       </c>
@@ -9388,12 +9283,12 @@
       <c r="Y74" s="42"/>
       <c r="Z74" s="42"/>
       <c r="AA74" s="42"/>
-      <c r="AB74" s="73"/>
-      <c r="AC74" s="78"/>
-      <c r="AD74" s="74"/>
-      <c r="AE74" s="116"/>
+      <c r="AB74" s="70"/>
+      <c r="AC74" s="75"/>
+      <c r="AD74" s="71"/>
+      <c r="AE74" s="100"/>
       <c r="AF74" s="43"/>
-      <c r="AG74" s="65"/>
+      <c r="AG74" s="64"/>
       <c r="AH74" s="44"/>
       <c r="AI74" s="41"/>
       <c r="AJ74" s="45"/>
@@ -9404,29 +9299,29 @@
       <c r="AO74" s="50"/>
     </row>
     <row r="75" spans="1:41" s="22" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A75" s="90"/>
-      <c r="B75" s="88"/>
-      <c r="C75" s="33"/>
-      <c r="D75" s="92"/>
-      <c r="E75" s="92"/>
-      <c r="F75" s="33"/>
-      <c r="G75" s="80"/>
+      <c r="A75" s="84"/>
+      <c r="B75" s="82"/>
+      <c r="C75" s="173"/>
+      <c r="D75" s="172"/>
+      <c r="E75" s="173"/>
+      <c r="F75" s="173"/>
+      <c r="G75" s="113"/>
       <c r="H75" s="34"/>
       <c r="I75" s="35"/>
       <c r="J75" s="36"/>
       <c r="K75" s="36"/>
       <c r="L75" s="36"/>
-      <c r="M75" s="86"/>
-      <c r="N75" s="124">
+      <c r="M75" s="81"/>
+      <c r="N75" s="107">
         <f>SUM(I75:M75)</f>
         <v>0</v>
       </c>
       <c r="O75" s="37"/>
-      <c r="P75" s="144"/>
-      <c r="Q75" s="145"/>
-      <c r="R75" s="145"/>
-      <c r="S75" s="145"/>
-      <c r="T75" s="145"/>
+      <c r="P75" s="114"/>
+      <c r="Q75" s="115"/>
+      <c r="R75" s="115"/>
+      <c r="S75" s="115"/>
+      <c r="T75" s="115"/>
       <c r="U75" s="40">
         <f>ROUND(((P75*I75)+(Q75*J75)+(R75*K75)+(S75*L75)+(T75*M75)),3)</f>
         <v>0</v>
@@ -9440,26 +9335,26 @@
       <c r="Y75" s="42"/>
       <c r="Z75" s="42"/>
       <c r="AA75" s="42"/>
-      <c r="AB75" s="73" t="e">
+      <c r="AB75" s="70" t="e">
         <f>(((((W75*I75)+(X75*J75)+(Y75*K75)+(Z75*L75)+(AA75*M75))/$L$2)))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AC75" s="78" t="e">
+      <c r="AC75" s="75" t="e">
         <f t="shared" ref="AC75" si="48">ROUND(11*AB75,3)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD75" s="75" t="e">
+      <c r="AD75" s="72" t="e">
         <f t="shared" ref="AD75" si="49">IF(AC75&gt;=11,11,AC75)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE75" s="116">
+      <c r="AE75" s="100">
         <f>IF(U76&gt;=94,4,IF(U76&gt;=91,3.9,IF(U76&gt;=88,3.8,IF(U76&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF75" s="43">
         <v>0.3</v>
       </c>
-      <c r="AG75" s="117">
+      <c r="AG75" s="101">
         <v>17</v>
       </c>
       <c r="AH75" s="44" t="e">
@@ -9484,29 +9379,29 @@
       <c r="AO75" s="50"/>
     </row>
     <row r="76" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A76" s="91"/>
-      <c r="B76" s="89"/>
-      <c r="C76" s="194" t="s">
-        <v>48</v>
-      </c>
-      <c r="D76" s="195"/>
-      <c r="E76" s="195"/>
-      <c r="F76" s="195"/>
-      <c r="G76" s="196"/>
+      <c r="A76" s="85"/>
+      <c r="B76" s="83"/>
+      <c r="C76" s="118" t="s">
+        <v>47</v>
+      </c>
+      <c r="D76" s="119"/>
+      <c r="E76" s="119"/>
+      <c r="F76" s="119"/>
+      <c r="G76" s="120"/>
       <c r="H76" s="34"/>
-      <c r="I76" s="57"/>
-      <c r="J76" s="61"/>
-      <c r="K76" s="61"/>
-      <c r="L76" s="61"/>
-      <c r="M76" s="85"/>
-      <c r="N76" s="62"/>
+      <c r="I76" s="56"/>
+      <c r="J76" s="60"/>
+      <c r="K76" s="60"/>
+      <c r="L76" s="60"/>
+      <c r="M76" s="80"/>
+      <c r="N76" s="61"/>
       <c r="O76" s="37"/>
-      <c r="P76" s="146"/>
-      <c r="Q76" s="147"/>
-      <c r="R76" s="147"/>
-      <c r="S76" s="147"/>
-      <c r="T76" s="147"/>
-      <c r="U76" s="77">
+      <c r="P76" s="116"/>
+      <c r="Q76" s="117"/>
+      <c r="R76" s="117"/>
+      <c r="S76" s="117"/>
+      <c r="T76" s="117"/>
+      <c r="U76" s="74">
         <f>(I75*P76)+(J75*Q76)+(K75*R76)+(L75*S76)+(M75*T76)</f>
         <v>0</v>
       </c>
@@ -9516,12 +9411,12 @@
       <c r="Y76" s="42"/>
       <c r="Z76" s="42"/>
       <c r="AA76" s="42"/>
-      <c r="AB76" s="73"/>
-      <c r="AC76" s="78"/>
-      <c r="AD76" s="74"/>
-      <c r="AE76" s="116"/>
+      <c r="AB76" s="70"/>
+      <c r="AC76" s="75"/>
+      <c r="AD76" s="71"/>
+      <c r="AE76" s="100"/>
       <c r="AF76" s="43"/>
-      <c r="AG76" s="65"/>
+      <c r="AG76" s="64"/>
       <c r="AH76" s="44"/>
       <c r="AI76" s="41"/>
       <c r="AJ76" s="45"/>
@@ -9532,29 +9427,29 @@
       <c r="AO76" s="50"/>
     </row>
     <row r="77" spans="1:41" s="22" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A77" s="90"/>
-      <c r="B77" s="88"/>
-      <c r="C77" s="53"/>
-      <c r="D77" s="82"/>
-      <c r="E77" s="53"/>
-      <c r="F77" s="33"/>
-      <c r="G77" s="69"/>
+      <c r="A77" s="84"/>
+      <c r="B77" s="82"/>
+      <c r="C77" s="173"/>
+      <c r="D77" s="172"/>
+      <c r="E77" s="173"/>
+      <c r="F77" s="173"/>
+      <c r="G77" s="113"/>
       <c r="H77" s="34"/>
       <c r="I77" s="35"/>
       <c r="J77" s="36"/>
       <c r="K77" s="36"/>
       <c r="L77" s="36"/>
-      <c r="M77" s="86"/>
-      <c r="N77" s="62">
+      <c r="M77" s="81"/>
+      <c r="N77" s="61">
         <f>SUM(I77:M77)</f>
         <v>0</v>
       </c>
       <c r="O77" s="37"/>
-      <c r="P77" s="145"/>
-      <c r="Q77" s="145"/>
-      <c r="R77" s="145"/>
-      <c r="S77" s="145"/>
-      <c r="T77" s="145"/>
+      <c r="P77" s="115"/>
+      <c r="Q77" s="115"/>
+      <c r="R77" s="115"/>
+      <c r="S77" s="115"/>
+      <c r="T77" s="115"/>
       <c r="U77" s="40">
         <f>ROUND(((P77*I77)+(Q77*J77)+(R77*K77)+(S77*L77)+(T77*M77)),3)</f>
         <v>0</v>
@@ -9568,26 +9463,26 @@
       <c r="Y77" s="42"/>
       <c r="Z77" s="42"/>
       <c r="AA77" s="42"/>
-      <c r="AB77" s="73" t="e">
+      <c r="AB77" s="70" t="e">
         <f>(((((W77*I77)+(X77*J77)+(Y77*K77)+(Z77*L77)+(AA77*M77))/$L$2)))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AC77" s="78" t="e">
+      <c r="AC77" s="75" t="e">
         <f t="shared" ref="AC77" si="50">ROUND(11*AB77,3)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD77" s="75" t="e">
+      <c r="AD77" s="72" t="e">
         <f t="shared" ref="AD77" si="51">IF(AC77&gt;=11,11,AC77)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE77" s="116">
+      <c r="AE77" s="100">
         <f>IF(U78&gt;=94,4,IF(U78&gt;=91,3.9,IF(U78&gt;=88,3.8,IF(U78&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF77" s="43">
         <v>0.3</v>
       </c>
-      <c r="AG77" s="117">
+      <c r="AG77" s="101">
         <v>17</v>
       </c>
       <c r="AH77" s="44" t="e">
@@ -9612,29 +9507,29 @@
       <c r="AO77" s="50"/>
     </row>
     <row r="78" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A78" s="91"/>
-      <c r="B78" s="89"/>
-      <c r="C78" s="194" t="s">
-        <v>48</v>
-      </c>
-      <c r="D78" s="195"/>
-      <c r="E78" s="195"/>
-      <c r="F78" s="195"/>
-      <c r="G78" s="196"/>
+      <c r="A78" s="85"/>
+      <c r="B78" s="83"/>
+      <c r="C78" s="118" t="s">
+        <v>47</v>
+      </c>
+      <c r="D78" s="119"/>
+      <c r="E78" s="119"/>
+      <c r="F78" s="119"/>
+      <c r="G78" s="120"/>
       <c r="H78" s="34"/>
-      <c r="I78" s="57"/>
-      <c r="J78" s="61"/>
-      <c r="K78" s="61"/>
-      <c r="L78" s="61"/>
-      <c r="M78" s="85"/>
-      <c r="N78" s="62"/>
+      <c r="I78" s="56"/>
+      <c r="J78" s="60"/>
+      <c r="K78" s="60"/>
+      <c r="L78" s="60"/>
+      <c r="M78" s="80"/>
+      <c r="N78" s="61"/>
       <c r="O78" s="37"/>
-      <c r="P78" s="146"/>
-      <c r="Q78" s="147"/>
-      <c r="R78" s="147"/>
-      <c r="S78" s="147"/>
-      <c r="T78" s="147"/>
-      <c r="U78" s="77">
+      <c r="P78" s="116"/>
+      <c r="Q78" s="117"/>
+      <c r="R78" s="117"/>
+      <c r="S78" s="117"/>
+      <c r="T78" s="117"/>
+      <c r="U78" s="74">
         <f>(I77*P78)+(J77*Q78)+(K77*R78)+(L77*S78)+(M77*T78)</f>
         <v>0</v>
       </c>
@@ -9644,12 +9539,12 @@
       <c r="Y78" s="42"/>
       <c r="Z78" s="42"/>
       <c r="AA78" s="42"/>
-      <c r="AB78" s="73"/>
-      <c r="AC78" s="78"/>
-      <c r="AD78" s="74"/>
-      <c r="AE78" s="116"/>
+      <c r="AB78" s="70"/>
+      <c r="AC78" s="75"/>
+      <c r="AD78" s="71"/>
+      <c r="AE78" s="100"/>
       <c r="AF78" s="43"/>
-      <c r="AG78" s="65"/>
+      <c r="AG78" s="64"/>
       <c r="AH78" s="44"/>
       <c r="AI78" s="41"/>
       <c r="AJ78" s="45"/>
@@ -9660,29 +9555,29 @@
       <c r="AO78" s="50"/>
     </row>
     <row r="79" spans="1:41" s="22" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A79" s="90"/>
-      <c r="B79" s="88"/>
-      <c r="C79" s="33"/>
-      <c r="D79" s="33"/>
-      <c r="E79" s="33"/>
-      <c r="F79" s="53"/>
-      <c r="G79" s="67"/>
-      <c r="H79" s="58"/>
+      <c r="A79" s="84"/>
+      <c r="B79" s="82"/>
+      <c r="C79" s="173"/>
+      <c r="D79" s="172"/>
+      <c r="E79" s="173"/>
+      <c r="F79" s="173"/>
+      <c r="G79" s="113"/>
+      <c r="H79" s="57"/>
       <c r="I79" s="35"/>
       <c r="J79" s="36"/>
       <c r="K79" s="36"/>
       <c r="L79" s="36"/>
-      <c r="M79" s="86"/>
-      <c r="N79" s="62">
+      <c r="M79" s="81"/>
+      <c r="N79" s="61">
         <f>SUM(I79:M79)</f>
         <v>0</v>
       </c>
       <c r="O79" s="37"/>
-      <c r="P79" s="144"/>
-      <c r="Q79" s="145"/>
-      <c r="R79" s="145"/>
-      <c r="S79" s="145"/>
-      <c r="T79" s="145"/>
+      <c r="P79" s="114"/>
+      <c r="Q79" s="115"/>
+      <c r="R79" s="115"/>
+      <c r="S79" s="115"/>
+      <c r="T79" s="115"/>
       <c r="U79" s="40">
         <f>ROUND(((P79*I79)+(Q79*J79)+(R79*K79)+(S79*L79)+(T79*M79)),3)</f>
         <v>0</v>
@@ -9696,26 +9591,26 @@
       <c r="Y79" s="51"/>
       <c r="Z79" s="42"/>
       <c r="AA79" s="42"/>
-      <c r="AB79" s="73" t="e">
+      <c r="AB79" s="70" t="e">
         <f>(((((W79*I79)+(X79*J79)+(Y79*K79)+(Z79*L79)+(AA79*M79))/$L$2)))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AC79" s="78" t="e">
+      <c r="AC79" s="75" t="e">
         <f t="shared" ref="AC79" si="52">ROUND(11*AB79,3)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD79" s="75" t="e">
+      <c r="AD79" s="72" t="e">
         <f t="shared" ref="AD79" si="53">IF(AC79&gt;=11,11,AC79)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE79" s="116">
+      <c r="AE79" s="100">
         <f>IF(U80&gt;=94,4,IF(U80&gt;=91,3.9,IF(U80&gt;=88,3.8,IF(U80&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF79" s="43">
         <v>0.3</v>
       </c>
-      <c r="AG79" s="117">
+      <c r="AG79" s="101">
         <v>17</v>
       </c>
       <c r="AH79" s="44" t="e">
@@ -9740,29 +9635,29 @@
       <c r="AO79" s="50"/>
     </row>
     <row r="80" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A80" s="91"/>
-      <c r="B80" s="89"/>
-      <c r="C80" s="194" t="s">
-        <v>48</v>
-      </c>
-      <c r="D80" s="195"/>
-      <c r="E80" s="195"/>
-      <c r="F80" s="195"/>
-      <c r="G80" s="196"/>
+      <c r="A80" s="85"/>
+      <c r="B80" s="83"/>
+      <c r="C80" s="118" t="s">
+        <v>47</v>
+      </c>
+      <c r="D80" s="119"/>
+      <c r="E80" s="119"/>
+      <c r="F80" s="119"/>
+      <c r="G80" s="120"/>
       <c r="H80" s="34"/>
-      <c r="I80" s="57"/>
-      <c r="J80" s="61"/>
-      <c r="K80" s="61"/>
-      <c r="L80" s="61"/>
-      <c r="M80" s="85"/>
-      <c r="N80" s="62"/>
+      <c r="I80" s="56"/>
+      <c r="J80" s="60"/>
+      <c r="K80" s="60"/>
+      <c r="L80" s="60"/>
+      <c r="M80" s="80"/>
+      <c r="N80" s="61"/>
       <c r="O80" s="37"/>
-      <c r="P80" s="147"/>
-      <c r="Q80" s="147"/>
-      <c r="R80" s="145"/>
-      <c r="S80" s="147"/>
-      <c r="T80" s="147"/>
-      <c r="U80" s="77">
+      <c r="P80" s="117"/>
+      <c r="Q80" s="117"/>
+      <c r="R80" s="115"/>
+      <c r="S80" s="117"/>
+      <c r="T80" s="117"/>
+      <c r="U80" s="74">
         <f>(I79*P80)+(J79*Q80)+(K79*R80)+(L79*S80)+(M79*T80)</f>
         <v>0</v>
       </c>
@@ -9772,12 +9667,12 @@
       <c r="Y80" s="42"/>
       <c r="Z80" s="42"/>
       <c r="AA80" s="42"/>
-      <c r="AB80" s="73"/>
-      <c r="AC80" s="78"/>
-      <c r="AD80" s="74"/>
-      <c r="AE80" s="116"/>
+      <c r="AB80" s="70"/>
+      <c r="AC80" s="75"/>
+      <c r="AD80" s="71"/>
+      <c r="AE80" s="100"/>
       <c r="AF80" s="43"/>
-      <c r="AG80" s="65"/>
+      <c r="AG80" s="64"/>
       <c r="AH80" s="44"/>
       <c r="AI80" s="41"/>
       <c r="AJ80" s="45"/>
@@ -9788,29 +9683,29 @@
       <c r="AO80" s="50"/>
     </row>
     <row r="81" spans="1:41" s="22" customFormat="1" ht="51.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A81" s="90"/>
-      <c r="B81" s="88"/>
-      <c r="C81" s="52"/>
-      <c r="D81" s="82"/>
-      <c r="E81" s="82"/>
-      <c r="F81" s="82"/>
-      <c r="G81" s="81"/>
+      <c r="A81" s="84"/>
+      <c r="B81" s="82"/>
+      <c r="C81" s="173"/>
+      <c r="D81" s="172"/>
+      <c r="E81" s="173"/>
+      <c r="F81" s="173"/>
+      <c r="G81" s="113"/>
       <c r="H81" s="34"/>
       <c r="I81" s="35"/>
       <c r="J81" s="36"/>
       <c r="K81" s="36"/>
       <c r="L81" s="36"/>
-      <c r="M81" s="86"/>
-      <c r="N81" s="62">
+      <c r="M81" s="81"/>
+      <c r="N81" s="61">
         <f>SUM(I81:M81)</f>
         <v>0</v>
       </c>
       <c r="O81" s="37"/>
-      <c r="P81" s="144"/>
-      <c r="Q81" s="145"/>
-      <c r="R81" s="145"/>
-      <c r="S81" s="145"/>
-      <c r="T81" s="145"/>
+      <c r="P81" s="114"/>
+      <c r="Q81" s="115"/>
+      <c r="R81" s="115"/>
+      <c r="S81" s="115"/>
+      <c r="T81" s="115"/>
       <c r="U81" s="40">
         <f>ROUND(((P81*I81)+(Q81*J81)+(R81*K81)+(S81*L81)+(T81*M81)),3)</f>
         <v>0</v>
@@ -9824,26 +9719,26 @@
       <c r="Y81" s="42"/>
       <c r="Z81" s="42"/>
       <c r="AA81" s="42"/>
-      <c r="AB81" s="73" t="e">
+      <c r="AB81" s="70" t="e">
         <f>(((((W81*I81)+(X81*J81)+(Y81*K81)+(Z81*L81)+(AA81*M81))/$L$2)))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AC81" s="78" t="e">
+      <c r="AC81" s="75" t="e">
         <f>ROUND(11*AB81,3)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD81" s="75" t="e">
+      <c r="AD81" s="72" t="e">
         <f t="shared" ref="AD81" si="54">IF(AC81&gt;=11,11,AC81)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE81" s="116">
+      <c r="AE81" s="100">
         <f>IF(U82&gt;=94,4,IF(U82&gt;=91,3.9,IF(U82&gt;=88,3.8,IF(U82&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF81" s="43">
         <v>0.2</v>
       </c>
-      <c r="AG81" s="117">
+      <c r="AG81" s="101">
         <v>17</v>
       </c>
       <c r="AH81" s="44" t="e">
@@ -9868,29 +9763,29 @@
       <c r="AO81" s="50"/>
     </row>
     <row r="82" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A82" s="91"/>
-      <c r="B82" s="89"/>
-      <c r="C82" s="194" t="s">
-        <v>48</v>
-      </c>
-      <c r="D82" s="195"/>
-      <c r="E82" s="195"/>
-      <c r="F82" s="195"/>
-      <c r="G82" s="196"/>
+      <c r="A82" s="85"/>
+      <c r="B82" s="83"/>
+      <c r="C82" s="118" t="s">
+        <v>47</v>
+      </c>
+      <c r="D82" s="119"/>
+      <c r="E82" s="119"/>
+      <c r="F82" s="119"/>
+      <c r="G82" s="120"/>
       <c r="H82" s="34"/>
-      <c r="I82" s="57"/>
-      <c r="J82" s="61"/>
-      <c r="K82" s="61"/>
-      <c r="L82" s="61"/>
-      <c r="M82" s="85"/>
-      <c r="N82" s="62"/>
+      <c r="I82" s="56"/>
+      <c r="J82" s="60"/>
+      <c r="K82" s="60"/>
+      <c r="L82" s="60"/>
+      <c r="M82" s="80"/>
+      <c r="N82" s="61"/>
       <c r="O82" s="37"/>
-      <c r="P82" s="146"/>
-      <c r="Q82" s="147"/>
-      <c r="R82" s="147"/>
-      <c r="S82" s="147"/>
-      <c r="T82" s="147"/>
-      <c r="U82" s="77">
+      <c r="P82" s="116"/>
+      <c r="Q82" s="117"/>
+      <c r="R82" s="117"/>
+      <c r="S82" s="117"/>
+      <c r="T82" s="117"/>
+      <c r="U82" s="74">
         <f>(I81*P82)+(J81*Q82)+(K81*R82)+(L81*S82)+(M81*T82)</f>
         <v>0</v>
       </c>
@@ -9900,12 +9795,12 @@
       <c r="Y82" s="42"/>
       <c r="Z82" s="42"/>
       <c r="AA82" s="42"/>
-      <c r="AB82" s="73"/>
-      <c r="AC82" s="78"/>
-      <c r="AD82" s="74"/>
-      <c r="AE82" s="116"/>
+      <c r="AB82" s="70"/>
+      <c r="AC82" s="75"/>
+      <c r="AD82" s="71"/>
+      <c r="AE82" s="100"/>
       <c r="AF82" s="43"/>
-      <c r="AG82" s="65"/>
+      <c r="AG82" s="64"/>
       <c r="AH82" s="44"/>
       <c r="AI82" s="41"/>
       <c r="AJ82" s="45"/>
@@ -9916,29 +9811,29 @@
       <c r="AO82" s="50"/>
     </row>
     <row r="83" spans="1:41" s="22" customFormat="1" ht="51.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A83" s="90"/>
-      <c r="B83" s="88"/>
-      <c r="C83" s="53"/>
-      <c r="D83" s="82"/>
-      <c r="E83" s="53"/>
-      <c r="F83" s="82"/>
-      <c r="G83" s="80"/>
+      <c r="A83" s="84"/>
+      <c r="B83" s="82"/>
+      <c r="C83" s="173"/>
+      <c r="D83" s="172"/>
+      <c r="E83" s="173"/>
+      <c r="F83" s="173"/>
+      <c r="G83" s="113"/>
       <c r="H83" s="34"/>
       <c r="I83" s="35"/>
       <c r="J83" s="36"/>
       <c r="K83" s="36"/>
       <c r="L83" s="36"/>
-      <c r="M83" s="86"/>
-      <c r="N83" s="62">
+      <c r="M83" s="81"/>
+      <c r="N83" s="61">
         <f>SUM(I83:M83)</f>
         <v>0</v>
       </c>
       <c r="O83" s="37"/>
-      <c r="P83" s="144"/>
-      <c r="Q83" s="145"/>
-      <c r="R83" s="145"/>
-      <c r="S83" s="145"/>
-      <c r="T83" s="145"/>
+      <c r="P83" s="114"/>
+      <c r="Q83" s="115"/>
+      <c r="R83" s="115"/>
+      <c r="S83" s="115"/>
+      <c r="T83" s="115"/>
       <c r="U83" s="40">
         <f>ROUND(((P83*I83)+(Q83*J83)+(R83*K83)+(S83*L83)+(T83*M83)),3)</f>
         <v>0</v>
@@ -9952,26 +9847,26 @@
       <c r="Y83" s="42"/>
       <c r="Z83" s="42"/>
       <c r="AA83" s="42"/>
-      <c r="AB83" s="73" t="e">
+      <c r="AB83" s="70" t="e">
         <f>(((((W83*I83)+(X83*J83)+(Y83*K83)+(Z83*L83)+(AA83*M83))/$L$2)))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AC83" s="78" t="e">
+      <c r="AC83" s="75" t="e">
         <f t="shared" ref="AC83:AC89" si="55">ROUND(11*AB83,3)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD83" s="75" t="e">
+      <c r="AD83" s="72" t="e">
         <f>IF(AC83&gt;=11,11,AC83)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE83" s="116">
+      <c r="AE83" s="100">
         <f>IF(U84&gt;=94,4,IF(U84&gt;=91,3.9,IF(U84&gt;=88,3.8,IF(U84&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF83" s="43">
         <v>0.3</v>
       </c>
-      <c r="AG83" s="117">
+      <c r="AG83" s="101">
         <v>17</v>
       </c>
       <c r="AH83" s="44" t="e">
@@ -9996,29 +9891,29 @@
       <c r="AO83" s="50"/>
     </row>
     <row r="84" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A84" s="91"/>
-      <c r="B84" s="88"/>
-      <c r="C84" s="194" t="s">
-        <v>48</v>
-      </c>
-      <c r="D84" s="195"/>
-      <c r="E84" s="195"/>
-      <c r="F84" s="195"/>
-      <c r="G84" s="196"/>
+      <c r="A84" s="85"/>
+      <c r="B84" s="82"/>
+      <c r="C84" s="118" t="s">
+        <v>47</v>
+      </c>
+      <c r="D84" s="119"/>
+      <c r="E84" s="119"/>
+      <c r="F84" s="119"/>
+      <c r="G84" s="120"/>
       <c r="H84" s="34"/>
-      <c r="I84" s="57"/>
-      <c r="J84" s="61"/>
-      <c r="K84" s="61"/>
-      <c r="L84" s="61"/>
-      <c r="M84" s="85"/>
-      <c r="N84" s="62"/>
+      <c r="I84" s="56"/>
+      <c r="J84" s="60"/>
+      <c r="K84" s="60"/>
+      <c r="L84" s="60"/>
+      <c r="M84" s="80"/>
+      <c r="N84" s="61"/>
       <c r="O84" s="37"/>
-      <c r="P84" s="146"/>
-      <c r="Q84" s="147"/>
-      <c r="R84" s="147"/>
-      <c r="S84" s="147"/>
-      <c r="T84" s="147"/>
-      <c r="U84" s="77">
+      <c r="P84" s="116"/>
+      <c r="Q84" s="117"/>
+      <c r="R84" s="117"/>
+      <c r="S84" s="117"/>
+      <c r="T84" s="117"/>
+      <c r="U84" s="74">
         <f>(I83*P84)+(J83*Q84)+(K83*R84)+(L83*S84)+(M83*T84)</f>
         <v>0</v>
       </c>
@@ -10028,12 +9923,12 @@
       <c r="Y84" s="42"/>
       <c r="Z84" s="42"/>
       <c r="AA84" s="42"/>
-      <c r="AB84" s="73"/>
-      <c r="AC84" s="78"/>
-      <c r="AD84" s="74"/>
-      <c r="AE84" s="116"/>
+      <c r="AB84" s="70"/>
+      <c r="AC84" s="75"/>
+      <c r="AD84" s="71"/>
+      <c r="AE84" s="100"/>
       <c r="AF84" s="43"/>
-      <c r="AG84" s="65"/>
+      <c r="AG84" s="64"/>
       <c r="AH84" s="44"/>
       <c r="AI84" s="41"/>
       <c r="AJ84" s="45"/>
@@ -10044,29 +9939,29 @@
       <c r="AO84" s="50"/>
     </row>
     <row r="85" spans="1:41" s="22" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A85" s="90"/>
-      <c r="B85" s="88"/>
-      <c r="C85" s="33"/>
-      <c r="D85" s="53"/>
-      <c r="E85" s="82"/>
-      <c r="F85" s="82"/>
-      <c r="G85" s="80"/>
-      <c r="H85" s="58"/>
+      <c r="A85" s="84"/>
+      <c r="B85" s="82"/>
+      <c r="C85" s="173"/>
+      <c r="D85" s="172"/>
+      <c r="E85" s="173"/>
+      <c r="F85" s="173"/>
+      <c r="G85" s="113"/>
+      <c r="H85" s="57"/>
       <c r="I85" s="35"/>
       <c r="J85" s="36"/>
-      <c r="K85" s="61"/>
+      <c r="K85" s="60"/>
       <c r="L85" s="36"/>
-      <c r="M85" s="86"/>
-      <c r="N85" s="62">
+      <c r="M85" s="81"/>
+      <c r="N85" s="61">
         <f>SUM(I85:M85)</f>
         <v>0</v>
       </c>
       <c r="O85" s="37"/>
-      <c r="P85" s="144"/>
-      <c r="Q85" s="145"/>
-      <c r="R85" s="145"/>
-      <c r="S85" s="145"/>
-      <c r="T85" s="145"/>
+      <c r="P85" s="114"/>
+      <c r="Q85" s="115"/>
+      <c r="R85" s="115"/>
+      <c r="S85" s="115"/>
+      <c r="T85" s="115"/>
       <c r="U85" s="40">
         <f>ROUND(((P85*I85)+(Q85*J85)+(R85*K85)+(S85*L85)+(T85*M85)),3)</f>
         <v>0</v>
@@ -10080,26 +9975,26 @@
       <c r="Y85" s="42"/>
       <c r="Z85" s="51"/>
       <c r="AA85" s="42"/>
-      <c r="AB85" s="73" t="e">
+      <c r="AB85" s="70" t="e">
         <f>(((((W85*I85)+(X85*J85)+(Y85*K85)+(Z85*L85)+(AA85*M85))/$L$2)))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AC85" s="78" t="e">
+      <c r="AC85" s="75" t="e">
         <f t="shared" si="55"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD85" s="75" t="e">
+      <c r="AD85" s="72" t="e">
         <f>IF(AC85&gt;=11,11,AC85)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE85" s="116">
+      <c r="AE85" s="100">
         <f>IF(U86&gt;=94,4,IF(U86&gt;=91,3.9,IF(U86&gt;=88,3.8,IF(U86&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF85" s="43">
         <v>0.3</v>
       </c>
-      <c r="AG85" s="117">
+      <c r="AG85" s="101">
         <v>17</v>
       </c>
       <c r="AH85" s="44" t="e">
@@ -10118,29 +10013,29 @@
       <c r="AO85" s="50"/>
     </row>
     <row r="86" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A86" s="91"/>
-      <c r="B86" s="89"/>
-      <c r="C86" s="194" t="s">
-        <v>48</v>
-      </c>
-      <c r="D86" s="195"/>
-      <c r="E86" s="195"/>
-      <c r="F86" s="195"/>
-      <c r="G86" s="196"/>
+      <c r="A86" s="85"/>
+      <c r="B86" s="83"/>
+      <c r="C86" s="118" t="s">
+        <v>47</v>
+      </c>
+      <c r="D86" s="119"/>
+      <c r="E86" s="119"/>
+      <c r="F86" s="119"/>
+      <c r="G86" s="120"/>
       <c r="H86" s="34"/>
-      <c r="I86" s="57"/>
-      <c r="J86" s="61"/>
-      <c r="K86" s="61"/>
-      <c r="L86" s="61"/>
-      <c r="M86" s="85"/>
-      <c r="N86" s="62"/>
+      <c r="I86" s="56"/>
+      <c r="J86" s="60"/>
+      <c r="K86" s="60"/>
+      <c r="L86" s="60"/>
+      <c r="M86" s="80"/>
+      <c r="N86" s="61"/>
       <c r="O86" s="37"/>
-      <c r="P86" s="146"/>
-      <c r="Q86" s="145"/>
-      <c r="R86" s="145"/>
-      <c r="S86" s="147"/>
-      <c r="T86" s="147"/>
-      <c r="U86" s="77">
+      <c r="P86" s="116"/>
+      <c r="Q86" s="115"/>
+      <c r="R86" s="115"/>
+      <c r="S86" s="117"/>
+      <c r="T86" s="117"/>
+      <c r="U86" s="74">
         <f>(I85*P86)+(J85*Q86)+(K85*R86)+(L85*S86)+(M85*T86)</f>
         <v>0</v>
       </c>
@@ -10150,12 +10045,12 @@
       <c r="Y86" s="42"/>
       <c r="Z86" s="42"/>
       <c r="AA86" s="42"/>
-      <c r="AB86" s="73"/>
-      <c r="AC86" s="78"/>
-      <c r="AD86" s="74"/>
-      <c r="AE86" s="116"/>
+      <c r="AB86" s="70"/>
+      <c r="AC86" s="75"/>
+      <c r="AD86" s="71"/>
+      <c r="AE86" s="100"/>
       <c r="AF86" s="43"/>
-      <c r="AG86" s="65"/>
+      <c r="AG86" s="64"/>
       <c r="AH86" s="44"/>
       <c r="AI86" s="41"/>
       <c r="AJ86" s="45"/>
@@ -10166,29 +10061,29 @@
       <c r="AO86" s="50"/>
     </row>
     <row r="87" spans="1:41" s="22" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A87" s="90"/>
-      <c r="B87" s="88"/>
+      <c r="A87" s="84"/>
+      <c r="B87" s="82"/>
       <c r="C87" s="52"/>
       <c r="D87" s="53"/>
       <c r="E87" s="53"/>
       <c r="F87" s="53"/>
-      <c r="G87" s="68"/>
-      <c r="H87" s="58"/>
+      <c r="G87" s="66"/>
+      <c r="H87" s="57"/>
       <c r="I87" s="35"/>
       <c r="J87" s="36"/>
       <c r="K87" s="36"/>
       <c r="L87" s="36"/>
-      <c r="M87" s="86"/>
-      <c r="N87" s="62">
+      <c r="M87" s="81"/>
+      <c r="N87" s="61">
         <f>SUM(I87:M87)</f>
         <v>0</v>
       </c>
       <c r="O87" s="37"/>
-      <c r="P87" s="144"/>
-      <c r="Q87" s="145"/>
-      <c r="R87" s="145"/>
-      <c r="S87" s="145"/>
-      <c r="T87" s="145"/>
+      <c r="P87" s="114"/>
+      <c r="Q87" s="115"/>
+      <c r="R87" s="115"/>
+      <c r="S87" s="115"/>
+      <c r="T87" s="115"/>
       <c r="U87" s="40">
         <f>ROUND(((P87*I87)+(Q87*J87)+(R87*K87)+(S87*L87)+(T87*M87)),3)</f>
         <v>0</v>
@@ -10202,26 +10097,26 @@
       <c r="Y87" s="42"/>
       <c r="Z87" s="42"/>
       <c r="AA87" s="42"/>
-      <c r="AB87" s="73" t="e">
+      <c r="AB87" s="70" t="e">
         <f>(((((W87*I87)+(X87*J87)+(Y87*K87)+(Z87*L87)+(AA87*M87))/$L$2)))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AC87" s="78" t="e">
+      <c r="AC87" s="75" t="e">
         <f t="shared" ref="AC87" si="56">ROUND(11*AB87,3)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD87" s="75" t="e">
+      <c r="AD87" s="72" t="e">
         <f t="shared" ref="AD87" si="57">IF(AC87&gt;=11,11,AC87)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE87" s="116">
+      <c r="AE87" s="100">
         <f>IF(U88&gt;=94,4,IF(U88&gt;=91,3.9,IF(U88&gt;=88,3.8,IF(U88&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF87" s="43">
         <v>0.3</v>
       </c>
-      <c r="AG87" s="117">
+      <c r="AG87" s="101">
         <v>17</v>
       </c>
       <c r="AH87" s="44" t="e">
@@ -10246,29 +10141,29 @@
       <c r="AO87" s="50"/>
     </row>
     <row r="88" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A88" s="91"/>
-      <c r="B88" s="89"/>
-      <c r="C88" s="194" t="s">
-        <v>48</v>
-      </c>
-      <c r="D88" s="195"/>
-      <c r="E88" s="195"/>
-      <c r="F88" s="195"/>
-      <c r="G88" s="196"/>
+      <c r="A88" s="85"/>
+      <c r="B88" s="83"/>
+      <c r="C88" s="118" t="s">
+        <v>47</v>
+      </c>
+      <c r="D88" s="119"/>
+      <c r="E88" s="119"/>
+      <c r="F88" s="119"/>
+      <c r="G88" s="120"/>
       <c r="H88" s="34"/>
-      <c r="I88" s="57"/>
-      <c r="J88" s="61"/>
-      <c r="K88" s="61"/>
-      <c r="L88" s="61"/>
-      <c r="M88" s="85"/>
-      <c r="N88" s="62"/>
+      <c r="I88" s="56"/>
+      <c r="J88" s="60"/>
+      <c r="K88" s="60"/>
+      <c r="L88" s="60"/>
+      <c r="M88" s="80"/>
+      <c r="N88" s="61"/>
       <c r="O88" s="37"/>
-      <c r="P88" s="146"/>
-      <c r="Q88" s="147"/>
-      <c r="R88" s="147"/>
-      <c r="S88" s="147"/>
-      <c r="T88" s="147"/>
-      <c r="U88" s="77">
+      <c r="P88" s="116"/>
+      <c r="Q88" s="117"/>
+      <c r="R88" s="117"/>
+      <c r="S88" s="117"/>
+      <c r="T88" s="117"/>
+      <c r="U88" s="74">
         <f>(I87*P88)+(J87*Q88)+(K87*R88)+(L87*S88)+(M87*T88)</f>
         <v>0</v>
       </c>
@@ -10278,12 +10173,12 @@
       <c r="Y88" s="42"/>
       <c r="Z88" s="42"/>
       <c r="AA88" s="42"/>
-      <c r="AB88" s="73"/>
-      <c r="AC88" s="78"/>
-      <c r="AD88" s="74"/>
-      <c r="AE88" s="116"/>
+      <c r="AB88" s="70"/>
+      <c r="AC88" s="75"/>
+      <c r="AD88" s="71"/>
+      <c r="AE88" s="100"/>
       <c r="AF88" s="43"/>
-      <c r="AG88" s="65"/>
+      <c r="AG88" s="64"/>
       <c r="AH88" s="44"/>
       <c r="AI88" s="41"/>
       <c r="AJ88" s="45"/>
@@ -10295,28 +10190,28 @@
     </row>
     <row r="89" spans="1:41" s="22" customFormat="1" ht="51.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" s="32"/>
-      <c r="B89" s="64"/>
-      <c r="C89" s="55"/>
+      <c r="B89" s="63"/>
+      <c r="C89" s="54"/>
       <c r="D89" s="52"/>
       <c r="E89" s="33"/>
       <c r="F89" s="53"/>
-      <c r="G89" s="81"/>
-      <c r="H89" s="58"/>
+      <c r="G89" s="77"/>
+      <c r="H89" s="57"/>
       <c r="I89" s="35"/>
       <c r="J89" s="36"/>
       <c r="K89" s="36"/>
       <c r="L89" s="36"/>
-      <c r="M89" s="86"/>
-      <c r="N89" s="62">
+      <c r="M89" s="81"/>
+      <c r="N89" s="61">
         <f>SUM(I89:M89)</f>
         <v>0</v>
       </c>
       <c r="O89" s="37"/>
-      <c r="P89" s="144"/>
-      <c r="Q89" s="145"/>
-      <c r="R89" s="145"/>
-      <c r="S89" s="145"/>
-      <c r="T89" s="145"/>
+      <c r="P89" s="114"/>
+      <c r="Q89" s="115"/>
+      <c r="R89" s="115"/>
+      <c r="S89" s="115"/>
+      <c r="T89" s="115"/>
       <c r="U89" s="40">
         <f>ROUND(((P89*I89)+(Q89*J89)+(R89*K89)+(S89*L89)+(T89*M89)),3)</f>
         <v>0</v>
@@ -10330,26 +10225,26 @@
       <c r="Y89" s="51"/>
       <c r="Z89" s="42"/>
       <c r="AA89" s="42"/>
-      <c r="AB89" s="73" t="e">
+      <c r="AB89" s="70" t="e">
         <f>(((((W89*I89)+(X89*J89)+(Y89*K89)+(Z89*L89)+(AA89*M89))/$L$2)))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AC89" s="78" t="e">
+      <c r="AC89" s="75" t="e">
         <f t="shared" si="55"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD89" s="75" t="e">
+      <c r="AD89" s="72" t="e">
         <f>IF(AC89&gt;=11,11,AC89)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE89" s="116">
+      <c r="AE89" s="100">
         <f>IF(U90&gt;=94,4,IF(U90&gt;=91,3.9,IF(U90&gt;=88,3.8,IF(U90&gt;=85,3.7,3.6))))</f>
         <v>3.6</v>
       </c>
       <c r="AF89" s="43">
         <v>0.3</v>
       </c>
-      <c r="AG89" s="117">
+      <c r="AG89" s="101">
         <v>17</v>
       </c>
       <c r="AH89" s="44" t="e">
@@ -10374,29 +10269,29 @@
       <c r="AO89" s="50"/>
     </row>
     <row r="90" spans="1:41" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A90" s="59"/>
-      <c r="B90" s="64"/>
-      <c r="C90" s="194" t="s">
-        <v>48</v>
-      </c>
-      <c r="D90" s="195"/>
-      <c r="E90" s="195"/>
-      <c r="F90" s="195"/>
-      <c r="G90" s="196"/>
+      <c r="A90" s="58"/>
+      <c r="B90" s="63"/>
+      <c r="C90" s="118" t="s">
+        <v>47</v>
+      </c>
+      <c r="D90" s="119"/>
+      <c r="E90" s="119"/>
+      <c r="F90" s="119"/>
+      <c r="G90" s="120"/>
       <c r="H90" s="34"/>
-      <c r="I90" s="57"/>
-      <c r="J90" s="61"/>
-      <c r="K90" s="61"/>
-      <c r="L90" s="61"/>
-      <c r="M90" s="85"/>
-      <c r="N90" s="62"/>
+      <c r="I90" s="56"/>
+      <c r="J90" s="60"/>
+      <c r="K90" s="60"/>
+      <c r="L90" s="60"/>
+      <c r="M90" s="80"/>
+      <c r="N90" s="61"/>
       <c r="O90" s="37"/>
-      <c r="P90" s="146"/>
-      <c r="Q90" s="147"/>
-      <c r="R90" s="147"/>
-      <c r="S90" s="147"/>
-      <c r="T90" s="147"/>
-      <c r="U90" s="77">
+      <c r="P90" s="116"/>
+      <c r="Q90" s="117"/>
+      <c r="R90" s="117"/>
+      <c r="S90" s="117"/>
+      <c r="T90" s="117"/>
+      <c r="U90" s="74">
         <f>(I89*P90)+(J89*Q90)+(K89*R90)+(L89*S90)+(M89*T90)</f>
         <v>0</v>
       </c>
@@ -10406,12 +10301,12 @@
       <c r="Y90" s="42"/>
       <c r="Z90" s="42"/>
       <c r="AA90" s="42"/>
-      <c r="AB90" s="73"/>
-      <c r="AC90" s="78"/>
-      <c r="AD90" s="74"/>
-      <c r="AE90" s="116"/>
+      <c r="AB90" s="70"/>
+      <c r="AC90" s="75"/>
+      <c r="AD90" s="71"/>
+      <c r="AE90" s="100"/>
       <c r="AF90" s="43"/>
-      <c r="AG90" s="65"/>
+      <c r="AG90" s="64"/>
       <c r="AH90" s="44"/>
       <c r="AI90" s="41"/>
       <c r="AJ90" s="45"/>
@@ -10423,14 +10318,53 @@
     </row>
   </sheetData>
   <mergeCells count="71">
-    <mergeCell ref="C88:G88"/>
-    <mergeCell ref="C90:G90"/>
-    <mergeCell ref="C74:G74"/>
-    <mergeCell ref="C76:G76"/>
-    <mergeCell ref="C78:G78"/>
-    <mergeCell ref="C80:G80"/>
-    <mergeCell ref="C82:G82"/>
-    <mergeCell ref="C84:G84"/>
+    <mergeCell ref="AC1:AD1"/>
+    <mergeCell ref="AE1:AG1"/>
+    <mergeCell ref="X2:Y2"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="L1:N1"/>
+    <mergeCell ref="Z1:AA1"/>
+    <mergeCell ref="Z2:AA2"/>
+    <mergeCell ref="AC2:AD2"/>
+    <mergeCell ref="AE2:AG2"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:H3"/>
+    <mergeCell ref="I3:M3"/>
+    <mergeCell ref="N3:N4"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="P2:T2"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="AK3:AK4"/>
+    <mergeCell ref="AL3:AL4"/>
+    <mergeCell ref="AM3:AM4"/>
+    <mergeCell ref="AO3:AO4"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="U3:AH3"/>
+    <mergeCell ref="AJ3:AJ4"/>
+    <mergeCell ref="O3:O4"/>
+    <mergeCell ref="P3:T3"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="C60:G60"/>
+    <mergeCell ref="C14:G14"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="C56:G56"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="C36:G36"/>
     <mergeCell ref="C42:G42"/>
     <mergeCell ref="C38:G38"/>
     <mergeCell ref="C86:G86"/>
@@ -10447,53 +10381,14 @@
     <mergeCell ref="C64:G64"/>
     <mergeCell ref="C66:G66"/>
     <mergeCell ref="C58:G58"/>
-    <mergeCell ref="C60:G60"/>
-    <mergeCell ref="C14:G14"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="C56:G56"/>
-    <mergeCell ref="C44:G44"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="AK3:AK4"/>
-    <mergeCell ref="AL3:AL4"/>
-    <mergeCell ref="AM3:AM4"/>
-    <mergeCell ref="AO3:AO4"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="U3:AH3"/>
-    <mergeCell ref="AJ3:AJ4"/>
-    <mergeCell ref="O3:O4"/>
-    <mergeCell ref="P3:T3"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="P2:T2"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:H3"/>
-    <mergeCell ref="I3:M3"/>
-    <mergeCell ref="N3:N4"/>
-    <mergeCell ref="AC1:AD1"/>
-    <mergeCell ref="AE1:AG1"/>
-    <mergeCell ref="X2:Y2"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="H1:J1"/>
-    <mergeCell ref="L1:N1"/>
-    <mergeCell ref="Z1:AA1"/>
-    <mergeCell ref="Z2:AA2"/>
-    <mergeCell ref="AC2:AD2"/>
-    <mergeCell ref="AE2:AG2"/>
+    <mergeCell ref="C88:G88"/>
+    <mergeCell ref="C90:G90"/>
+    <mergeCell ref="C74:G74"/>
+    <mergeCell ref="C76:G76"/>
+    <mergeCell ref="C78:G78"/>
+    <mergeCell ref="C80:G80"/>
+    <mergeCell ref="C82:G82"/>
+    <mergeCell ref="C84:G84"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
